--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -1291,25 +1291,25 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="M9" t="n">
-        <v>0.277992277992278</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05800653594771243</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1327,13 +1327,13 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1062129221359085</v>
+        <v>0.10658480352762</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1062129221359085</v>
+        <v>0.10658480352762</v>
       </c>
       <c r="X9" t="n">
         <v>0.3842052001281865</v>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -1850,16 +1850,16 @@
         <v>2.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="N15" t="n">
-        <v>0.375767498976668</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>1.298076923076923</v>
+        <v>1.30952380952381</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB47"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5472927597399772</v>
+        <v>0.5220408361549084</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3174877309452435</v>
+        <v>0.3379505868208877</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1352195093147789</v>
+        <v>0.140008577024204</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07446294626865269</v>
+        <v>-0.09971486985372147</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.07446294626865269</v>
+        <v>-0.09971486985372147</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5472927597399772</v>
+        <v>0.5220408361549084</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>6.884337015187532</v>
+        <v>6.566695772639449</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.884337015187532</v>
+        <v>6.566695772639449</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2100382114772122</v>
+        <v>0.207553355472195</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2980519455785725</v>
+        <v>0.3037866193818217</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4919098429442151</v>
+        <v>0.4886600251459832</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1961635515511977</v>
+        <v>-0.1994133693494297</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1961635515511977</v>
+        <v>-0.1994133693494297</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4919098429442151</v>
+        <v>0.4886600251459832</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>6.187681235770201</v>
+        <v>6.14680212570923</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.187681235770201</v>
+        <v>6.14680212570923</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4465517429240594</v>
+        <v>0.4465820355191964</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3099576327625041</v>
+        <v>0.3101629369696617</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2434906243134364</v>
+        <v>0.243255027511142</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.336819888577925</v>
+        <v>-0.336789595982788</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.336819888577925</v>
+        <v>-0.336789595982788</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4465517429240594</v>
+        <v>0.4465820355191964</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>5.617126553015594</v>
+        <v>5.617507600325788</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.617126553015594</v>
+        <v>5.617507600325788</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2312737815347075</v>
+        <v>0.2370212419216871</v>
       </c>
       <c r="R5" t="n">
-        <v>0.364304302167788</v>
+        <v>0.3695038916916568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4044219162975047</v>
+        <v>0.3934748663866562</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07357752833976383</v>
+        <v>0.06263047842891528</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07357752833976383</v>
+        <v>0.06263047842891528</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4044219162975047</v>
+        <v>0.3934748663866562</v>
       </c>
       <c r="Y5" t="n">
         <v>2.88</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>5.087179975563296</v>
+        <v>4.949478207054307</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.087179975563296</v>
+        <v>4.949478207054307</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4860935572145377</v>
+        <v>0.4897759797988454</v>
       </c>
       <c r="R6" t="n">
-        <v>0.346874166327044</v>
+        <v>0.3433771863567628</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1670322764584181</v>
+        <v>0.1668468338443916</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2232249406992314</v>
+        <v>-0.2195425181149238</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2232249406992314</v>
+        <v>-0.2195425181149238</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4860935572145377</v>
+        <v>0.4897759797988454</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>6.114518800442628</v>
+        <v>6.160839599779999</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.114518800442628</v>
+        <v>6.160839599779999</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3022649971005809</v>
+        <v>0.3043641035498073</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3669991019301996</v>
+        <v>0.3687775967439796</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3307359009692193</v>
+        <v>0.3268582997062129</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09443378126511648</v>
+        <v>0.09621227607889649</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09443378126511648</v>
+        <v>0.09621227607889649</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3669991019301996</v>
+        <v>0.3687775967439796</v>
       </c>
       <c r="Y7" t="n">
         <v>3.5</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>4.616442401246155</v>
+        <v>4.638813897049684</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.616442401246155</v>
+        <v>4.638813897049684</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3743799427639963</v>
+        <v>0.3680185758941866</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3946336719648086</v>
+        <v>0.4001103182268416</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2309863852711951</v>
+        <v>0.231871105878972</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1238003386314753</v>
+        <v>0.1292769848935082</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1238003386314753</v>
+        <v>0.1292769848935082</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3946336719648086</v>
+        <v>0.4001103182268416</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>4.964054698325397</v>
+        <v>5.032944845161461</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.964054698325397</v>
+        <v>5.032944845161461</v>
       </c>
     </row>
     <row r="9">
@@ -1291,52 +1291,52 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3997567403202919</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2763024528684371</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.323940806811271</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.06447714815933714</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3144227816646827</v>
+        <v>0.3113709705938002</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3842052001281865</v>
+        <v>0.3848328992815713</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3013720182071305</v>
+        <v>0.3037961301246284</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.10658480352762</v>
+        <v>0.1085304464131342</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.10658480352762</v>
+        <v>0.1085304464131342</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3842052001281865</v>
+        <v>0.3848328992815713</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>4.832876067877577</v>
+        <v>4.840771828307701</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.832876067877577</v>
+        <v>4.840771828307701</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2820683392247597</v>
+        <v>0.2801216700200164</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3380256032651838</v>
+        <v>0.3393572867730009</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3799060575100564</v>
+        <v>0.3805210432069825</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1289717221830999</v>
+        <v>-0.1283567364861737</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1289717221830999</v>
+        <v>-0.1283567364861737</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3799060575100564</v>
+        <v>0.3805210432069825</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>4.778797613279301</v>
+        <v>4.786533452502116</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.778797613279301</v>
+        <v>4.786533452502116</v>
       </c>
     </row>
     <row r="11">
@@ -1487,55 +1487,55 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="J11" t="n">
         <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1895352559438931</v>
+        <v>0.1789903110657828</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2429939178767861</v>
+        <v>0.2409484956654768</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5674708261793209</v>
+        <v>0.5800611932687404</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05521265161983724</v>
+        <v>0.06417039750373088</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1725710825428429</v>
+        <v>0.1638635360947085</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3082493863644105</v>
+        <v>0.3029693204168782</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5191795310927471</v>
+        <v>0.5331671434884132</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04829129508657382</v>
+        <v>-0.04689404978032718</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04829129508657382</v>
+        <v>-0.04689404978032718</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5191795310927471</v>
+        <v>0.5331671434884132</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1543,36 +1543,36 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>6.53070372267968</v>
+        <v>6.706652401071354</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.53070372267968</v>
+        <v>6.706652401071354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>manchester utd</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>manchester city</t>
-        </is>
-      </c>
       <c r="E12" t="n">
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,96 +1581,76 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>fa community shield</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2077442718852288</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1968103628386378</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.5954453652761335</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06969121317093152</v>
-      </c>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2992414176127644</v>
+        <v>0.4341283003984296</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3364340154000717</v>
+        <v>0.3532899363163176</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3643245669871641</v>
+        <v>0.2125817632852529</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>-0.2311207982889693</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.2311207982889693</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.3643245669871641</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.57</v>
-      </c>
+        <v>0.5658716996015704</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>4.582799712613659</v>
+        <v>7.118039510087844</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.582799712613659</v>
+        <v>7.118039510087844</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>stoke</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1679,78 +1659,76 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.171161652671968</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2477339709725852</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.5811043763554469</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06226002717230772</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4602908440200329</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2972663122500965</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2424428437298706</v>
+      </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>1.251404494382022</v>
-      </c>
+      <c r="X13" t="n">
+        <v>0.5397091559799672</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>6.788943675618493</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.788943675618493</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>leyton orient</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>newport</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1759,76 +1737,76 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.6263219741480611</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2291421856639248</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.1445358401880141</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06441525953721072</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3658167622948515</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3442914929513189</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2898917447538296</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="n">
-        <v>1.21875</v>
-      </c>
+      <c r="X14" t="n">
+        <v>0.6341832377051485</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>7.977323032410138</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.977323032410138</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>stockport county</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>blackburn</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1837,78 +1815,76 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3437815975733064</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2780586450960567</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3781597573306371</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05775401069518704</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5495091702158204</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2512022812302508</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.199288548553929</v>
+      </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
-        <v>1.30952380952381</v>
-      </c>
+      <c r="X15" t="n">
+        <v>0.4504908297841796</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>5.666675904792235</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.666675904792235</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>barrow</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>port vale</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1917,76 +1893,76 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.3765084473049075</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2614641995172969</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.3620273531777956</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06239316239316239</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4044071336571292</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3559653636716902</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2396275026711805</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>1.274509803921569</v>
-      </c>
+      <c r="X16" t="n">
+        <v>0.5955928663428708</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>7.491898883686916</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.491898883686916</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bolton</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>mansfield</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1995,76 +1971,76 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.5683355886332883</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2232746955345061</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2083897158322057</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06637806637806642</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6683911707294922</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2391716004562361</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.09243722881427212</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>1.207317073170732</v>
-      </c>
+      <c r="X17" t="n">
+        <v>0.3316088292705078</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>4.171271951404192</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.171271951404192</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bristol city</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>coventry</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2073,96 +2049,76 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2615384615384615</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06209150326797408</v>
-      </c>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4837268191341964</v>
+        <v>0.2981603243925068</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2733478735333315</v>
+        <v>0.3910006081310099</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2429253073324721</v>
+        <v>0.3108390674764833</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0.1144960499034272</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1144960499034272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>0.4837268191341964</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.55</v>
-      </c>
+        <v>0.6089993918689901</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>6.084747855583996</v>
+        <v>7.660538132575152</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.084747855583996</v>
+        <v>7.660538132575152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bromley</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>afc wimbledon</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2171,76 +2127,76 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3231597845601437</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2603231597845602</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.4165170556552962</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.06704980842911867</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2843609750436352</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3559417876989703</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3596972372573942</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="n">
-        <v>1.266990291262136</v>
-      </c>
+      <c r="X19" t="n">
+        <v>0.6403027627426058</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>8.054299882516377</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.054299882516377</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>burton</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>blackpool</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2249,76 +2205,76 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.3129548762736535</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.2503639010189229</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.4366812227074235</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.06511627906976747</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2243322171901986</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5079823808529856</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2676854019568154</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>1.252427184466019</v>
-      </c>
+      <c r="X20" t="n">
+        <v>0.4920176191470144</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AA20" t="n">
+        <v>6.18903694108346</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.18903694108346</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cambridge utd</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>qpr</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2327,78 +2283,76 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.2088709677419355</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2540322580645161</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.5370967741935484</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.06392106392106389</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5225684782528016</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3044504124414911</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1729811093057073</v>
+      </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
+      <c r="X21" t="n">
+        <v>0.4774315217471984</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AA21" t="n">
+        <v>6.005559983916345</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.005559983916345</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45514.45833333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cardiff</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bristol rovers</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2407,71 +2361,89 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>fa community shield</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="K22" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5884729329383249</v>
+        <v>0.5954453652761335</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2477780770266631</v>
+        <v>0.1968103628386378</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1637489900350121</v>
+        <v>0.2077442718852288</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06207093821510279</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+        <v>0.06969121317093152</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.563419184179024</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2681802783102836</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1684005375106921</v>
+      </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>-0.03202618109710942</v>
+      </c>
       <c r="V22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.03202618109710942</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.563419184179024</v>
+      </c>
       <c r="Y22" t="n">
-        <v>1.251700680272109</v>
+        <v>1.57</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.08718958122751</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.08718958122751</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>charlton</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>birmingham</t>
+          <t>stoke</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2491,25 +2463,25 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.1572297973961944</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2418919959941453</v>
       </c>
       <c r="N23" t="n">
-        <v>0.418835684482416</v>
+        <v>0.6008782066096602</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.06001959823615888</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -2520,12 +2492,12 @@
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>1.303738317757009</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2538,20 +2510,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>colchester</t>
+          <t>leyton orient</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>newport</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2571,25 +2543,25 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.33</v>
+        <v>1.48</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>0.216998191681736</v>
+        <v>0.6359687998581812</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.2295692253146606</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.1344619748271583</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06243525755720869</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2598,12 +2570,12 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>1.271451876019576</v>
+        <v>1.221698113207547</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2616,20 +2588,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>crawley</t>
+          <t>stockport county</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>swindon</t>
+          <t>blackburn</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2649,39 +2621,41 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.4</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>1.298181818181818</v>
+        <v>1.311428571428571</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2694,7 +2668,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2702,12 +2676,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>derby</t>
+          <t>barrow</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>chesterfield</t>
+          <t>port vale</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2727,25 +2701,25 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5991550377672512</v>
+        <v>0.4012738853503184</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2579695301497887</v>
+        <v>0.2619426751592356</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1428754320829599</v>
+        <v>0.3367834394904458</v>
       </c>
       <c r="O26" t="n">
-        <v>0.07678522194651238</v>
+        <v>0.06045254981425208</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2754,12 +2728,12 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>1.251552795031056</v>
+        <v>1.277669902912621</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2772,7 +2746,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2780,12 +2754,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fleetwood</t>
+          <t>bolton</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>west brom</t>
+          <t>mansfield</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2805,41 +2779,39 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>1.57</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1562352694704865</v>
+        <v>0.5683355886332883</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2466872675849787</v>
+        <v>0.2232746955345061</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5970774629445346</v>
+        <v>0.2083897158322057</v>
       </c>
       <c r="O27" t="n">
-        <v>0.06676723656274453</v>
+        <v>0.06637806637806642</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>1.244385733157199</v>
+        <v>1.207317073170732</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -2852,7 +2824,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2860,12 +2832,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>grimsby</t>
+          <t>bristol city</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>bradford city</t>
+          <t>coventry</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2885,52 +2857,72 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3632006498781478</v>
+        <v>0.4012738853503184</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2777416734362307</v>
+        <v>0.2619426751592356</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3590576766856215</v>
+        <v>0.3367834394904458</v>
       </c>
       <c r="O28" t="n">
-        <v>0.05896116855633737</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+        <v>0.06045254981425208</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4856024500446495</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.273266202941484</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2411313470138665</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.08432856469433103</v>
+      </c>
       <c r="V28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.08432856469433103</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4856024500446495</v>
+      </c>
       <c r="Y28" t="n">
-        <v>1.307456978967495</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>6.108341215945271</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.108341215945271</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2938,12 +2930,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>huddersfield</t>
+          <t>bromley</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>morecambe</t>
+          <t>afc wimbledon</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2963,41 +2955,39 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5970774629445346</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2466872675849787</v>
+        <v>0.2597402597402598</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1562352694704865</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="O29" t="n">
-        <v>0.06676723656274453</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>1.244385733157199</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3010,7 +3000,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -3018,12 +3008,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lincoln</t>
+          <t>burton</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>harrogate</t>
+          <t>blackpool</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3043,25 +3033,25 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6485017704889973</v>
+        <v>0.3027681660899654</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2171657199097104</v>
+        <v>0.2502883506343714</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1343325096012923</v>
+        <v>0.4469434832756632</v>
       </c>
       <c r="O30" t="n">
-        <v>0.06345919748802609</v>
+        <v>0.06543778801843314</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -3070,12 +3060,12 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>1.201183431952663</v>
+        <v>1.251923076923077</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3088,7 +3078,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -3096,12 +3086,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>northampton</t>
+          <t>cambridge utd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>wycombe</t>
+          <t>qpr</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3121,39 +3111,41 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2768860353130017</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.06223358908780896</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>1.30188679245283</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3166,7 +3158,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -3174,12 +3166,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>norwich</t>
+          <t>cardiff</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>stevenage</t>
+          <t>bristol rovers</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3199,25 +3191,25 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="J32" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6500776404176282</v>
+        <v>0.5420741468672235</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2161921021250311</v>
+        <v>0.2604967428000824</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1337302574573407</v>
+        <v>0.197429110332694</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06824846951867736</v>
+        <v>0.06633877564817636</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3228,12 +3220,12 @@
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>1.194312796208531</v>
+        <v>1.268132716049382</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3246,7 +3238,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -3254,12 +3246,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>oxford utd</t>
+          <t>charlton</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>peterborough</t>
+          <t>birmingham</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3279,39 +3271,41 @@
         </is>
       </c>
       <c r="I33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K33" t="n">
         <v>2.2</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.4265402843601896</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2606635071090048</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3127962085308057</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06565656565656552</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
-        <v>1.269230769230769</v>
+        <v>1.303703703703704</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3324,7 +3318,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -3332,12 +3326,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>portsmouth</t>
+          <t>colchester</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>millwall</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3357,41 +3351,39 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3830753353973168</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2932920536635707</v>
+        <v>0.2674124864669793</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3236326109391125</v>
+        <v>0.492601948754962</v>
       </c>
       <c r="O34" t="n">
-        <v>0.06549085151301903</v>
+        <v>0.06844033159822649</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>1.32803738317757</v>
+        <v>1.277586206896552</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3404,7 +3396,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -3412,12 +3404,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>preston</t>
+          <t>crawley</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>swindon</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3437,72 +3429,52 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="J35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K35" t="n">
         <v>3.4</v>
       </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2768860353130017</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="O35" t="n">
-        <v>0.06223358908780896</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.3897291218114294</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.3323829537189195</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.2778879244696511</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>-0.01958066952083393</v>
-      </c>
+        <v>0.06763681082188988</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>-0.01958066952083393</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.3897291218114294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="n">
-        <v>2.3</v>
+        <v>1.278899082568807</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA35" t="n">
-        <v>4.902360887174315</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>4.902360887174315</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3510,12 +3482,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>rotherham</t>
+          <t>derby</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>crewe</t>
+          <t>chesterfield</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3538,38 +3510,36 @@
         <v>1.57</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.5890052356020942</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2568717277486911</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.1541230366492146</v>
       </c>
       <c r="O36" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.08138711960368017</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>1.208577712609971</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3582,7 +3552,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3590,12 +3560,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>salford</t>
+          <t>fleetwood</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>doncaster</t>
+          <t>west brom</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3615,39 +3585,41 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.1562352694704865</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2466872675849787</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.5970774629445346</v>
       </c>
       <c r="O37" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06676723656274453</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>1.285714285714286</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3660,7 +3632,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3668,12 +3640,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>shrewsbury</t>
+          <t>grimsby</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>notts co</t>
+          <t>bradford city</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3693,25 +3665,25 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="J38" t="n">
         <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="L38" t="n">
-        <v>0.418835684482416</v>
+        <v>0.3271028037383177</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2770753161077515</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.3958218801539307</v>
       </c>
       <c r="O38" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -3720,12 +3692,12 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>1.303738317757009</v>
+        <v>1.303117870722433</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3738,7 +3710,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3746,12 +3718,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>swansea</t>
+          <t>huddersfield</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>gillingham</t>
+          <t>morecambe</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3771,25 +3743,25 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="J39" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="K39" t="n">
         <v>7</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6500776404176282</v>
+        <v>0.6359687998581812</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2161921021250311</v>
+        <v>0.2295692253146606</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1337302574573407</v>
+        <v>0.1344619748271583</v>
       </c>
       <c r="O39" t="n">
-        <v>0.06824846951867736</v>
+        <v>0.06243525755720869</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -3800,12 +3772,12 @@
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>1.194312796208531</v>
+        <v>1.221698113207547</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -3818,7 +3790,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3826,12 +3798,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tranmere</t>
+          <t>lincoln</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>accrington</t>
+          <t>harrogate</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3851,25 +3823,25 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4564841498559078</v>
+        <v>0.6558682952734998</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2599423631123919</v>
+        <v>0.1988316516197557</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2835734870317003</v>
+        <v>0.1453000531067446</v>
       </c>
       <c r="O40" t="n">
-        <v>0.06861295885686136</v>
+        <v>0.05881691408007184</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -3878,12 +3850,12 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>1.264485981308411</v>
+        <v>1.178841309823678</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -3896,7 +3868,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3904,12 +3876,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>walsall</t>
+          <t>northampton</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>exeter</t>
+          <t>wycombe</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3929,25 +3901,25 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N41" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="O41" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -3956,12 +3928,12 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>1.285714285714286</v>
+        <v>1.311428571428571</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -3974,7 +3946,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -3982,12 +3954,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>watford</t>
+          <t>norwich</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>mk dons</t>
+          <t>stevenage</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4010,22 +3982,22 @@
         <v>1.5</v>
       </c>
       <c r="J42" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6264014466546112</v>
+        <v>0.6263219741480611</v>
       </c>
       <c r="M42" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1566003616636528</v>
+        <v>0.1445358401880141</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06441525953721072</v>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -4036,12 +4008,12 @@
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>1.21875</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4054,7 +4026,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -4062,12 +4034,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wigan</t>
+          <t>oxford utd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>barnsley</t>
+          <t>peterborough</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4090,22 +4062,22 @@
         <v>2.25</v>
       </c>
       <c r="J43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2597402597402598</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="O43" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -4114,12 +4086,12 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>1.321100917431193</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4132,20 +4104,20 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.66666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sheffield utd</t>
+          <t>portsmouth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>wrexham</t>
+          <t>millwall</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4165,25 +4137,25 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6133566993028307</v>
+        <v>0.3830753353973168</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2234370833174597</v>
+        <v>0.2932920536635707</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1632062173797097</v>
+        <v>0.3236326109391125</v>
       </c>
       <c r="O44" t="n">
-        <v>0.06560305281532886</v>
+        <v>0.06549085151301903</v>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -4194,12 +4166,12 @@
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>1.208447802197802</v>
+        <v>1.32803738317757</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4212,20 +4184,20 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>hull</t>
+          <t>preston</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sheffield wed</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4245,55 +4217,55 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="J45" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4903728275762602</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2754741472560756</v>
+        <v>0.2861952861952861</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2341530251676643</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="O45" t="n">
-        <v>0.06767785648290725</v>
+        <v>0.05882352941176494</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4583953404723956</v>
+        <v>0.3895221312549161</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3140287278096991</v>
+        <v>0.3367295201756419</v>
       </c>
       <c r="S45" t="n">
-        <v>0.2275759317179051</v>
+        <v>0.273748348569442</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.03197748710386461</v>
+        <v>0.04608778782057277</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>-0.03197748710386461</v>
+        <v>0.04608778782057277</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4583953404723956</v>
+        <v>0.3895221312549161</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -4301,29 +4273,29 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>5.766105898245254</v>
+        <v>4.899757175130554</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.766105898245254</v>
+        <v>4.899757175130554</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>plymouth</t>
+          <t>rotherham</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cheltenham</t>
+          <t>crewe</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4343,25 +4315,25 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="J46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5993833395353783</v>
+        <v>0.5652658981033842</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2295199617245229</v>
+        <v>0.2359985124581629</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1710966987400989</v>
+        <v>0.1987355894384529</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06266329600180764</v>
+        <v>0.05932871099905457</v>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -4372,12 +4344,12 @@
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>1.221357850070721</v>
+        <v>1.235591900311527</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4390,20 +4362,20 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45518.66666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>leeds</t>
+          <t>salford</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>middlesbrough</t>
+          <t>doncaster</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4423,66 +4395,874 @@
         </is>
       </c>
       <c r="I47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.338495575221239</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.2632743362831859</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.3982300884955752</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.0550887021475257</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="n">
+        <v>1.286486486486486</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>shrewsbury</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>notts co</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>48</v>
+      </c>
+      <c r="F48" t="n">
+        <v>484</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.4276704769412693</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.2688214426487978</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.303508080409933</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.06284038542103043</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="n">
+        <v>1.286792452830189</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>swansea</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>gillingham</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>48</v>
+      </c>
+      <c r="F49" t="n">
+        <v>484</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.6261180679785332</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.223613595706619</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.150268336314848</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.06476190476190458</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="n">
+        <v>1.209677419354839</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>tranmere</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>accrington</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>48</v>
+      </c>
+      <c r="F50" t="n">
+        <v>484</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.4697535474234503</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.2539208364451083</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.2763256161314414</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.06438791732909377</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="n">
+        <v>1.259259259259259</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>walsall</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>exeter</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>48</v>
+      </c>
+      <c r="F51" t="n">
+        <v>484</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.3027576765108547</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.2607079992176805</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.4365343242714649</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.06547470200883554</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="n">
+        <v>1.269523809523809</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>watford</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mk dons</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>48</v>
+      </c>
+      <c r="F52" t="n">
+        <v>484</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.6048853824355068</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.2165294094168674</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.1785852081476258</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.06658436301586113</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="n">
+        <v>1.196691176470588</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>wigan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>barnsley</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>48</v>
+      </c>
+      <c r="F53" t="n">
+        <v>484</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.3772968558595345</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.2858309514087382</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.3368721927317272</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.06017316017316032</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="n">
+        <v>1.320754716981132</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sheffield utd</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>wrexham</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>48</v>
+      </c>
+      <c r="F54" t="n">
+        <v>484</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>1.67</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J54" t="n">
         <v>4</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K54" t="n">
         <v>4.75</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L54" t="n">
         <v>0.5652658981033842</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M54" t="n">
         <v>0.2359985124581629</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N54" t="n">
         <v>0.1987355894384529</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O54" t="n">
         <v>0.05932871099905457</v>
       </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.6016001238134623</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.2709673188211533</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.1274325573653845</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.03633422571007805</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.03633422571007805</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.6016001238134623</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z47" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="n">
+        <v>1.235591900311527</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hull</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sheffield wed</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>48</v>
+      </c>
+      <c r="F55" t="n">
+        <v>484</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.4926019487549621</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.2674124864669794</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.2399855647780585</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.06844033159822627</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.4588895444290663</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.3136905648545075</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.2274198907164262</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-0.03371240432589584</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-0.03371240432589584</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.4588895444290663</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z55" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA47" t="n">
-        <v>7.567463532092283</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>7.567463532092283</v>
+      <c r="AA55" t="n">
+        <v>5.772322436891912</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>5.772322436891912</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>plymouth</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>cheltenham</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>48</v>
+      </c>
+      <c r="F56" t="n">
+        <v>484</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.5513666352497643</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.2403393025447691</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.2082940622054665</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.0668677727501259</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="n">
+        <v>1.233870967741935</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>leeds</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>middlesbrough</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>48</v>
+      </c>
+      <c r="F57" t="n">
+        <v>484</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.5682242990654205</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.234392523364486</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.1973831775700934</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.06658692185007986</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.6144761647206293</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.2674875619966797</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.1180362732826915</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.04625186565520878</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.04625186565520878</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.6144761647206293</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>7.729429871768316</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>7.729429871768316</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB57"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5220408361549084</v>
+        <v>0.5220408361549081</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3379505868208877</v>
+        <v>0.3379505868208875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.140008577024204</v>
+        <v>0.1400085770242041</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09971486985372147</v>
+        <v>-0.09971486985372169</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.09971486985372147</v>
+        <v>-0.09971486985372169</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5220408361549084</v>
+        <v>0.5220408361549081</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>6.566695772639449</v>
+        <v>6.566695772639446</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.566695772639449</v>
+        <v>6.566695772639446</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.207553355472195</v>
+        <v>0.2098515491476057</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3037866193818217</v>
+        <v>0.3052243745983683</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4886600251459832</v>
+        <v>0.484924076254026</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1994133693494297</v>
+        <v>-0.2031493182413868</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1994133693494297</v>
+        <v>-0.2031493182413868</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4886600251459832</v>
+        <v>0.484924076254026</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>6.14680212570923</v>
+        <v>6.099808024680067</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.14680212570923</v>
+        <v>6.099808024680067</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4465820355191964</v>
+        <v>0.4465820355191963</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3101629369696617</v>
+        <v>0.3101629369696618</v>
       </c>
       <c r="S4" t="n">
-        <v>0.243255027511142</v>
+        <v>0.2432550275111419</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.336789595982788</v>
+        <v>-0.3367895959827881</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.336789595982788</v>
+        <v>-0.3367895959827881</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4465820355191964</v>
+        <v>0.4465820355191963</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>5.617507600325788</v>
+        <v>5.617507600325786</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.617507600325788</v>
+        <v>5.617507600325786</v>
       </c>
     </row>
     <row r="5">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -908,43 +908,43 @@
         <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.3841205083947906</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2824415502902872</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.3334379413149224</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.0413398692810456</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2370212419216871</v>
+        <v>0.2370212419216869</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3695038916916568</v>
+        <v>0.3695038916916571</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3934748663866562</v>
+        <v>0.3934748663866559</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06263047842891528</v>
+        <v>0.06003692507173347</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06263047842891528</v>
+        <v>0.06003692507173347</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3934748663866562</v>
+        <v>0.3934748663866559</v>
       </c>
       <c r="Y5" t="n">
         <v>2.88</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>4.949478207054307</v>
+        <v>4.949478207054303</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.949478207054307</v>
+        <v>4.949478207054303</v>
       </c>
     </row>
     <row r="6">
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="J6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7093184979137691</v>
+        <v>0.6934812760055478</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1796940194714882</v>
+        <v>0.188626907073509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1109874826147427</v>
+        <v>0.1178918169209431</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06000294854784016</v>
+        <v>0.06029411764705883</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4897759797988454</v>
+        <v>0.489095160225368</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3433771863567628</v>
+        <v>0.3415951146802712</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1668468338443916</v>
+        <v>0.1693097250943605</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2195425181149238</v>
+        <v>-0.2043861157801797</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2195425181149238</v>
+        <v>-0.2043861157801797</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4897759797988454</v>
+        <v>0.489095160225368</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>6.160839599779999</v>
+        <v>6.152275643274196</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.160839599779999</v>
+        <v>6.152275643274196</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3043641035498073</v>
+        <v>0.3043641035498076</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3687775967439796</v>
+        <v>0.3687775967439799</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3268582997062129</v>
+        <v>0.3268582997062122</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09621227607889649</v>
+        <v>0.09621227607889682</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09621227607889649</v>
+        <v>0.09621227607889682</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3687775967439796</v>
+        <v>0.3687775967439799</v>
       </c>
       <c r="Y7" t="n">
         <v>3.5</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>4.638813897049684</v>
+        <v>4.638813897049689</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.638813897049684</v>
+        <v>4.638813897049689</v>
       </c>
     </row>
     <row r="8">
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3680185758941866</v>
+        <v>0.3680185758941875</v>
       </c>
       <c r="R8" t="n">
         <v>0.4001103182268416</v>
       </c>
       <c r="S8" t="n">
-        <v>0.231871105878972</v>
+        <v>0.2318711058789708</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1315,28 +1315,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3113709705938002</v>
+        <v>0.3113709705937981</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3848328992815713</v>
+        <v>0.3848328992815724</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3037961301246284</v>
+        <v>0.3037961301246293</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1085304464131342</v>
+        <v>0.1085304464131354</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1085304464131342</v>
+        <v>0.1085304464131354</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3848328992815713</v>
+        <v>0.3848328992815724</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>4.840771828307701</v>
+        <v>4.840771828307716</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.840771828307701</v>
+        <v>4.840771828307716</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2801216700200164</v>
+        <v>0.2801216700200165</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3393572867730009</v>
+        <v>0.3393572867730006</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3805210432069825</v>
+        <v>0.3805210432069828</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1283567364861737</v>
+        <v>-0.1283567364861735</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1283567364861737</v>
+        <v>-0.1283567364861735</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3805210432069825</v>
+        <v>0.3805210432069828</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>4.786533452502116</v>
+        <v>4.78653345250212</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.786533452502116</v>
+        <v>4.78653345250212</v>
       </c>
     </row>
     <row r="11">
@@ -1490,52 +1490,52 @@
         <v>5.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1789903110657828</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2409484956654768</v>
+        <v>0.2346368715083799</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5800611932687404</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06417039750373088</v>
+        <v>0.06547619047619047</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1638635360947085</v>
+        <v>0.1691215048360634</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3029693204168782</v>
+        <v>0.3080170885628083</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5331671434884132</v>
+        <v>0.5228614066011285</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04689404978032718</v>
+        <v>-0.06373077216982126</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04689404978032718</v>
+        <v>-0.06373077216982126</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5331671434884132</v>
+        <v>0.5228614066011285</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1543,24 +1543,24 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>6.706652401071354</v>
+        <v>6.577017640407562</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.706652401071354</v>
+        <v>6.577017640407562</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45514.45833333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1572,7 +1572,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,76 +1581,96 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>fa community shield</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6013630896699185</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2098089001737271</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1888280101563544</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0591648973814578</v>
+      </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4341283003984296</v>
+        <v>0.631817708239324</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3532899363163176</v>
+        <v>0.2258488301524321</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2125817632852529</v>
+        <v>0.1423334616082436</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0.03045461856940557</v>
+      </c>
       <c r="V12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.03045461856940557</v>
+      </c>
       <c r="X12" t="n">
-        <v>0.5658716996015704</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+        <v>0.631817708239324</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.57</v>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>7.118039510087844</v>
+        <v>7.947567290584082</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.118039510087844</v>
+        <v>7.947567290584082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>stoke</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1659,7 +1679,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1669,66 +1689,52 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.4602908440200329</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2972663122500965</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2424428437298706</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>0.5397091559799672</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA13" t="n">
-        <v>6.788943675618493</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6.788943675618493</v>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>leyton orient</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>newport</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1737,76 +1743,76 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3658167622948515</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3442914929513189</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2898917447538296</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6359687998581812</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2295692253146606</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1344619748271583</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06243525755720869</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="n">
-        <v>0.6341832377051485</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>1.221698113207547</v>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>7.977323032410138</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.977323032410138</v>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>stockport county</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>blackburn</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1815,76 +1821,78 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5495091702158204</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2512022812302508</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.199288548553929</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3505154639175257</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2783505154639175</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3711340206185567</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05664488017429203</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="n">
-        <v>0.4504908297841796</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1.311428571428571</v>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA15" t="n">
-        <v>5.666675904792235</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.666675904792235</v>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>barrow</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>port vale</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1893,76 +1901,76 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.4044071336571292</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3559653636716902</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2396275026711805</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4012738853503184</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2619426751592356</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3367834394904458</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06045254981425208</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>0.5955928663428708</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>1.277669902912621</v>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA16" t="n">
-        <v>7.491898883686916</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7.491898883686916</v>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>bolton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>mansfield</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1971,76 +1979,76 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.6683911707294922</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.2391716004562361</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.09243722881427212</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5683355886332883</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2232746955345061</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2083897158322057</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06637806637806642</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>0.3316088292705078</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>1.207317073170732</v>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA17" t="n">
-        <v>4.171271951404192</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.171271951404192</v>
-      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>bristol city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>coventry</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2049,76 +2057,96 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4012738853503184</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2619426751592356</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3367834394904458</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06045254981425208</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2981603243925068</v>
+        <v>0.4871059020915888</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3910006081310099</v>
+        <v>0.2729602230685538</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3108390674764833</v>
+        <v>0.2399338748398575</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>0.08583201674127033</v>
+      </c>
       <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.08583201674127033</v>
+      </c>
       <c r="X18" t="n">
-        <v>0.6089993918689901</v>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+        <v>0.4871059020915888</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.35</v>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>7.660538132575152</v>
+        <v>6.12725297823904</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.660538132575152</v>
+        <v>6.12725297823904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>bromley</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>afc wimbledon</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2127,76 +2155,76 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2843609750436352</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3559417876989703</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3596972372573942</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3246753246753247</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2597402597402598</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4155844155844156</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06944444444444442</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>0.6403027627426058</v>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>1.263157894736842</v>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA19" t="n">
-        <v>8.054299882516377</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.054299882516377</v>
-      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>burton</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>blackpool</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2205,76 +2233,76 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.2243322171901986</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.5079823808529856</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.2676854019568154</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3027681660899654</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2502883506343714</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4469434832756632</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06543778801843314</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="n">
-        <v>0.4920176191470144</v>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>1.251923076923077</v>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA20" t="n">
-        <v>6.18903694108346</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>6.18903694108346</v>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>cambridge utd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>qpr</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2283,76 +2311,78 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.5225684782528016</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3044504124414911</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1729811093057073</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.197429110332694</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2604967428000824</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5420741468672235</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06633877564817636</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="n">
-        <v>0.4774315217471984</v>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>1.268132716049382</v>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA21" t="n">
-        <v>6.005559983916345</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.005559983916345</v>
-      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>cardiff</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>bristol rovers</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2361,89 +2391,71 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="J22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.75</v>
       </c>
-      <c r="K22" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.5954453652761335</v>
+        <v>0.5420741468672235</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1968103628386378</v>
+        <v>0.2604967428000824</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2077442718852288</v>
+        <v>0.197429110332694</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06969121317093152</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.563419184179024</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2681802783102836</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.1684005375106921</v>
-      </c>
+        <v>0.06633877564817636</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>-0.03202618109710942</v>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-0.03202618109710942</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.563419184179024</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>1.57</v>
+        <v>1.268132716049382</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>7.08718958122751</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.08718958122751</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>charlton</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>stoke</t>
+          <t>birmingham</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2463,25 +2475,25 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1572297973961944</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2418919959941453</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6008782066096602</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06001959823615888</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -2497,7 +2509,7 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>1.244385733157199</v>
+        <v>1.303703703703704</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2510,20 +2522,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>leyton orient</t>
+          <t>colchester</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>newport</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2543,25 +2555,25 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.48</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6359687998581812</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2295692253146606</v>
+        <v>0.2674124864669793</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1344619748271583</v>
+        <v>0.492601948754962</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06243525755720869</v>
+        <v>0.06844033159822649</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2575,7 +2587,7 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>1.221698113207547</v>
+        <v>1.277586206896552</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2588,20 +2600,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>stockport county</t>
+          <t>crawley</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>blackburn</t>
+          <t>swindon</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2621,33 +2633,31 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.4</v>
       </c>
-      <c r="K25" t="n">
-        <v>2.55</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="O25" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
         <v>0</v>
@@ -2655,7 +2665,7 @@
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>1.311428571428571</v>
+        <v>1.278899082568807</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2668,7 +2678,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2676,12 +2686,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>barrow</t>
+          <t>derby</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>port vale</t>
+          <t>chesterfield</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2701,25 +2711,25 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4012738853503184</v>
+        <v>0.5890052356020942</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2619426751592356</v>
+        <v>0.2568717277486911</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3367834394904458</v>
+        <v>0.1541230366492146</v>
       </c>
       <c r="O26" t="n">
-        <v>0.06045254981425208</v>
+        <v>0.08138711960368017</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2733,7 +2743,7 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>1.277669902912621</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2746,7 +2756,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2754,12 +2764,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bolton</t>
+          <t>fleetwood</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>mansfield</t>
+          <t>west brom</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2779,31 +2789,33 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5683355886332883</v>
+        <v>0.1562352694704865</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2232746955345061</v>
+        <v>0.2466872675849787</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2083897158322057</v>
+        <v>0.5970774629445346</v>
       </c>
       <c r="O27" t="n">
-        <v>0.06637806637806642</v>
+        <v>0.06676723656274453</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
         <v>0</v>
@@ -2811,7 +2823,7 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>1.207317073170732</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -2824,7 +2836,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2832,12 +2844,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bristol city</t>
+          <t>grimsby</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>coventry</t>
+          <t>bradford city</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2857,72 +2869,52 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4012738853503184</v>
+        <v>0.3271028037383177</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2619426751592356</v>
+        <v>0.2770753161077515</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3367834394904458</v>
+        <v>0.3958218801539307</v>
       </c>
       <c r="O28" t="n">
-        <v>0.06045254981425208</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.4856024500446495</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.273266202941484</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.2411313470138665</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.08432856469433103</v>
-      </c>
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.08432856469433103</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.4856024500446495</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>1.303117870722433</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA28" t="n">
-        <v>6.108341215945271</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>6.108341215945271</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2930,12 +2922,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bromley</t>
+          <t>huddersfield</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>afc wimbledon</t>
+          <t>morecambe</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2955,31 +2947,33 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="J29" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.6359687998581812</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2597402597402598</v>
+        <v>0.2295692253146606</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4155844155844156</v>
+        <v>0.1344619748271583</v>
       </c>
       <c r="O29" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.06243525755720869</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>0</v>
@@ -2987,7 +2981,7 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>1.263157894736842</v>
+        <v>1.221698113207547</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3000,7 +2994,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -3008,12 +3002,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>burton</t>
+          <t>lincoln</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>blackpool</t>
+          <t>harrogate</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3033,25 +3027,25 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="K30" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3027681660899654</v>
+        <v>0.6558682952734998</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2502883506343714</v>
+        <v>0.1988316516197557</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4469434832756632</v>
+        <v>0.1453000531067446</v>
       </c>
       <c r="O30" t="n">
-        <v>0.06543778801843314</v>
+        <v>0.05881691408007184</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -3065,7 +3059,7 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>1.251923076923077</v>
+        <v>1.178841309823678</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3078,7 +3072,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -3086,12 +3080,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>cambridge utd</t>
+          <t>northampton</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>qpr</t>
+          <t>wycombe</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3111,33 +3105,31 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2074074074074074</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
         <v>0</v>
@@ -3145,7 +3137,7 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.306666666666667</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3158,7 +3150,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -3166,12 +3158,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>cardiff</t>
+          <t>norwich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bristol rovers</t>
+          <t>stevenage</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3191,25 +3183,25 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5420741468672235</v>
+        <v>0.6106870229007634</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2604967428000824</v>
+        <v>0.233587786259542</v>
       </c>
       <c r="N32" t="n">
-        <v>0.197429110332694</v>
+        <v>0.1557251908396947</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06633877564817636</v>
+        <v>0.0702614379084967</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3225,7 +3217,7 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>1.268132716049382</v>
+        <v>1.219123505976096</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3238,7 +3230,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -3246,12 +3238,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>charlton</t>
+          <t>oxford utd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>birmingham</t>
+          <t>peterborough</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3271,33 +3263,31 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2944881889763779</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2771653543307087</v>
+        <v>0.2597402597402598</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4283464566929133</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06116310160427818</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
         <v>0</v>
@@ -3305,7 +3295,7 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
-        <v>1.303703703703704</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3318,7 +3308,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -3326,12 +3316,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>colchester</t>
+          <t>portsmouth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>millwall</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3351,31 +3341,33 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.3830753353973168</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2674124864669793</v>
+        <v>0.2932920536635707</v>
       </c>
       <c r="N34" t="n">
-        <v>0.492601948754962</v>
+        <v>0.3236326109391125</v>
       </c>
       <c r="O34" t="n">
-        <v>0.06844033159822649</v>
+        <v>0.06549085151301903</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
         <v>0</v>
@@ -3383,7 +3375,7 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>1.277586206896552</v>
+        <v>1.32803738317757</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3396,7 +3388,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -3404,12 +3396,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>crawley</t>
+          <t>preston</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>swindon</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3429,52 +3421,72 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.2861952861952861</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="O35" t="n">
-        <v>0.06763681082188988</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+        <v>0.05882352941176494</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3912480672049762</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.3335287037443681</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2752232290506555</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.04781372377063281</v>
+      </c>
       <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.04781372377063281</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.3912480672049762</v>
+      </c>
       <c r="Y35" t="n">
-        <v>1.278899082568807</v>
+        <v>2.75</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.921467538615879</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4.921467538615879</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3482,12 +3494,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>derby</t>
+          <t>rotherham</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>chesterfield</t>
+          <t>crewe</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3507,31 +3519,33 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5890052356020942</v>
+        <v>0.5546995377503853</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2568717277486911</v>
+        <v>0.2357473035439137</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1541230366492146</v>
+        <v>0.2095531587057011</v>
       </c>
       <c r="O36" t="n">
-        <v>0.08138711960368017</v>
+        <v>0.06045751633986929</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
         <v>0</v>
@@ -3539,7 +3553,7 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>1.244385733157199</v>
+        <v>1.233870967741935</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3552,7 +3566,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3560,12 +3574,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fleetwood</t>
+          <t>salford</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>west brom</t>
+          <t>doncaster</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3585,33 +3599,31 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1562352694704865</v>
+        <v>0.338495575221239</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2466872675849787</v>
+        <v>0.2632743362831859</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5970774629445346</v>
+        <v>0.3982300884955752</v>
       </c>
       <c r="O37" t="n">
-        <v>0.06676723656274453</v>
+        <v>0.0550887021475257</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
         <v>0</v>
@@ -3619,7 +3631,7 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>1.244385733157199</v>
+        <v>1.286486486486486</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3632,7 +3644,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3640,12 +3652,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>grimsby</t>
+          <t>shrewsbury</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>bradford city</t>
+          <t>notts co</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3665,25 +3677,25 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.4276704769412693</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="O38" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.06284038542103043</v>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -3697,7 +3709,7 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>1.303117870722433</v>
+        <v>1.286792452830189</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3710,7 +3722,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3718,12 +3730,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>huddersfield</t>
+          <t>swansea</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>morecambe</t>
+          <t>gillingham</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3743,25 +3755,25 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6359687998581812</v>
+        <v>0.6261180679785332</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2295692253146606</v>
+        <v>0.223613595706619</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1344619748271583</v>
+        <v>0.150268336314848</v>
       </c>
       <c r="O39" t="n">
-        <v>0.06243525755720869</v>
+        <v>0.06476190476190458</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -3777,7 +3789,7 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>1.221698113207547</v>
+        <v>1.209677419354839</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -3790,7 +3802,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3798,12 +3810,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lincoln</t>
+          <t>tranmere</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>harrogate</t>
+          <t>accrington</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3823,25 +3835,25 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="K40" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6558682952734998</v>
+        <v>0.4697535474234503</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1988316516197557</v>
+        <v>0.2539208364451083</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1453000531067446</v>
+        <v>0.2763256161314414</v>
       </c>
       <c r="O40" t="n">
-        <v>0.05881691408007184</v>
+        <v>0.06438791732909377</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -3855,7 +3867,7 @@
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>1.178841309823678</v>
+        <v>1.259259259259259</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -3868,7 +3880,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3876,12 +3888,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>northampton</t>
+          <t>walsall</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>wycombe</t>
+          <t>exeter</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3901,25 +3913,25 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K41" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3027576765108547</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2607079992176805</v>
       </c>
       <c r="N41" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.4365343242714649</v>
       </c>
       <c r="O41" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.06547470200883554</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -3933,7 +3945,7 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>1.311428571428571</v>
+        <v>1.269523809523809</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -3946,7 +3958,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -3954,12 +3966,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>norwich</t>
+          <t>watford</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>stevenage</t>
+          <t>mk dons</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3979,25 +3991,25 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="J42" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="K42" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6263219741480611</v>
+        <v>0.6048853824355068</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2291421856639248</v>
+        <v>0.2165294094168674</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1445358401880141</v>
+        <v>0.1785852081476258</v>
       </c>
       <c r="O42" t="n">
-        <v>0.06441525953721072</v>
+        <v>0.06658436301586113</v>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -4013,7 +4025,7 @@
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
-        <v>1.21875</v>
+        <v>1.196691176470588</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4026,7 +4038,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -4034,12 +4046,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>oxford utd</t>
+          <t>wigan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>peterborough</t>
+          <t>barnsley</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4059,25 +4071,25 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="J43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K43" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4155844155844156</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2597402597402598</v>
+        <v>0.2861952861952861</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="O43" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.05882352941176494</v>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -4091,7 +4103,7 @@
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>1.263157894736842</v>
+        <v>1.32311320754717</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4104,20 +4116,20 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>portsmouth</t>
+          <t>sheffield utd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>millwall</t>
+          <t>wrexham</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4137,25 +4149,25 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3830753353973168</v>
+        <v>0.5652658981033842</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2932920536635707</v>
+        <v>0.2359985124581629</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3236326109391125</v>
+        <v>0.1987355894384529</v>
       </c>
       <c r="O44" t="n">
-        <v>0.06549085151301903</v>
+        <v>0.05932871099905457</v>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -4171,7 +4183,7 @@
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>1.32803738317757</v>
+        <v>1.235591900311527</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4184,20 +4196,20 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>preston</t>
+          <t>hull</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>sheffield wed</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4217,55 +4229,55 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.4830216088614491</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2861952861952861</v>
+        <v>0.2691120392228074</v>
       </c>
       <c r="N45" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.2478663519157436</v>
       </c>
       <c r="O45" t="n">
-        <v>0.05882352941176494</v>
+        <v>0.06169269327164062</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.3895221312549161</v>
+        <v>0.4556736538692437</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3367295201756419</v>
+        <v>0.3139593210070291</v>
       </c>
       <c r="S45" t="n">
-        <v>0.273748348569442</v>
+        <v>0.2303670251237272</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04608778782057277</v>
+        <v>-0.02734795499220544</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0.04608778782057277</v>
+        <v>-0.02734795499220544</v>
       </c>
       <c r="X45" t="n">
-        <v>0.3895221312549161</v>
+        <v>0.4556736538692437</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -4273,29 +4285,29 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>4.899757175130554</v>
+        <v>5.731870093929624</v>
       </c>
       <c r="AB45" t="n">
-        <v>4.899757175130554</v>
+        <v>5.731870093929624</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>rotherham</t>
+          <t>plymouth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>crewe</t>
+          <t>cheltenham</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4315,25 +4327,25 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K46" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5652658981033842</v>
+        <v>0.5513666352497643</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2359985124581629</v>
+        <v>0.2403393025447691</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1987355894384529</v>
+        <v>0.2082940622054665</v>
       </c>
       <c r="O46" t="n">
-        <v>0.05932871099905457</v>
+        <v>0.0668677727501259</v>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -4349,7 +4361,7 @@
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>1.235591900311527</v>
+        <v>1.233870967741935</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4362,20 +4374,20 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.66666666666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>salford</t>
+          <t>leeds</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>doncaster</t>
+          <t>middlesbrough</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4395,874 +4407,66 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="J47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>2.38</v>
+        <v>4.75</v>
       </c>
       <c r="L47" t="n">
-        <v>0.338495575221239</v>
+        <v>0.5682242990654205</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2632743362831859</v>
+        <v>0.234392523364486</v>
       </c>
       <c r="N47" t="n">
-        <v>0.3982300884955752</v>
+        <v>0.1973831775700934</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0550887021475257</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+        <v>0.06658692185007986</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.6016329915580843</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.2722644251372123</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.1261025833047036</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.03340869249266376</v>
+      </c>
       <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.03340869249266376</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.6016329915580843</v>
+      </c>
       <c r="Y47" t="n">
-        <v>1.286486486486486</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>shrewsbury</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>notts co</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>48</v>
-      </c>
-      <c r="F48" t="n">
-        <v>484</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.4276704769412693</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.2688214426487978</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.303508080409933</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.06284038542103043</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="n">
-        <v>1.286792452830189</v>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>swansea</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>gillingham</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>48</v>
-      </c>
-      <c r="F49" t="n">
-        <v>484</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.6261180679785332</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.223613595706619</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.150268336314848</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.06476190476190458</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="n">
-        <v>1.209677419354839</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>tranmere</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>accrington</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>48</v>
-      </c>
-      <c r="F50" t="n">
-        <v>484</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.4697535474234503</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.2539208364451083</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.2763256161314414</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.06438791732909377</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="n">
-        <v>1.259259259259259</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>walsall</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>exeter</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>48</v>
-      </c>
-      <c r="F51" t="n">
-        <v>484</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.3027576765108547</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.2607079992176805</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.4365343242714649</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.06547470200883554</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="n">
-        <v>1.269523809523809</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>watford</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>mk dons</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>48</v>
-      </c>
-      <c r="F52" t="n">
-        <v>484</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="K52" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.6048853824355068</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.2165294094168674</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.1785852081476258</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0.06658436301586113</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="n">
-        <v>1.196691176470588</v>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>wigan</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>barnsley</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>48</v>
-      </c>
-      <c r="F53" t="n">
-        <v>484</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.3772968558595345</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.2858309514087382</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.3368721927317272</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.06017316017316032</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="n">
-        <v>1.320754716981132</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>sheffield utd</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>wrexham</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>48</v>
-      </c>
-      <c r="F54" t="n">
-        <v>484</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.5652658981033842</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.2359985124581629</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.1987355894384529</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.05932871099905457</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="n">
-        <v>1.235591900311527</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>hull</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>sheffield wed</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>48</v>
-      </c>
-      <c r="F55" t="n">
-        <v>484</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.4926019487549621</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.2674124864669794</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.2399855647780585</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.06844033159822627</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.4588895444290663</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.3136905648545075</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0.2274198907164262</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>-0.03371240432589584</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-0.03371240432589584</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0.4588895444290663</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA55" t="n">
-        <v>5.772322436891912</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>5.772322436891912</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>plymouth</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>cheltenham</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>48</v>
-      </c>
-      <c r="F56" t="n">
-        <v>484</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.5513666352497643</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.2403393025447691</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.2082940622054665</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.0668677727501259</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="n">
-        <v>1.233870967741935</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>leeds</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>middlesbrough</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>48</v>
-      </c>
-      <c r="F57" t="n">
-        <v>484</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J57" t="n">
-        <v>4</v>
-      </c>
-      <c r="K57" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.5682242990654205</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.234392523364486</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.1973831775700934</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.06658692185007986</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0.6144761647206293</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.2674875619966797</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.1180362732826915</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.04625186565520878</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0.04625186565520878</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0.6144761647206293</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA57" t="n">
-        <v>7.729429871768316</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>7.729429871768316</v>
+      <c r="AA47" t="n">
+        <v>7.567876971932076</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>7.567876971932076</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6217557060086298</v>
+        <v>0.6072187370353144</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2196965889591694</v>
+        <v>0.2269841469393913</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1585477050322006</v>
+        <v>0.1657971160252945</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05120832012558685</v>
+        <v>0.04895095673273442</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5243470435753469</v>
+        <v>0.5234152254722908</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3325096453358647</v>
+        <v>0.3332936849211541</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1431433110887884</v>
+        <v>0.1432910896065553</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.09740866243328294</v>
+        <v>-0.08380351156302357</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.09740866243328294</v>
+        <v>-0.08380351156302357</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5243470435753469</v>
+        <v>0.5234152254722908</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.595705308809392</v>
+        <v>6.583984068679451</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.595705308809392</v>
+        <v>6.583984068679451</v>
       </c>
     </row>
     <row r="3">
@@ -811,22 +811,22 @@
         <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7833716315019844</v>
+        <v>0.7784120394395433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1529141424691874</v>
+        <v>0.1582771146860404</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06371422602882806</v>
+        <v>0.06331084587441618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0463387978142078</v>
+        <v>0.0530054644808744</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -845,13 +845,13 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.3368449596835279</v>
+        <v>-0.3318853676210868</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3368449596835279</v>
+        <v>-0.3318853676210868</v>
       </c>
       <c r="Y4" t="n">
         <v>0.4465266718184565</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -916,16 +916,16 @@
         <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.3841205083947906</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2824415502902872</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.3334379413149224</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.0413398692810456</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -944,13 +944,13 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06380131034348685</v>
+        <v>0.06120775698630537</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06380131034348685</v>
+        <v>0.06120775698630537</v>
       </c>
       <c r="Y5" t="n">
         <v>0.3946456983012278</v>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3741092636579573</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2725653206650831</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3533254156769596</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04824151882975425</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1142,19 +1142,19 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09876415133955985</v>
+        <v>0.09370907540407636</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09876415133955985</v>
+        <v>0.09370907540407636</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3713294720046429</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3645833333333334</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2708333333333334</v>
+        <v>0.2701754385964912</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3645833333333334</v>
+        <v>0.343859649122807</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05494505494505475</v>
+        <v>0.0575139146567718</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1241,13 +1241,13 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.127700449063711</v>
+        <v>0.1283583438005532</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.127700449063711</v>
+        <v>0.1283583438005532</v>
       </c>
       <c r="Y8" t="n">
         <v>0.3985337823970444</v>
@@ -1303,25 +1303,25 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2768860353130017</v>
       </c>
       <c r="N9" t="n">
-        <v>0.323940806811271</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.06223358908780896</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1340,13 +1340,13 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1065071921732091</v>
+        <v>0.1059236097286446</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1065071921732091</v>
+        <v>0.1059236097286446</v>
       </c>
       <c r="Y9" t="n">
         <v>0.3828096450416462</v>
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2296155835200828</v>
+        <v>0.2185397867104184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2615066367867609</v>
+        <v>0.2557506152584085</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5088777796931563</v>
+        <v>0.5257095980311731</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06222075734270849</v>
+        <v>0.0567727080429159</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2863213504688617</v>
+        <v>0.302199506290355</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3421488817675583</v>
+        <v>0.3377991579972073</v>
       </c>
       <c r="S10" t="n">
-        <v>0.37152976776358</v>
+        <v>0.3600013357124378</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1373480119295763</v>
+        <v>-0.1657082623187354</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1373480119295763</v>
+        <v>-0.1657082623187354</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.37152976776358</v>
+        <v>0.3600013357124378</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.673433161575243</v>
+        <v>4.528418249383713</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.673433161575243</v>
+        <v>4.528418249383713</v>
       </c>
     </row>
     <row r="11">
@@ -1504,22 +1504,22 @@
         <v>5.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1789903110657828</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2409484956654768</v>
+        <v>0.2346368715083799</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5800611932687404</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06417039750373088</v>
+        <v>0.06547619047619047</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1538,19 +1538,19 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.05006698544149268</v>
+        <v>-0.056597970943702</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.05006698544149268</v>
+        <v>-0.056597970943702</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5299942078272477</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4334033618080579</v>
+        <v>0.4201801992737436</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3518678188277172</v>
+        <v>0.3827337577944768</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2147288193642247</v>
+        <v>0.1970860429317796</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.5665966381919421</v>
+        <v>0.5798198007262565</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>7.127158434982455</v>
+        <v>7.293491180433121</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.127158434982455</v>
+        <v>7.293491180433121</v>
       </c>
     </row>
     <row r="13">
@@ -1847,13 +1847,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5477098265816043</v>
+        <v>0.5595522590652725</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2515013540184746</v>
+        <v>0.2394327372055071</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2007888193999214</v>
+        <v>0.2010150037292205</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.4522901734183957</v>
+        <v>0.4404477409347275</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.689309655675329</v>
+        <v>5.540344965669361</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.689309655675329</v>
+        <v>5.540344965669361</v>
       </c>
     </row>
     <row r="16">

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45523.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K2" t="n">
         <v>1.57</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.75</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.6072187370353144</v>
+        <v>0.1814679252552495</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2269841469393913</v>
+        <v>0.2117125794644577</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1657971160252945</v>
+        <v>0.6068194952802928</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04895095673273442</v>
+        <v>0.04964108785764831</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5234152254722908</v>
+        <v>0.1984654699119831</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3332936849211541</v>
+        <v>0.2994943685209133</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1432910896065553</v>
+        <v>0.5020401615671038</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.08380351156302357</v>
+        <v>-0.1047793337131889</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.08380351156302357</v>
+        <v>-0.1047793337131889</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5234152254722908</v>
+        <v>0.5020401615671038</v>
       </c>
       <c r="Z2" t="n">
         <v>1.57</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.583984068679451</v>
+        <v>6.315109428871697</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.583984068679451</v>
+        <v>6.315109428871697</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.3807716387541087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.2572781342933166</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.3619502269525748</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.0504984071523995</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1969580025197008</v>
+        <v>0.4139991524649383</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3049629879795524</v>
+        <v>0.3809908168050184</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4980790095007467</v>
+        <v>0.205010030730043</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1899943849946661</v>
+        <v>0.0332275137108296</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1899943849946661</v>
+        <v>0.0332275137108296</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4980790095007467</v>
+        <v>0.4139991524649383</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.265282521228765</v>
+        <v>5.207651003687221</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.265282521228765</v>
+        <v>5.207651003687221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7784120394395433</v>
+        <v>0.4524744697564808</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1582771146860404</v>
+        <v>0.2576590730557737</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06331084587441618</v>
+        <v>0.2898664571877455</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0530054644808744</v>
+        <v>0.07808265582655838</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4465266718184565</v>
+        <v>0.4502421799781174</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3097885483826098</v>
+        <v>0.2955148357321733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2436847797989334</v>
+        <v>0.2542429842897094</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.3318853676210868</v>
+        <v>-0.002232289778363372</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3318853676210868</v>
+        <v>-0.002232289778363372</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4465266718184565</v>
+        <v>0.4502421799781174</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.61681118626308</v>
+        <v>5.663548165509685</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.61681118626308</v>
+        <v>5.663548165509685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3841205083947906</v>
+        <v>0.5290697674418605</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2824415502902872</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3334379413149224</v>
+        <v>0.2267441860465116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0413398692810456</v>
+        <v>0.05006105006105011</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2345030970113675</v>
+        <v>0.3629778363242953</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3708512046874048</v>
+        <v>0.3454235818380411</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.2915985818376635</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06120775698630537</v>
+        <v>-0.1660919311175653</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06120775698630537</v>
+        <v>-0.1660919311175653</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.3629778363242953</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.964205976323313</v>
+        <v>4.565859331826818</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.964205976323313</v>
+        <v>4.565859331826818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7093184979137691</v>
+        <v>0.8512769153730596</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1796940194714882</v>
+        <v>0.09364046069103657</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1109874826147427</v>
+        <v>0.05508262393590386</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06000294854784016</v>
+        <v>0.06791443850267376</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4839286611290518</v>
+        <v>0.5606007206908046</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3439236706290538</v>
+        <v>0.2388520673653664</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1721476682418941</v>
+        <v>0.2005472119438289</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2253898367847173</v>
+        <v>-0.290676194682255</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2253898367847173</v>
+        <v>-0.290676194682255</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4839286611290518</v>
+        <v>0.5606007206908046</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.087286804422023</v>
+        <v>7.051736430838452</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.087286804422023</v>
+        <v>7.051736430838452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>bournemouth</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1111,50 +1111,50 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.302881567933547</v>
+        <v>0.4212253382936238</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3713294720046429</v>
+        <v>0.3428374306281331</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3257889600618101</v>
+        <v>0.2359372310782431</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09370907540407636</v>
+        <v>0.03830325372313137</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09370907540407636</v>
+        <v>0.03830325372313137</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3713294720046429</v>
+        <v>0.4212253382936238</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.670913662673247</v>
+        <v>5.298548421374016</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.670913662673247</v>
+        <v>5.298548421374016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="K8" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2701754385964912</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="N8" t="n">
-        <v>0.343859649122807</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0575139146567718</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3811557120837989</v>
+        <v>0.674892986044167</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3985337823970444</v>
+        <v>0.2345072723844793</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2203105055191567</v>
+        <v>0.09059974157135366</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1283583438005532</v>
+        <v>0.02058835028257766</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1283583438005532</v>
+        <v>0.02058835028257766</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3985337823970444</v>
+        <v>0.674892986044167</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.013113769789665</v>
+        <v>8.489406597159702</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.013113769789665</v>
+        <v>8.489406597159702</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45528.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.2343636426568828</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2768860353130017</v>
+        <v>0.253366100169603</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.5122702571735143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06223358908780896</v>
+        <v>0.0667183577019641</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.308712675107635</v>
+        <v>0.3195673732912551</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3828096450416462</v>
+        <v>0.4218274545862332</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3084776798507189</v>
+        <v>0.2586051721225117</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1059236097286446</v>
+        <v>0.1684613544166302</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1059236097286446</v>
+        <v>0.1684613544166302</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3828096450416462</v>
+        <v>0.4218274545862332</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.81532152989398</v>
+        <v>5.306122377738116</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.81532152989398</v>
+        <v>5.306122377738116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.52083333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2185397867104184</v>
+        <v>0.3118996275240149</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2557506152584085</v>
+        <v>0.2528915898843364</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5257095980311731</v>
+        <v>0.4352087825916487</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0567727080429159</v>
+        <v>0.06871988267337104</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.302199506290355</v>
+        <v>0.2491215235010418</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3377991579972073</v>
+        <v>0.3574570761551938</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3600013357124378</v>
+        <v>0.3934214003437644</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1657082623187354</v>
+        <v>-0.04178738224788431</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1657082623187354</v>
+        <v>-0.04178738224788431</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3600013357124378</v>
+        <v>0.3934214003437644</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.528418249383713</v>
+        <v>4.94880566342645</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.528418249383713</v>
+        <v>4.94880566342645</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.66666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1787709497206704</v>
+        <v>0.2115884421342302</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2346368715083799</v>
+        <v>0.238036997401009</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5865921787709497</v>
+        <v>0.5503745604647607</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06547619047619047</v>
+        <v>0.05025690430314711</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1620949559165673</v>
+        <v>0.2098388985327569</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3079108362561851</v>
+        <v>0.4899269864510464</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5299942078272477</v>
+        <v>0.3002341150161967</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.056597970943702</v>
+        <v>0.2518899890500375</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.056597970943702</v>
+        <v>0.2518899890500375</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5299942078272477</v>
+        <v>0.4899269864510464</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.666740383179233</v>
+        <v>6.162739096286734</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.666740383179233</v>
+        <v>6.162739096286734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,67 +1599,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06666666666666665</v>
+      </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4201801992737436</v>
+        <v>0.5365236227025854</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3827337577944768</v>
+        <v>0.2998966361674108</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1970860429317796</v>
+        <v>0.1635797411300039</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.2134763772974146</v>
+      </c>
       <c r="W12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.2134763772974146</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5798198007262565</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.5365236227025854</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.25</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>7.293491180433121</v>
+        <v>6.748873193661066</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.293491180433121</v>
+        <v>6.748873193661066</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1689,13 +1709,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4585042516923099</v>
+        <v>0.6894247301534645</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2980555862866562</v>
+        <v>0.2144023634708641</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2434401620210337</v>
+        <v>0.09617290637567152</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1707,7 +1727,7 @@
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>0.5414957483076901</v>
+        <v>0.3105752698465355</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
@@ -1716,29 +1736,29 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>6.811417029182747</v>
+        <v>3.906693059893922</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.811417029182747</v>
+        <v>3.906693059893922</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1765,16 +1785,16 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3661185558879717</v>
+        <v>0.2590490131886587</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3444027951446086</v>
+        <v>0.4416148801129426</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2894786489674195</v>
+        <v>0.2993361066983987</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1782,11 +1802,11 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.6338814441120284</v>
+        <v>0.5583851198870574</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
@@ -1795,29 +1815,29 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>7.973526803121356</v>
+        <v>7.023866625596806</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.973526803121356</v>
+        <v>7.023866625596806</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1847,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5595522590652725</v>
+        <v>0.3746857391025852</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2394327372055071</v>
+        <v>0.2974032641796376</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2010150037292205</v>
+        <v>0.3279109967177773</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1865,7 +1885,7 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.4404477409347275</v>
+        <v>0.6253142608974148</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1874,29 +1894,29 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.540344965669361</v>
+        <v>7.865761122924382</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.540344965669361</v>
+        <v>7.865761122924382</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1923,16 +1943,16 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4048621671972947</v>
+        <v>0.3118901882843966</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3524844864137729</v>
+        <v>0.404495867826843</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2426533463889323</v>
+        <v>0.2836139438887605</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1940,11 +1960,11 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.5951378328027053</v>
+        <v>0.595504132173157</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -1953,29 +1973,29 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>7.486175065514715</v>
+        <v>7.490782706068628</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.486175065514715</v>
+        <v>7.490782706068628</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2005,13 +2025,13 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6750319510992732</v>
+        <v>0.5118347695889779</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2345401618175841</v>
+        <v>0.2480105897419462</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09042788708314296</v>
+        <v>0.2401546406690757</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2023,7 +2043,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.3249680489007268</v>
+        <v>0.4881652304110221</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2032,29 +2052,29 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.087738286293886</v>
+        <v>6.140578155725723</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.087738286293886</v>
+        <v>6.140578155725723</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2081,16 +2101,16 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2890997883354035</v>
+        <v>0.5308064402203464</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3971268210688618</v>
+        <v>0.2646686050580849</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3137733905957346</v>
+        <v>0.2045249547215686</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -2098,11 +2118,11 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.6028731789311381</v>
+        <v>0.4691935597796536</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
@@ -2111,29 +2131,29 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>7.583477156086055</v>
+        <v>5.901935542529946</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.583477156086055</v>
+        <v>5.901935542529946</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45535.5625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2160,16 +2180,16 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3057220661847874</v>
+        <v>0.2628339186139623</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3499457135311053</v>
+        <v>0.3571793563627601</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3443322202841073</v>
+        <v>0.3799867250232775</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2177,11 +2197,11 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>0.6500542864688947</v>
+        <v>0.6200132749767224</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
@@ -2190,29 +2210,29 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8.176963255178689</v>
+        <v>7.799080588710575</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.176963255178689</v>
+        <v>7.799080588710575</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2239,16 +2259,16 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2126273385644954</v>
+        <v>0.564901721178678</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5036997800859342</v>
+        <v>0.3021406663969232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2836728813495706</v>
+        <v>0.1329576124243989</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2256,11 +2276,11 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>0.4963002199140658</v>
+        <v>0.435098278821322</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
@@ -2269,29 +2289,29 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>6.242907317508483</v>
+        <v>5.473054654618731</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.242907317508483</v>
+        <v>5.473054654618731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2318,16 +2338,16 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5295790047290388</v>
+        <v>0.135661313660232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3023696763548994</v>
+        <v>0.3979862501342901</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1680513189160616</v>
+        <v>0.466352436205478</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -2335,11 +2355,11 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
-        <v>0.4704209952709612</v>
+        <v>0.5336475637945219</v>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
@@ -2348,10 +2368,89 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.917375322129037</v>
+        <v>6.712695556653685</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.917375322129037</v>
+        <v>6.712695556653685</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" t="n">
+        <v>481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3003047794248846</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4551125270206358</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2445826935544795</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5448874729793642</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.854081170607942</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.854081170607942</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>fulham</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.75</v>
+        <v>2.63</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6072187370353144</v>
+        <v>0.3807716387541087</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2269841469393913</v>
+        <v>0.2572781342933166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1657971160252945</v>
+        <v>0.3619502269525748</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04895095673273442</v>
+        <v>0.0504984071523995</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5234152254722908</v>
+        <v>0.4135967408248821</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3332936849211541</v>
+        <v>0.3806498419345348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1432910896065553</v>
+        <v>0.2057534172405832</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.08380351156302357</v>
+        <v>0.03282510207077338</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.08380351156302357</v>
+        <v>0.03282510207077338</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5234152254722908</v>
+        <v>0.4135967408248821</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.583984068679451</v>
+        <v>5.202589110761217</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.583984068679451</v>
+        <v>5.202589110761217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>2.15</v>
       </c>
       <c r="J3" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.4321728691476591</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.2581032412965186</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.3097238895558223</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.07622739018087854</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1969580025197008</v>
+        <v>0.4498414128665832</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3049629879795524</v>
+        <v>0.2956869029872177</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4980790095007467</v>
+        <v>0.2544716841461988</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1899943849946661</v>
+        <v>0.01766854371892418</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1899943849946661</v>
+        <v>0.01766854371892418</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4980790095007467</v>
+        <v>0.4498414128665832</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.265282521228765</v>
+        <v>5.658506958931847</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.265282521228765</v>
+        <v>5.658506958931847</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>4.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7784120394395433</v>
+        <v>0.539701816903434</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1582771146860404</v>
+        <v>0.2421738922002589</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06331084587441618</v>
+        <v>0.2181242908963071</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0530054644808744</v>
+        <v>0.05878571005591793</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4465266718184565</v>
+        <v>0.3627507372382341</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3097885483826098</v>
+        <v>0.3457817723697896</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2436847797989334</v>
+        <v>0.2914674903919762</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.3318853676210868</v>
+        <v>-0.1769510796651999</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3318853676210868</v>
+        <v>-0.1769510796651999</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4465266718184565</v>
+        <v>0.3627507372382341</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.61681118626308</v>
+        <v>4.563002676743296</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.61681118626308</v>
+        <v>4.563002676743296</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3841205083947906</v>
+        <v>0.8647083160943319</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2824415502902872</v>
+        <v>0.08568473314025653</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3334379413149224</v>
+        <v>0.04960695076541167</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0413398692810456</v>
+        <v>0.0609718625170097</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2345030970113675</v>
+        <v>0.5629561455712984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3708512046874048</v>
+        <v>0.2377463557826995</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.1992974986460023</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06120775698630537</v>
+        <v>-0.3017521705230335</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06120775698630537</v>
+        <v>-0.3017521705230335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.5629561455712984</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>1.09</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.964205976323313</v>
+        <v>7.081365068167733</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.964205976323313</v>
+        <v>7.081365068167733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7093184979137691</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1796940194714882</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1109874826147427</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06000294854784016</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4839286611290518</v>
+        <v>0.4212253382936241</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3439236706290538</v>
+        <v>0.3428374306281334</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1721476682418941</v>
+        <v>0.2359372310782425</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2253898367847173</v>
+        <v>0.0383032537231317</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2253898367847173</v>
+        <v>0.0383032537231317</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4839286611290518</v>
+        <v>0.4212253382936241</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.087286804422023</v>
+        <v>5.29854842137402</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.087286804422023</v>
+        <v>5.29854842137402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.6694720734506504</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.1928079571537873</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.1377199693955624</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.03730158730158717</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.302881567933547</v>
+        <v>0.6770695003939216</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3713294720046429</v>
+        <v>0.232959881634916</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3257889600618101</v>
+        <v>0.08997061797116201</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09370907540407636</v>
+        <v>0.007597426943271146</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09370907540407636</v>
+        <v>0.007597426943271146</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3713294720046429</v>
+        <v>0.6770695003939216</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.670913662673247</v>
+        <v>8.516784738082343</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.670913662673247</v>
+        <v>8.516784738082343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.2343636426568828</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2701754385964912</v>
+        <v>0.253366100169603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.343859649122807</v>
+        <v>0.5122702571735143</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0575139146567718</v>
+        <v>0.0667183577019641</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3811557120837989</v>
+        <v>0.3169820802417898</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3985337823970444</v>
+        <v>0.4205494237733842</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2203105055191567</v>
+        <v>0.262468495984826</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1283583438005532</v>
+        <v>0.1671833236037812</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1283583438005532</v>
+        <v>0.1671833236037812</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3985337823970444</v>
+        <v>0.4205494237733842</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.013113769789665</v>
+        <v>5.290046165007608</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.013113769789665</v>
+        <v>5.290046165007608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.3118996275240149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2768860353130017</v>
+        <v>0.2528915898843364</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.4352087825916487</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06223358908780896</v>
+        <v>0.06871988267337104</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.308712675107635</v>
+        <v>0.247572887414938</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3828096450416462</v>
+        <v>0.3579287211581472</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3084776798507189</v>
+        <v>0.3944983914269147</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1059236097286446</v>
+        <v>-0.04071039116473396</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1059236097286446</v>
+        <v>-0.04071039116473396</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3828096450416462</v>
+        <v>0.3944983914269147</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.81532152989398</v>
+        <v>4.962353018926422</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.81532152989398</v>
+        <v>4.962353018926422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.52083333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>chelsea</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>manchester city</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2185397867104184</v>
+        <v>0.2115884421342302</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2557506152584085</v>
+        <v>0.238036997401009</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5257095980311731</v>
+        <v>0.5503745604647607</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0567727080429159</v>
+        <v>0.05025690430314711</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.302199506290355</v>
+        <v>0.2050307080504469</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3377991579972073</v>
+        <v>0.5048616165758183</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3600013357124378</v>
+        <v>0.290107675373735</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1657082623187354</v>
+        <v>0.2668246191748093</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1657082623187354</v>
+        <v>0.2668246191748093</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3600013357124378</v>
+        <v>0.5048616165758183</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.528418249383713</v>
+        <v>6.350600209276699</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.528418249383713</v>
+        <v>6.350600209276699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.66666666666</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1787709497206704</v>
+        <v>0.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2346368715083799</v>
+        <v>0.15625</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5865921787709497</v>
+        <v>0.09375</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06547619047619047</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1620949559165673</v>
+        <v>0.5322684351398148</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3079108362561851</v>
+        <v>0.2989215459776636</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5299942078272477</v>
+        <v>0.1688100188825216</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.056597970943702</v>
+        <v>-0.2177315648601852</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.056597970943702</v>
+        <v>-0.2177315648601852</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5299942078272477</v>
+        <v>0.5322684351398148</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.666740383179233</v>
+        <v>6.695347644997011</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.666740383179233</v>
+        <v>6.695347644997011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>brighton</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,67 +1599,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7184292695122826</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.174787800811575</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1067829296761426</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02347461169869258</v>
+      </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4201801992737436</v>
+        <v>0.6978854772798477</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3827337577944768</v>
+        <v>0.2121230210400642</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1970860429317796</v>
+        <v>0.08999150168008795</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.02054379223243485</v>
+      </c>
       <c r="W12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.02054379223243485</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5798198007262565</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.6978854772798477</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.36</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>7.293491180433121</v>
+        <v>8.778626682147443</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.293491180433121</v>
+        <v>8.778626682147443</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1678,67 +1698,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5325312570829989</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2365369418596816</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2309318010573194</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02613335867818556</v>
+      </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4585042516923099</v>
+        <v>0.2565698812124252</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2980555862866562</v>
+        <v>0.4472026458110161</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2434401620210337</v>
+        <v>0.2962274729765587</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2106657039513345</v>
+      </c>
       <c r="W13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2106657039513345</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.5414957483076901</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.4472026458110161</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.12</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>6.811417029182747</v>
+        <v>5.625314190725431</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.811417029182747</v>
+        <v>5.625314190725431</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1757,67 +1797,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4182949968376552</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2662916236698734</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3154133794924714</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.02603318854132586</v>
+      </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3661185558879717</v>
+        <v>0.3746857391025852</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3444027951446086</v>
+        <v>0.2974032641796368</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2894786489674195</v>
+        <v>0.327910996717778</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.04360925773506996</v>
+      </c>
       <c r="W14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.04360925773506996</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.6338814441120284</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.3746857391025852</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.33</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>7.973526803121356</v>
+        <v>4.71313178707562</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.973526803121356</v>
+        <v>4.71313178707562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1836,67 +1896,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3375149298574894</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2594197200234427</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.403065350119068</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.02520134855005307</v>
+      </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5595522590652725</v>
+        <v>0.3118901882843965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2394327372055071</v>
+        <v>0.4044958678268427</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2010150037292205</v>
+        <v>0.2836139438887608</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1450761478034001</v>
+      </c>
       <c r="W15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1450761478034001</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.4404477409347275</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.4044958678268427</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.76</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.540344965669361</v>
+        <v>5.088110203931369</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.540344965669361</v>
+        <v>5.088110203931369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1915,67 +1995,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2308514762339465</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2453887228481749</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5237598009178787</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.02649040201244324</v>
+      </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4048621671972947</v>
+        <v>0.2795713806465628</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3524844864137729</v>
+        <v>0.3961070928780267</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2426533463889323</v>
+        <v>0.3243215264754103</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1507183700298518</v>
+      </c>
       <c r="W16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1507183700298518</v>
+      </c>
       <c r="Y16" t="n">
-        <v>0.5951378328027053</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+        <v>0.3961070928780267</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.97</v>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>7.486175065514715</v>
+        <v>4.982588702204121</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.486175065514715</v>
+        <v>4.982588702204121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1994,67 +2094,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4845874148644616</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.260433343282772</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2549792418527664</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.02667222166737226</v>
+      </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6750319510992732</v>
+        <v>0.530349760778192</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2345401618175841</v>
+        <v>0.2626856615018118</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09042788708314296</v>
+        <v>0.206964577719996</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.04576234591373041</v>
+      </c>
       <c r="W17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.04576234591373041</v>
+      </c>
       <c r="Y17" t="n">
-        <v>0.3249680489007268</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>0.530349760778192</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.01</v>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.087738286293886</v>
+        <v>6.671212845672995</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.087738286293886</v>
+        <v>6.671212845672995</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2073,67 +2193,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1201409216741935</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.169536840690064</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.7103222376357425</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.02759982529729132</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2890997883354035</v>
+        <v>0.2583208704825306</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3971268210688618</v>
+        <v>0.3557625332145566</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3137733905957346</v>
+        <v>0.3859165963029126</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.3244056413328299</v>
+      </c>
       <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.3244056413328299</v>
+      </c>
       <c r="Y18" t="n">
-        <v>0.6028731789311381</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
+        <v>0.3859165963029126</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.37</v>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>7.583477156086055</v>
+        <v>4.85440353708604</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.583477156086055</v>
+        <v>4.85440353708604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2152,67 +2292,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5449139057541359</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2339078876018953</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.221178206643969</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.02522474096882554</v>
+      </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3057220661847874</v>
+        <v>0.569463768186811</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3499457135311053</v>
+        <v>0.2982728698254571</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3443322202841073</v>
+        <v>0.132263361987732</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.0245498624326751</v>
+      </c>
       <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.0245498624326751</v>
+      </c>
       <c r="Y19" t="n">
-        <v>0.6500542864688947</v>
-      </c>
-      <c r="Z19" t="inlineStr"/>
+        <v>0.569463768186811</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.79</v>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8.176963255178689</v>
+        <v>7.16322375614696</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.176963255178689</v>
+        <v>7.16322375614696</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2231,67 +2391,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4319924318371151</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2313513971449953</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3366561710178897</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.02427228695764105</v>
+      </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2126273385644954</v>
+        <v>0.1235467217392634</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5036997800859342</v>
+        <v>0.4356381323605248</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2836728813495706</v>
+        <v>0.4408151459002118</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1041589748823221</v>
+      </c>
       <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1041589748823221</v>
+      </c>
       <c r="Y20" t="n">
-        <v>0.4963002199140658</v>
-      </c>
-      <c r="Z20" t="inlineStr"/>
+        <v>0.4408151459002118</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>6.242907317508483</v>
+        <v>5.544966513384789</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.242907317508483</v>
+        <v>5.544966513384789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>liverpool</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>brentford</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2310,48 +2490,68 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2414799967831536</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2311799021336352</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5273401010832111</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.02503211766033786</v>
+      </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5295790047290388</v>
+        <v>0.3036969033636501</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3023696763548994</v>
+        <v>0.440597423374963</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1680513189160616</v>
+        <v>0.255705673261387</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.2094175212413278</v>
+      </c>
       <c r="W21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.2094175212413278</v>
+      </c>
       <c r="Y21" t="n">
-        <v>0.4704209952709612</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
+        <v>0.440597423374963</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.22</v>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.917375322129037</v>
+        <v>5.542227805055591</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.917375322129037</v>
+        <v>5.542227805055591</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -634,29 +634,29 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4135967408248821</v>
+        <v>0.3989778390404748</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3806498419345348</v>
+        <v>0.3927254384539149</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2057534172405832</v>
+        <v>0.2082967225056102</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.03282510207077338</v>
+        <v>0.01820620028636616</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03282510207077338</v>
+        <v>0.01820620028636616</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4135967408248821</v>
+        <v>0.3989778390404748</v>
       </c>
       <c r="Z2" t="n">
         <v>2.5</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.202589110761217</v>
+        <v>6.081161189893853</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.202589110761217</v>
+        <v>6.081161189893853</v>
       </c>
     </row>
     <row r="3">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4321728691476591</v>
+        <v>0.4465116279069767</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2581032412965186</v>
+        <v>0.2604651162790698</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3097238895558223</v>
+        <v>0.2930232558139535</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07622739018087854</v>
+        <v>0.06646825396825395</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -746,19 +746,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.01766854371892418</v>
+        <v>0.003329784959606508</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01766854371892418</v>
+        <v>0.003329784959606508</v>
       </c>
       <c r="Y3" t="n">
         <v>0.4498414128665832</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.658506958931847</v>
+        <v>6.856416256377014</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.658506958931847</v>
+        <v>6.856416256377014</v>
       </c>
     </row>
     <row r="4">
@@ -808,25 +808,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.539701816903434</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2421738922002589</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2181242908963071</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05878571005591793</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -845,19 +845,19 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1769510796651999</v>
+        <v>-0.1629409623665091</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1769510796651999</v>
+        <v>-0.1629409623665091</v>
       </c>
       <c r="Y4" t="n">
         <v>0.3627507372382341</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.563002676743296</v>
+        <v>5.528993064386082</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.563002676743296</v>
+        <v>5.528993064386082</v>
       </c>
     </row>
     <row r="5">
@@ -931,29 +931,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5629561455712984</v>
+        <v>0.5491749849148966</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2377463557826995</v>
+        <v>0.2434615904871366</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1992974986460023</v>
+        <v>0.2073634245979667</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.3017521705230335</v>
+        <v>-0.3155333311794353</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3017521705230335</v>
+        <v>-0.3155333311794353</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5629561455712984</v>
+        <v>0.5491749849148966</v>
       </c>
       <c r="Z5" t="n">
         <v>1.09</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.081365068167733</v>
+        <v>8.370443864142086</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.081365068167733</v>
+        <v>8.370443864142086</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4212253382936241</v>
+        <v>0.4193737193529274</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3428374306281334</v>
+        <v>0.3441924580806889</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2359372310782425</v>
+        <v>0.2364338225663835</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.0383032537231317</v>
+        <v>0.03645163478243496</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0383032537231317</v>
+        <v>0.03645163478243496</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4212253382936241</v>
+        <v>0.4193737193529274</v>
       </c>
       <c r="Z6" t="n">
         <v>2.45</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.29854842137402</v>
+        <v>6.392032179841803</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.29854842137402</v>
+        <v>6.392032179841803</v>
       </c>
     </row>
     <row r="7">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -1114,47 +1114,47 @@
         <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6694720734506504</v>
+        <v>0.66793893129771</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1928079571537873</v>
+        <v>0.1937022900763359</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1377199693955624</v>
+        <v>0.1383587786259542</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03730158730158717</v>
+        <v>0.0325123152709359</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6770695003939216</v>
+        <v>0.6788392562006584</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232959881634916</v>
+        <v>0.2325314729990392</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08997061797116201</v>
+        <v>0.08862927080030206</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.007597426943271146</v>
+        <v>0.01090032490294846</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.007597426943271146</v>
+        <v>0.01090032490294846</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6770695003939216</v>
+        <v>0.6788392562006584</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>8.516784738082343</v>
+        <v>10.34676750195409</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.516784738082343</v>
+        <v>10.34676750195409</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2343636426568828</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="M8" t="n">
-        <v>0.253366100169603</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5122702571735143</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0667183577019641</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3169820802417898</v>
+        <v>0.3053589458051205</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4205494237733842</v>
+        <v>0.4237776487019204</v>
       </c>
       <c r="S8" t="n">
-        <v>0.262468495984826</v>
+        <v>0.2708634054929589</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1671833236037812</v>
+        <v>0.1722806427138965</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1671833236037812</v>
+        <v>0.1722806427138965</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4205494237733842</v>
+        <v>0.4237776487019204</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.290046165007608</v>
+        <v>6.459156219373769</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.290046165007608</v>
+        <v>6.459156219373769</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.247572887414938</v>
+        <v>0.2636927884311544</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3579287211581472</v>
+        <v>0.3442526354915076</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3944983914269147</v>
+        <v>0.392054576077338</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.04071039116473396</v>
+        <v>-0.04315420651431068</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.04071039116473396</v>
+        <v>-0.04315420651431068</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3944983914269147</v>
+        <v>0.392054576077338</v>
       </c>
       <c r="Z9" t="n">
         <v>2.15</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.962353018926422</v>
+        <v>5.975637840175709</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.962353018926422</v>
+        <v>5.975637840175709</v>
       </c>
     </row>
     <row r="10">
@@ -1426,29 +1426,29 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2050307080504469</v>
+        <v>0.2272182115925958</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5048616165758183</v>
+        <v>0.4944436303175734</v>
       </c>
       <c r="S10" t="n">
-        <v>0.290107675373735</v>
+        <v>0.2783381580898309</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2668246191748093</v>
+        <v>0.2564066329165644</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2668246191748093</v>
+        <v>0.2564066329165644</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5048616165758183</v>
+        <v>0.4944436303175734</v>
       </c>
       <c r="Z10" t="n">
         <v>4</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.350600209276699</v>
+        <v>7.536236655420911</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.350600209276699</v>
+        <v>7.536236655420911</v>
       </c>
     </row>
     <row r="11">
@@ -1504,50 +1504,50 @@
         <v>1.25</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="K11" t="n">
         <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0.75</v>
+        <v>0.7449392712550608</v>
       </c>
       <c r="M11" t="n">
-        <v>0.15625</v>
+        <v>0.1619433198380567</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09375</v>
+        <v>0.0931174089068826</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.07391304347826089</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5322684351398148</v>
+        <v>0.5238695024426842</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2989215459776636</v>
+        <v>0.2999955701380816</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1688100188825216</v>
+        <v>0.1761349274192343</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.2177315648601852</v>
+        <v>-0.2210697688123766</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2177315648601852</v>
+        <v>-0.2210697688123766</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5322684351398148</v>
+        <v>0.5238695024426842</v>
       </c>
       <c r="Z11" t="n">
         <v>1.25</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.695347644997011</v>
+        <v>7.98474144449981</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.695347644997011</v>
+        <v>7.98474144449981</v>
       </c>
     </row>
     <row r="12">
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="J12" t="n">
-        <v>5.59</v>
+        <v>6.2</v>
       </c>
       <c r="K12" t="n">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7184292695122826</v>
+        <v>0.7399399062087557</v>
       </c>
       <c r="M12" t="n">
-        <v>0.174787800811575</v>
+        <v>0.1503748841650052</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1067829296761426</v>
+        <v>0.1096852096262391</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02347461169869258</v>
+        <v>0.07258817505496817</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1637,19 +1637,19 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.02054379223243485</v>
+        <v>-0.04205442892890798</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.02054379223243485</v>
+        <v>-0.04205442892890798</v>
       </c>
       <c r="Y12" t="n">
         <v>0.6978854772798477</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>8.778626682147443</v>
+        <v>10.63706718556422</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.778626682147443</v>
+        <v>10.63706718556422</v>
       </c>
     </row>
     <row r="13">
@@ -1699,56 +1699,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5325312570829989</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2365369418596816</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2309318010573194</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02613335867818556</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2565698812124252</v>
+        <v>0.2600936500338568</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4472026458110161</v>
+        <v>0.4395775508286483</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2962274729765587</v>
+        <v>0.3003287991374951</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2106657039513345</v>
+        <v>0.1948076763516609</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2106657039513345</v>
+        <v>0.1948076763516609</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4472026458110161</v>
+        <v>0.4395775508286483</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.625314190725431</v>
+        <v>6.699975989835837</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.625314190725431</v>
+        <v>6.699975989835837</v>
       </c>
     </row>
     <row r="14">
@@ -1798,56 +1798,56 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="J14" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4182949968376552</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2662916236698734</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3154133794924714</v>
+        <v>0.3109756097560976</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02603318854132586</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3746857391025852</v>
+        <v>0.380636738846739</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2974032641796368</v>
+        <v>0.3017834860568411</v>
       </c>
       <c r="S14" t="n">
-        <v>0.327910996717778</v>
+        <v>0.31757977509642</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.04360925773506996</v>
+        <v>-0.03399740749472441</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.04360925773506996</v>
+        <v>-0.03399740749472441</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3746857391025852</v>
+        <v>0.380636738846739</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>4.71313178707562</v>
+        <v>5.801608854490116</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.71313178707562</v>
+        <v>5.801608854490116</v>
       </c>
     </row>
     <row r="15">
@@ -1897,56 +1897,56 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3375149298574894</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2594197200234427</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="N15" t="n">
-        <v>0.403065350119068</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02520134855005307</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3118901882843965</v>
+        <v>0.3132764197385587</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4044958678268427</v>
+        <v>0.4047879625307436</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2836139438887608</v>
+        <v>0.2819356177306978</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1450761478034001</v>
+        <v>0.1288588133549475</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1450761478034001</v>
+        <v>0.1288588133549475</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4044958678268427</v>
+        <v>0.4047879625307436</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.088110203931369</v>
+        <v>6.169718232466657</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.088110203931369</v>
+        <v>6.169718232466657</v>
       </c>
     </row>
     <row r="16">
@@ -1996,25 +1996,25 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2308514762339465</v>
+        <v>0.2113676731793961</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2453887228481749</v>
+        <v>0.2415630550621669</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5237598009178787</v>
+        <v>0.547069271758437</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02649040201244324</v>
+        <v>0.07524828113063409</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2033,19 +2033,19 @@
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1507183700298518</v>
+        <v>0.1545440378158598</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1507183700298518</v>
+        <v>0.1545440378158598</v>
       </c>
       <c r="Y16" t="n">
         <v>0.3961070928780267</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>4.982588702204121</v>
+        <v>6.03740570164142</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.982588702204121</v>
+        <v>6.03740570164142</v>
       </c>
     </row>
     <row r="17">
@@ -2095,56 +2095,56 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4845874148644616</v>
+        <v>0.4899328859060403</v>
       </c>
       <c r="M17" t="n">
-        <v>0.260433343282772</v>
+        <v>0.2550335570469799</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2549792418527664</v>
+        <v>0.2550335570469799</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02667222166737226</v>
+        <v>0.07426099495313609</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.530349760778192</v>
+        <v>0.5277683832868997</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2626856615018118</v>
+        <v>0.2589914324549981</v>
       </c>
       <c r="S17" t="n">
-        <v>0.206964577719996</v>
+        <v>0.2132401842581021</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.04576234591373041</v>
+        <v>0.03783549738085934</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.04576234591373041</v>
+        <v>0.03783549738085934</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.530349760778192</v>
+        <v>0.5277683832868997</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>6.671212845672995</v>
+        <v>8.044167609448934</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.671212845672995</v>
+        <v>8.044167609448934</v>
       </c>
     </row>
     <row r="18">
@@ -2194,56 +2194,56 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.74</v>
+        <v>5.8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1201409216741935</v>
+        <v>0.1240335581510117</v>
       </c>
       <c r="M18" t="n">
-        <v>0.169536840690064</v>
+        <v>0.1603882217469979</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7103222376357425</v>
+        <v>0.7155782201019903</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02759982529729132</v>
+        <v>0.07497789566755086</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2583208704825306</v>
+        <v>0.2620487569102588</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3557625332145566</v>
+        <v>0.3548187203193317</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3859165963029126</v>
+        <v>0.3831325227704095</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-0.3244056413328299</v>
+        <v>-0.3324456973315809</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3244056413328299</v>
+        <v>-0.3324456973315809</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3859165963029126</v>
+        <v>0.3831325227704095</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>4.85440353708604</v>
+        <v>5.839649223778512</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.85440353708604</v>
+        <v>5.839649223778512</v>
       </c>
     </row>
     <row r="19">
@@ -2293,25 +2293,25 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="J19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5449139057541359</v>
+        <v>0.5605730302086578</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2339078876018953</v>
+        <v>0.232637807536593</v>
       </c>
       <c r="N19" t="n">
-        <v>0.221178206643969</v>
+        <v>0.2067891622547493</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02522474096882554</v>
+        <v>0.07463186077643913</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2330,19 +2330,19 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.0245498624326751</v>
+        <v>0.008890737978153207</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0245498624326751</v>
+        <v>0.008890737978153207</v>
       </c>
       <c r="Y19" t="n">
         <v>0.569463768186811</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>7.16322375614696</v>
+        <v>8.679682496844231</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.16322375614696</v>
+        <v>8.679682496844231</v>
       </c>
     </row>
     <row r="20">
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="J20" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4319924318371151</v>
+        <v>0.4337722695584818</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2313513971449953</v>
+        <v>0.233152594887684</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3366561710178897</v>
+        <v>0.3330751355538342</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02427228695764105</v>
+        <v>0.07225913621262459</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1041589748823221</v>
+        <v>0.1077400103463775</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1041589748823221</v>
+        <v>0.1077400103463775</v>
       </c>
       <c r="Y20" t="n">
         <v>0.4408151459002118</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>5.544966513384789</v>
+        <v>6.71883923080204</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.544966513384789</v>
+        <v>6.71883923080204</v>
       </c>
     </row>
     <row r="21">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="K21" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2414799967831536</v>
+        <v>0.2331308380691097</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2311799021336352</v>
+        <v>0.2247044222352864</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5273401010832111</v>
+        <v>0.5421647396956039</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02503211766033786</v>
+        <v>0.07235920425889608</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2528,19 +2528,19 @@
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2094175212413278</v>
+        <v>0.2158930011396766</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2094175212413278</v>
+        <v>0.2158930011396766</v>
       </c>
       <c r="Y21" t="n">
         <v>0.440597423374963</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.542227805055591</v>
+        <v>6.715520736286424</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.542227805055591</v>
+        <v>6.715520736286424</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3807716387541087</v>
+        <v>0.3265602322206096</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2572781342933166</v>
+        <v>0.2525399129172714</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3619502269525748</v>
+        <v>0.420899854862119</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0504984071523995</v>
+        <v>0.0559386973180076</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3651282136956015</v>
+        <v>0.3414706538032015</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3867635366828823</v>
+        <v>0.3484468234964621</v>
       </c>
       <c r="S2" t="n">
-        <v>0.248108249621516</v>
+        <v>0.3100825227003365</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1294854023895657</v>
+        <v>0.09590691057919065</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1294854023895657</v>
+        <v>0.09590691057919065</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3867635366828823</v>
+        <v>0.3484468234964621</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.894992600587604</v>
+        <v>4.520862871078755</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.894992600587604</v>
+        <v>4.520862871078755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4407039020657995</v>
+        <v>0.2194529351830081</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2631981637337414</v>
+        <v>0.2375578023356062</v>
       </c>
       <c r="N3" t="n">
-        <v>0.296097934200459</v>
+        <v>0.5429892624813857</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05539405684754528</v>
+        <v>0.05237545364566154</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4501236750161868</v>
+        <v>0.2231079220403186</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2955406595191336</v>
+        <v>0.4954316762670784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2543356654646798</v>
+        <v>0.2814604016926031</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.009419772950387262</v>
+        <v>0.2578738739314722</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009419772950387262</v>
+        <v>0.2578738739314722</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4501236750161868</v>
+        <v>0.4954316762670784</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.860718454297763</v>
+        <v>7.664144197087736</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.860718454297763</v>
+        <v>7.664144197087736</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.7714348688560723</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.1344500771434869</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.09411505400044082</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.06252927400468389</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3696892676679485</v>
+        <v>0.5330998300562646</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3474616123366054</v>
+        <v>0.294482836970695</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2828491199954459</v>
+        <v>0.1724173329730405</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1578191383551499</v>
+        <v>-0.2383350387998077</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1578191383551499</v>
+        <v>-0.2383350387998077</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3696892676679485</v>
+        <v>0.5330998300562646</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.634749118570826</v>
+        <v>2.998942280218844</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.634749118570826</v>
+        <v>2.998942280218844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8760951188986232</v>
+        <v>0.7101928819304333</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07884856070087611</v>
+        <v>0.1717375514486321</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04505632040050063</v>
+        <v>0.1180695666209345</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05687830687830675</v>
+        <v>0.05869788106630214</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5558670086678195</v>
+        <v>0.6701789378831791</v>
       </c>
       <c r="R5" t="n">
-        <v>0.240258235145118</v>
+        <v>0.2356857997484584</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2038747561870623</v>
+        <v>0.0941352623683625</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.3202281102308038</v>
+        <v>-0.04001394404725422</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3202281102308038</v>
+        <v>-0.04001394404725422</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5558670086678195</v>
+        <v>0.6701789378831791</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>8.472442700032301</v>
+        <v>6.411309965049989</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.472442700032301</v>
+        <v>6.411309965049989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>southampton</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>nottingham</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4167545830538981</v>
+        <v>0.257103999840847</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3396299526711907</v>
+        <v>0.4488244192043908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2436154642749111</v>
+        <v>0.2940715809547624</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.02784362904643128</v>
+        <v>0.1998125614968809</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02784362904643128</v>
+        <v>0.1998125614968809</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4167545830538981</v>
+        <v>0.4488244192043908</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.352111691899406</v>
+        <v>6.599244291174911</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.352111691899406</v>
+        <v>6.599244291174911</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6655744419414295</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.189023141511366</v>
+        <v>0.2840909090909091</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1454024165472046</v>
+        <v>0.3409090909090908</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05807150595882993</v>
+        <v>0.06666666666666687</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6343401981952623</v>
+        <v>0.3648565432684523</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2631415418540304</v>
+        <v>0.3094633496312834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.102518259950707</v>
+        <v>0.3256801071002642</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.03123424374616712</v>
+        <v>-0.01014345673154765</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.03123424374616712</v>
+        <v>-0.01014345673154765</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6343401981952623</v>
+        <v>0.3648565432684523</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>9.668519443916463</v>
+        <v>3.608857313073502</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.668519443916463</v>
+        <v>3.608857313073502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,67 +1204,661 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2115884421342302</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="M8" t="n">
-        <v>0.238036997401009</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5503745604647607</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05025690430314711</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3226665213935301</v>
+        <v>0.2863666961828495</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4078427917557404</v>
+        <v>0.4243917943199728</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2694906868507294</v>
+        <v>0.2892415094971777</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1698057943547314</v>
+        <v>0.1475057590069712</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1698057943547314</v>
+        <v>0.1475057590069712</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4078427917557404</v>
+        <v>0.4243917943199728</v>
       </c>
       <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.818495978828386</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.818495978828386</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1982507288629737</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2478134110787172</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5539358600583091</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0619195046439629</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2601219111679994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4015406686696749</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3383374201623257</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1537272575909577</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1537272575909577</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4015406686696749</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.649305854387632</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.649305854387632</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.473491773308958</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2705667276051188</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2559414990859232</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05598455598455598</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5303673627555352</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2637497609368518</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2058828763076134</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.05687558944657722</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.05687558944657722</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5303673627555352</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.974620342587714</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.974620342587714</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1189603465511496</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1812729090303233</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6997667444185273</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05077030812324912</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2693238507358822</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3508711657708304</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3798049834932873</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.3199617609252399</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.3199617609252399</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3798049834932873</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6088460211915918</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6088460211915918</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5738880918220947</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.236728837876614</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1893830703012913</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05606060606060614</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5564943542970062</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3014575181889912</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1420481275140022</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.01739373752508844</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.01739373752508844</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5564943542970062</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB8" t="n">
-        <v>6.216279487521526</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.216279487521526</v>
+      <c r="AB12" t="n">
+        <v>5.484819357284569</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.484819357284569</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.425531914893617</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2340425531914893</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3404255319148936</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06818181818181834</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1252894972557409</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4368824987952959</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.437828003948963</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.09740247203406949</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.09740247203406949</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.437828003948963</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.445444475390722</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.445444475390722</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2508352608583912</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2351580570547417</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5140066820868672</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06311475409836054</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3195689671805956</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4526536631475223</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2277773696718821</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2174956060927806</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2174956060927806</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4526536631475223</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.818110701131717</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.818110701131717</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>dif_prob_limited</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="K2" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3265602322206096</v>
+        <v>0.7044320516583504</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2525399129172714</v>
+        <v>0.1784561197534488</v>
       </c>
       <c r="N2" t="n">
-        <v>0.420899854862119</v>
+        <v>0.1171118285882008</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0559386973180076</v>
+        <v>0.06735588972431072</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3414706538032015</v>
+        <v>0.6672175658776862</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3484468234964621</v>
+        <v>0.2362950978086863</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3100825227003365</v>
+        <v>0.09648733631362705</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.09590691057919065</v>
+        <v>-0.03721448578066422</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09590691057919065</v>
+        <v>-0.03721448578066422</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3484468234964621</v>
+        <v>0.6672175658776862</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>1.33</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.520862871078755</v>
+        <v>-0.03721448578066422</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.520862871078755</v>
+        <v>6.409662651762421</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6.409662651762421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2194529351830081</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2375578023356062</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5429892624813857</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05237545364566154</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2231079220403186</v>
+        <v>0.2690389483506044</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4954316762670784</v>
+        <v>0.4371485844030001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2814604016926031</v>
+        <v>0.2938124672463954</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2578738739314722</v>
+        <v>0.1941452741411885</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2578738739314722</v>
+        <v>0.1941452741411885</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4954316762670784</v>
+        <v>0.4371485844030001</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.664144197087736</v>
+        <v>0.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.664144197087736</v>
+        <v>5.9736602429047</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.9736602429047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7714348688560723</v>
+        <v>0.3500611995104039</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1344500771434869</v>
+        <v>0.2864137086903305</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09411505400044082</v>
+        <v>0.3635250917992656</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06252927400468389</v>
+        <v>0.05801605801605803</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5330998300562646</v>
+        <v>0.3775662407684194</v>
       </c>
       <c r="R4" t="n">
-        <v>0.294482836970695</v>
+        <v>0.3061922990688685</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1724173329730405</v>
+        <v>0.3162414601627119</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.2383350387998077</v>
+        <v>0.02750504125801551</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2383350387998077</v>
+        <v>0.02750504125801551</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5330998300562646</v>
+        <v>0.3775662407684194</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +876,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.998942280218844</v>
+        <v>0.02750504125801551</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.998942280218844</v>
+        <v>4.121202498417174</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.121202498417174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.35416666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7101928819304333</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1717375514486321</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1180695666209345</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05869788106630214</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6701789378831791</v>
+        <v>0.2829514750874087</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2356857997484584</v>
+        <v>0.4207131119734042</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0941352623683625</v>
+        <v>0.296335412939187</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.04001394404725422</v>
+        <v>0.1438270766604026</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.04001394404725422</v>
+        <v>0.1438270766604026</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6701789378831791</v>
+        <v>0.4207131119734042</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,16 +978,19 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.411309965049989</v>
+        <v>0.1438270766604026</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.411309965049989</v>
+        <v>5.743642018302139</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5.743642018302139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -981,12 +998,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.2095808383233533</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="N6" t="n">
-        <v>0.225296442687747</v>
+        <v>0.5389221556886227</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.257103999840847</v>
+        <v>0.2604150849387148</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4488244192043908</v>
+        <v>0.3897903281490144</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2940715809547624</v>
+        <v>0.3497945869122707</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1998125614968809</v>
+        <v>0.1382933221609905</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1998125614968809</v>
+        <v>0.1382933221609905</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4488244192043908</v>
+        <v>0.3897903281490144</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,16 +1080,19 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.599244291174911</v>
+        <v>0.1382933221609905</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.599244291174911</v>
+        <v>5.37273254263635</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.37273254263635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1080,12 +1100,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3749999999999999</v>
+        <v>0.4902227790184651</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2840909090909091</v>
+        <v>0.2600904188681301</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3409090909090908</v>
+        <v>0.2496868021134049</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06666666666666687</v>
+        <v>0.06800465386852816</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3648565432684523</v>
+        <v>0.5288904567085696</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3094633496312834</v>
+        <v>0.264687169148089</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3256801071002642</v>
+        <v>0.2064223741433413</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.01014345673154765</v>
+        <v>0.03866767769010454</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.01014345673154765</v>
+        <v>0.03866767769010454</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3648565432684523</v>
+        <v>0.5288904567085696</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.608857313073502</v>
+        <v>0.03866767769010454</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.608857313073502</v>
+        <v>5.774346652716205</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.774346652716205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.1260273972602739</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2768860353130016</v>
+        <v>0.1890410958904109</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06223358908780918</v>
+        <v>0.05797101449275388</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2863666961828495</v>
+        <v>0.2729219326125357</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4243917943199728</v>
+        <v>0.3525309327803374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2892415094971777</v>
+        <v>0.3745471346071269</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1475057590069712</v>
+        <v>-0.3103843722421881</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1475057590069712</v>
+        <v>-0.3103843722421881</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4243917943199728</v>
+        <v>0.3745471346071269</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.818495978828386</v>
+        <v>-0.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.818495978828386</v>
+        <v>2.284546580359447</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.284546580359447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.75</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1982507288629737</v>
+        <v>0.5714914533049666</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2478134110787172</v>
+        <v>0.2299904629154134</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5539358600583091</v>
+        <v>0.19851808377962</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0619195046439629</v>
+        <v>0.06048936087446988</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2601219111679994</v>
+        <v>0.5511760864714842</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4015406686696749</v>
+        <v>0.2957071990772793</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3383374201623257</v>
+        <v>0.1531167144512364</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1537272575909577</v>
+        <v>-0.02031536683348245</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1537272575909577</v>
+        <v>-0.02031536683348245</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4015406686696749</v>
+        <v>0.5511760864714842</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.649305854387632</v>
+        <v>-0.02031536683348245</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.649305854387632</v>
+        <v>5.400986495855554</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.400986495855554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="L10" t="n">
-        <v>0.473491773308958</v>
+        <v>0.3935185185185184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.236111111111111</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.05882352941176494</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5303673627555352</v>
+        <v>0.1420404457482405</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2637497609368518</v>
+        <v>0.4408900048065116</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2058828763076134</v>
+        <v>0.417069549445248</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.05687558944657722</v>
+        <v>0.2047788936954005</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05687558944657722</v>
+        <v>0.2047788936954005</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5303673627555352</v>
+        <v>0.4408900048065116</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1488,32 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.974620342587714</v>
+        <v>0.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.974620342587714</v>
+        <v>6.011725521285936</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6.011725521285936</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1533,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1189603465511496</v>
+        <v>0.2414486921529175</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1812729090303233</v>
+        <v>0.2354124748490946</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6997667444185273</v>
+        <v>0.5231388329979879</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05077030812324912</v>
+        <v>0.06196581196581197</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2693238507358822</v>
+        <v>0.3338456535702459</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3508711657708304</v>
+        <v>0.4377967811533599</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3798049834932873</v>
+        <v>0.228357565276394</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.3199617609252399</v>
+        <v>0.2023843063042653</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3199617609252399</v>
+        <v>0.2023843063042653</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3798049834932873</v>
+        <v>0.4377967811533599</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,307 +1590,13 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>0.6088460211915918</v>
+        <v>0.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.6088460211915918</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>crystal palace</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5738880918220947</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.236728837876614</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1893830703012913</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.05606060606060614</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.5564943542970062</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3014575181889912</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1420481275140022</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.01739373752508844</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.01739373752508844</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5564943542970062</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.484819357284569</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5.484819357284569</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>newcastle</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" t="n">
-        <v>481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.425531914893617</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2340425531914893</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.3404255319148936</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06818181818181834</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1252894972557409</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.4368824987952959</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.437828003948963</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.09740247203406949</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.09740247203406949</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.437828003948963</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>5.445444475390722</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.445444475390722</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>liverpool</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2508352608583912</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2351580570547417</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.5140066820868672</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06311475409836054</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3195689671805956</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.4526536631475223</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2277773696718821</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.2174956060927806</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.2174956060927806</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4526536631475223</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.818110701131717</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.818110701131717</v>
+        <v>5.980255008284473</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.980255008284473</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,10 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_limited</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -672,12 +667,9 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-0.03721448578066422</v>
+        <v>6.409662651762421</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.409662651762421</v>
-      </c>
-      <c r="AD2" t="n">
         <v>6.409662651762421</v>
       </c>
     </row>
@@ -774,12 +766,9 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.15</v>
+        <v>5.9736602429047</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9736602429047</v>
-      </c>
-      <c r="AD3" t="n">
         <v>5.9736602429047</v>
       </c>
     </row>
@@ -876,12 +865,9 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.02750504125801551</v>
+        <v>4.121202498417174</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.121202498417174</v>
-      </c>
-      <c r="AD4" t="n">
         <v>4.121202498417174</v>
       </c>
     </row>
@@ -978,12 +964,9 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.1438270766604026</v>
+        <v>5.743642018302139</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.743642018302139</v>
-      </c>
-      <c r="AD5" t="n">
         <v>5.743642018302139</v>
       </c>
     </row>
@@ -1080,12 +1063,9 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.1382933221609905</v>
+        <v>5.37273254263635</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.37273254263635</v>
-      </c>
-      <c r="AD6" t="n">
         <v>5.37273254263635</v>
       </c>
     </row>
@@ -1182,12 +1162,9 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.03866767769010454</v>
+        <v>5.774346652716205</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.774346652716205</v>
-      </c>
-      <c r="AD7" t="n">
         <v>5.774346652716205</v>
       </c>
     </row>
@@ -1284,12 +1261,9 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-0.15</v>
+        <v>2.284546580359447</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.284546580359447</v>
-      </c>
-      <c r="AD8" t="n">
         <v>2.284546580359447</v>
       </c>
     </row>
@@ -1386,12 +1360,9 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-0.02031536683348245</v>
+        <v>5.400986495855554</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.400986495855554</v>
-      </c>
-      <c r="AD9" t="n">
         <v>5.400986495855554</v>
       </c>
     </row>
@@ -1488,12 +1459,9 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.15</v>
+        <v>6.011725521285936</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.011725521285936</v>
-      </c>
-      <c r="AD10" t="n">
         <v>6.011725521285936</v>
       </c>
     </row>
@@ -1590,12 +1558,9 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>0.15</v>
+        <v>5.980255008284473</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.980255008284473</v>
-      </c>
-      <c r="AD11" t="n">
         <v>5.980255008284473</v>
       </c>
     </row>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -634,29 +634,29 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6672175658776862</v>
+        <v>0.6628477424400651</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2362950978086863</v>
+        <v>0.23756277683258</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09648733631362705</v>
+        <v>0.09958948072735496</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.03721448578066422</v>
+        <v>-0.04158430921828538</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03721448578066422</v>
+        <v>-0.04158430921828538</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6672175658776862</v>
+        <v>0.6628477424400651</v>
       </c>
       <c r="Z2" t="n">
         <v>1.33</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.409662651762421</v>
+        <v>9.059073400882111</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.409662651762421</v>
+        <v>9.059073400882111</v>
       </c>
     </row>
     <row r="3">
@@ -709,53 +709,53 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="J3" t="n">
         <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5574781823653325</v>
+        <v>0.5441860465116279</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2430033102618116</v>
+        <v>0.244186046511628</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1995185073728558</v>
+        <v>0.2116279069767442</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05517186631737725</v>
+        <v>0.05006105006104988</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2690389483506044</v>
+        <v>0.2695687867755708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4371485844030001</v>
+        <v>0.4381085430417852</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2938124672463954</v>
+        <v>0.292322670182644</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1941452741411885</v>
+        <v>0.1939224965301572</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1941452741411885</v>
+        <v>0.1939224965301572</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4371485844030001</v>
+        <v>0.4381085430417852</v>
       </c>
       <c r="Z3" t="n">
         <v>3.9</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.9736602429047</v>
+        <v>7.84653422104285</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9736602429047</v>
+        <v>7.84653422104285</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3500611995104039</v>
+        <v>0.3368721927317272</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2864137086903305</v>
+        <v>0.2858309514087382</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3635250917992656</v>
+        <v>0.3772968558595345</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05801605801605803</v>
+        <v>0.06017316017316032</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3775662407684194</v>
+        <v>0.3937602166575641</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3061922990688685</v>
+        <v>0.3135591315478707</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3162414601627119</v>
+        <v>0.292680651794565</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.02750504125801551</v>
+        <v>0.05688802392583692</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02750504125801551</v>
+        <v>0.05688802392583692</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3775662407684194</v>
+        <v>0.3937602166575641</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.121202498417174</v>
+        <v>6.571214835955183</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.121202498417174</v>
+        <v>6.571214835955183</v>
       </c>
     </row>
     <row r="5">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.3212510356255179</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2768860353130016</v>
+        <v>0.2823115161557581</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.3964374482187241</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06223358908780918</v>
+        <v>0.07338980413081653</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2829514750874087</v>
+        <v>0.2838073991274223</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4207131119734042</v>
+        <v>0.4200644398565816</v>
       </c>
       <c r="S5" t="n">
-        <v>0.296335412939187</v>
+        <v>0.296128161015996</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1438270766604026</v>
+        <v>0.1377529237008235</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1438270766604026</v>
+        <v>0.1377529237008235</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4207131119734042</v>
+        <v>0.4200644398565816</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.743642018302139</v>
+        <v>7.583420626282964</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.743642018302139</v>
+        <v>7.583420626282964</v>
       </c>
     </row>
     <row r="6">
@@ -1009,53 +1009,53 @@
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2095808383233533</v>
+        <v>0.2089704059251724</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2514970059880239</v>
+        <v>0.2474649543850726</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5389221556886227</v>
+        <v>0.543564639689755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06031746031746033</v>
+        <v>0.06341479903998914</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2604150849387148</v>
+        <v>0.2646078634996389</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3897903281490144</v>
+        <v>0.3891742873764772</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3497945869122707</v>
+        <v>0.3462178491238836</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1382933221609905</v>
+        <v>0.1417093329914046</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1382933221609905</v>
+        <v>0.1417093329914046</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3897903281490144</v>
+        <v>0.3891742873764772</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.37273254263635</v>
+        <v>7.132989869026711</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.37273254263635</v>
+        <v>7.132989869026711</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4902227790184651</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2600904188681301</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2496868021134049</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06800465386852816</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5288904567085696</v>
+        <v>0.5284225786984257</v>
       </c>
       <c r="R7" t="n">
-        <v>0.264687169148089</v>
+        <v>0.2662849222737163</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2064223741433413</v>
+        <v>0.2052924990278578</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.03866767769010454</v>
+        <v>0.07152106209255127</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03866767769010454</v>
+        <v>0.07152106209255127</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5288904567085696</v>
+        <v>0.5284225786984257</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.774346652716205</v>
+        <v>8.748194707248672</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.774346652716205</v>
+        <v>8.748194707248672</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1260273972602739</v>
+        <v>0.1350755982777611</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1890410958904109</v>
+        <v>0.1990587764093321</v>
       </c>
       <c r="N8" t="n">
-        <v>0.684931506849315</v>
+        <v>0.6658656253129068</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05797101449275388</v>
+        <v>0.05760881075929269</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2729219326125357</v>
+        <v>0.2650283800996614</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3525309327803374</v>
+        <v>0.3502749481669983</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3745471346071269</v>
+        <v>0.3846966717333406</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.3103843722421881</v>
+        <v>-0.2811689535795662</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3103843722421881</v>
+        <v>-0.2811689535795662</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3745471346071269</v>
+        <v>0.3846966717333406</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.284546580359447</v>
+        <v>1.509609527342126</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.284546580359447</v>
+        <v>1.509609527342126</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5714914533049666</v>
+        <v>0.5879059350503919</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2299904629154134</v>
+        <v>0.2239641657334826</v>
       </c>
       <c r="N9" t="n">
-        <v>0.19851808377962</v>
+        <v>0.1881298992161254</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06048936087446988</v>
+        <v>0.06309523809523809</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5511760864714842</v>
+        <v>0.5557722828627591</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2957071990772793</v>
+        <v>0.2935787473574423</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1531167144512364</v>
+        <v>0.1506489697797985</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02031536683348245</v>
+        <v>-0.03213365218763276</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02031536683348245</v>
+        <v>-0.03213365218763276</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5511760864714842</v>
+        <v>0.5557722828627591</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.400986495855554</v>
+        <v>7.635538383811432</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.400986495855554</v>
+        <v>7.635538383811432</v>
       </c>
     </row>
     <row r="10">
@@ -1402,53 +1402,53 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3935185185185184</v>
+        <v>0.3857280617164899</v>
       </c>
       <c r="M10" t="n">
-        <v>0.236111111111111</v>
+        <v>0.2362584378013501</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3780135004821601</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05882352941176494</v>
+        <v>0.05816326530612237</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1420404457482405</v>
+        <v>0.1496592658274537</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4408900048065116</v>
+        <v>0.4475438883580122</v>
       </c>
       <c r="S10" t="n">
-        <v>0.417069549445248</v>
+        <v>0.4027968458145341</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2047788936954005</v>
+        <v>0.2112854505566622</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2047788936954005</v>
+        <v>0.2112854505566622</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4408900048065116</v>
+        <v>0.4475438883580122</v>
       </c>
       <c r="Z10" t="n">
         <v>4</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.011725521285936</v>
+        <v>7.984117541115475</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.011725521285936</v>
+        <v>7.984117541115475</v>
       </c>
     </row>
     <row r="11">
@@ -1501,53 +1501,53 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2414486921529175</v>
+        <v>0.2522368981678739</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2354124748490946</v>
+        <v>0.2364720920323818</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5231388329979879</v>
+        <v>0.5112910097997444</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06196581196581197</v>
+        <v>0.05720720720720696</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3338456535702459</v>
+        <v>0.3329908007186286</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4377967811533599</v>
+        <v>0.4435746912911929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.228357565276394</v>
+        <v>0.2234345079901784</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2023843063042653</v>
+        <v>0.2071025992588111</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2023843063042653</v>
+        <v>0.2071025992588111</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4377967811533599</v>
+        <v>0.4435746912911929</v>
       </c>
       <c r="Z11" t="n">
         <v>4</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.980255008284473</v>
+        <v>7.926239923267577</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.980255008284473</v>
+        <v>7.926239923267577</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="n">
         <v>5.25</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7044320516583504</v>
+        <v>0.6942607775720708</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1784561197534488</v>
+        <v>0.1798466014281936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1171118285882008</v>
+        <v>0.1258926209997355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06735588972431072</v>
+        <v>0.05910364145658265</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6628477424400651</v>
+        <v>0.6163991002140746</v>
       </c>
       <c r="R2" t="n">
-        <v>0.23756277683258</v>
+        <v>0.2669066274600873</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09958948072735496</v>
+        <v>0.116694272325838</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.04158430921828538</v>
+        <v>-0.07786167735799621</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.04158430921828538</v>
+        <v>-0.07786167735799621</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6628477424400651</v>
+        <v>0.6163991002140746</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>9.059073400882111</v>
+        <v>7.852788015343426</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.059073400882111</v>
+        <v>7.852788015343426</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +715,47 @@
         <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5441860465116279</v>
+        <v>0.539701816903434</v>
       </c>
       <c r="M3" t="n">
-        <v>0.244186046511628</v>
+        <v>0.2421738922002589</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2116279069767442</v>
+        <v>0.2181242908963071</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05006105006104988</v>
+        <v>0.05878571005591793</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2695687867755708</v>
+        <v>0.2397687640438481</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4381085430417852</v>
+        <v>0.4655015758899603</v>
       </c>
       <c r="S3" t="n">
-        <v>0.292322670182644</v>
+        <v>0.2947296600661913</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1939224965301572</v>
+        <v>0.2233276836897014</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1939224965301572</v>
+        <v>0.2233276836897014</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4381085430417852</v>
+        <v>0.4655015758899603</v>
       </c>
       <c r="Z3" t="n">
         <v>3.9</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.84653422104285</v>
+        <v>8.245971049245494</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.84653422104285</v>
+        <v>8.245971049245494</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3368721927317272</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2858309514087382</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3772968558595345</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06017316017316032</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3937602166575641</v>
+        <v>0.3745906830557912</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3135591315478707</v>
+        <v>0.3118302927967421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.292680651794565</v>
+        <v>0.3135790241474666</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.05688802392583692</v>
+        <v>0.04374629509805034</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05688802392583692</v>
+        <v>0.04374629509805034</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3937602166575641</v>
+        <v>0.3745906830557912</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.571214835955183</v>
+        <v>6.100061887991398</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.571214835955183</v>
+        <v>6.100061887991398</v>
       </c>
     </row>
     <row r="5">
@@ -910,53 +910,53 @@
         <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>2.35</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3212510356255179</v>
+        <v>0.3265184597062326</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2823115161557581</v>
+        <v>0.2705438666137356</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3964374482187241</v>
+        <v>0.4029376736800317</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07338980413081653</v>
+        <v>0.05607378681479935</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2838073991274223</v>
+        <v>0.3422109501943484</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4200644398565816</v>
+        <v>0.3722065463082159</v>
       </c>
       <c r="S5" t="n">
-        <v>0.296128161015996</v>
+        <v>0.2855825034974356</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1377529237008235</v>
+        <v>0.1016626796944803</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1377529237008235</v>
+        <v>0.1016626796944803</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4200644398565816</v>
+        <v>0.3722065463082159</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.583420626282964</v>
+        <v>6.885571457504543</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.583420626282964</v>
+        <v>6.885571457504543</v>
       </c>
     </row>
     <row r="6">
@@ -1009,53 +1009,53 @@
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>1.73</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2089704059251724</v>
+        <v>0.210304843837666</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2474649543850726</v>
+        <v>0.2426594351973069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.543564639689755</v>
+        <v>0.5470357209650272</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06341479903998914</v>
+        <v>0.0566671607134035</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2646078634996389</v>
+        <v>0.4197518560377545</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3891742873764772</v>
+        <v>0.2740125834579001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3462178491238836</v>
+        <v>0.3062355605043455</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1417093329914046</v>
+        <v>0.2094470122000885</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1417093329914046</v>
+        <v>0.2094470122000885</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3891742873764772</v>
+        <v>0.4197518560377545</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.132989869026711</v>
+        <v>7.57886262462496</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.132989869026711</v>
+        <v>7.57886262462496</v>
       </c>
     </row>
     <row r="7">
@@ -1108,50 +1108,50 @@
         <v>2.05</v>
       </c>
       <c r="J7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.5</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5284225786984257</v>
+        <v>0.5144347736576399</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2662849222737163</v>
+        <v>0.2801183045599838</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2052924990278578</v>
+        <v>0.2054469217823763</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.07152106209255127</v>
+        <v>0.05043182760718884</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07152106209255127</v>
+        <v>0.05043182760718884</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5284225786984257</v>
+        <v>0.5144347736576399</v>
       </c>
       <c r="Z7" t="n">
         <v>2.05</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>8.748194707248672</v>
+        <v>8.236712043437064</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.748194707248672</v>
+        <v>8.236712043437064</v>
       </c>
     </row>
     <row r="8">
@@ -1207,53 +1207,53 @@
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1350755982777611</v>
+        <v>0.1361434977578475</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1990587764093321</v>
+        <v>0.1732735426008968</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6658656253129068</v>
+        <v>0.6905829596412556</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05760881075929269</v>
+        <v>0.04931300583474507</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2650283800996614</v>
+        <v>0.2405927808084823</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3502749481669983</v>
+        <v>0.3822913669338626</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3846966717333406</v>
+        <v>0.3771158522576549</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.2811689535795662</v>
+        <v>0.2090178243329657</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2811689535795662</v>
+        <v>0.2090178243329657</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3846966717333406</v>
+        <v>0.3822913669338626</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.509609527342126</v>
+        <v>7.032625227929575</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.509609527342126</v>
+        <v>7.032625227929575</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5879059350503919</v>
+        <v>0.5888816959792844</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2239641657334826</v>
+        <v>0.2203206345234275</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1881298992161254</v>
+        <v>0.1907976694972882</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06309523809523809</v>
+        <v>0.0482308328343739</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5557722828627591</v>
+        <v>0.5550193491993652</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2935787473574423</v>
+        <v>0.2950473748303297</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1506489697797985</v>
+        <v>0.1499332759703048</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.03213365218763276</v>
+        <v>-0.03386234677991917</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.03213365218763276</v>
+        <v>-0.03386234677991917</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5557722828627591</v>
+        <v>0.5550193491993652</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.635538383811432</v>
+        <v>7.599352039469022</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.635538383811432</v>
+        <v>7.599352039469022</v>
       </c>
     </row>
     <row r="10">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -1411,44 +1411,44 @@
         <v>2.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3857280617164899</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2362584378013501</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3780135004821601</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05816326530612237</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1496592658274537</v>
+        <v>0.1410078808304249</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4475438883580122</v>
+        <v>0.4347808303596482</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4027968458145341</v>
+        <v>0.4242112888099266</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2112854505566622</v>
+        <v>0.1966855922644101</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2112854505566622</v>
+        <v>0.1966855922644101</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4475438883580122</v>
+        <v>0.4347808303596482</v>
       </c>
       <c r="Z10" t="n">
         <v>4</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>7.984117541115475</v>
+        <v>7.798010532326465</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.984117541115475</v>
+        <v>7.798010532326465</v>
       </c>
     </row>
     <row r="11">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
         <v>1.85</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2522368981678739</v>
+        <v>0.2576687116564417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2364720920323818</v>
+        <v>0.2269938650306749</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5112910097997444</v>
+        <v>0.5153374233128835</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05720720720720696</v>
+        <v>0.04890604890604866</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3329908007186286</v>
+        <v>0.3276785143971981</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4435746912911929</v>
+        <v>0.4289925548951946</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2234345079901784</v>
+        <v>0.2433289307076072</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2071025992588111</v>
+        <v>0.2019986898645197</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2071025992588111</v>
+        <v>0.2019986898645197</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4435746912911929</v>
+        <v>0.4289925548951946</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,10 +1558,802 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>7.926239923267577</v>
+        <v>7.71360766955844</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.926239923267577</v>
+        <v>7.71360766955844</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2546157729465405</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3710500625143644</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.374334164539095</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1476670410064144</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1476670410064144</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.374334164539095</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.305190680547172</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.305190680547172</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6866642573183954</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1966028189374774</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1167329237441272</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07082043343653233</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3545506353334584</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4686505586189422</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1767988060475996</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2720477396814647</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2720477396814647</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4686505586189422</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.291888552440589</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.291888552440589</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5967984457957977</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2402496307434366</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1629519234607656</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06726597504775311</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5336530787501176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2644190970481768</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2019278242017057</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.06314536704568008</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.06314536704568008</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5336530787501176</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.860799570815868</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.860799570815868</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3739565943238731</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2921535893155259</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.333889816360601</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06964285714285712</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4710277044786925</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2474972523761889</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2814750431451186</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.0970711101548194</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0970711101548194</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4710277044786925</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.283843190368357</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.283843190368357</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7700592353257942</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1445341949380722</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.08540656973613354</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0644273759027858</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6549696850061787</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2246064160078307</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1204238989859904</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1150895503196155</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1150895503196155</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6549696850061787</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.872367028654276</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.872367028654276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7841087297438578</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.123366440146367</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.09252483010977522</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.08079096045197742</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5933602491455227</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2377481209950953</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1688916298593821</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1907484805983352</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1907484805983352</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5933602491455227</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.870761690276266</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.870761690276266</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.629537369997383</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2151767454032626</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1552858845993545</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.07328922455943232</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5736786495404097</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3034338078605047</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1228875425990855</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.05585872045697327</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.05585872045697327</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5736786495404097</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.550691856560356</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.550691856560356</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.336389635295347</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4158726077244334</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2477377569802196</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1546785778736871</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1546785778736871</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4158726077244334</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.522296611994244</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.522296611994244</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5918858330143802</v>
+        <v>0.2075820469581009</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2187107004210181</v>
+        <v>0.2524646517057984</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1894034665646017</v>
+        <v>0.5399533013361008</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0559468822170901</v>
+        <v>0.07052717457341728</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.479925443109475</v>
+        <v>0.05560597576932098</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3520600711049651</v>
+        <v>0.2268268024708799</v>
       </c>
       <c r="S2" t="n">
-        <v>0.16801448578556</v>
+        <v>0.7175672217597991</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1119603899049053</v>
+        <v>0.1776139204236984</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1119603899049053</v>
+        <v>0.1776139204236984</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.479925443109475</v>
+        <v>0.7175672217597991</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.043925502908963</v>
+        <v>8.985040589109454</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.043925502908963</v>
+        <v>8.985040589109454</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.55</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3838193791157102</v>
+        <v>0.6866642573183954</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2398871119473189</v>
+        <v>0.1966028189374774</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3762935089369708</v>
+        <v>0.1167329237441272</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04215686274509811</v>
+        <v>0.07082043343653233</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1551421882762828</v>
+        <v>0.451699592286615</v>
       </c>
       <c r="R3" t="n">
-        <v>0.346044550569588</v>
+        <v>0.3731589851943989</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4988132611541293</v>
+        <v>0.1751414225189862</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1225197522171584</v>
+        <v>-0.2349646650317804</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1225197522171584</v>
+        <v>-0.2349646650317804</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4988132611541293</v>
+        <v>0.451699592286615</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.580940763727926</v>
+        <v>2.381910706095444</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.580940763727926</v>
+        <v>2.381910706095444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,67 +808,760 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2536759245507204</v>
+        <v>0.5878322828172102</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2264963612060003</v>
+        <v>0.2411619621814196</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5198277142432793</v>
+        <v>0.1710057550013702</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05120999219359867</v>
+        <v>0.06322843822843827</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2927306652526654</v>
+        <v>0.4363069180470675</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3489646874610516</v>
+        <v>0.4085451754263297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.358304647286283</v>
+        <v>0.1551479065266028</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1615230669569964</v>
+        <v>-0.1515253647701427</v>
       </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1515253647701427</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4363069180470675</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.129741196956368</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.129741196956368</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3739565943238731</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2921535893155259</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.333889816360601</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06964285714285712</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="X4" t="n">
-        <v>-0.1615230669569964</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.358304647286283</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0.2238881585576396</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3877088490258642</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3884029924164961</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.05451317605589512</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05451317605589512</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3884029924164961</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>2.162623989061057</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.162623989061057</v>
+      <c r="AB5" t="n">
+        <v>4.867636134838203</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.867636134838203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7755791985681615</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1455702495774088</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07885055185442974</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05685161832702823</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7246698241864312</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2358725665321518</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03945760928141705</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.05090937438173027</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.05090937438173027</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.7246698241864312</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.404608242244911</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.404608242244911</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7969570729940229</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1175511682666183</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08549175873935881</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06336671802773508</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5864276947950272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3484494216273408</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.065122883577632</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.2105293781989956</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.2105293781989956</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5864276947950272</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.131111842673111</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.131111842673111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6253722453841571</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.220369267421084</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1542584871947588</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08043758043758054</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6183617614959116</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2777173132762904</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.103920925227798</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.007010483888245544</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.007010483888245544</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6183617614959116</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.718733209099529</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.718733209099529</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2618399564507349</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2547632008709852</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4833968426782798</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06086856086856107</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1395859575540654</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4045739451383095</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.455840097307625</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.02755674537065478</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.02755674537065478</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.455840097307625</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.706821895954275</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.706821895954275</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2406061042326519</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2681039447163835</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4912899510509645</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06568475154862607</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2863278608168799</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2915906923464772</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4220814468366429</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.06920850421432156</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.06920850421432156</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4220814468366429</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.878063635471388</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.878063635471388</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06442577030812324</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1746719819048206</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4380454543529845</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3872825637421948</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1617296648793002</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1617296648793002</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4380454543529845</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.913104289750668</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.913104289750668</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,53 +613,53 @@
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2075820469581009</v>
+        <v>0.2063106796116505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2524646517057984</v>
+        <v>0.2475728155339806</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5399533013361008</v>
+        <v>0.546116504854369</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07052717457341728</v>
+        <v>0.0771241830065359</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05560597576932098</v>
+        <v>0.09590594157817675</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2268268024708799</v>
+        <v>0.2013100351146803</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7175672217597991</v>
+        <v>0.7027840233071428</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1776139204236984</v>
+        <v>0.1566675184527738</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1776139204236984</v>
+        <v>0.1566675184527738</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7175672217597991</v>
+        <v>0.7027840233071428</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.985040589109454</v>
+        <v>7.211290622450806</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.985040589109454</v>
+        <v>7.211290622450806</v>
       </c>
     </row>
     <row r="3">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
         <v>4.75</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6866642573183954</v>
+        <v>0.6961506961506961</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1966028189374774</v>
+        <v>0.1949221949221949</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1167329237441272</v>
+        <v>0.1089271089271089</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07082043343653233</v>
+        <v>0.08005307386112337</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.451699592286615</v>
+        <v>0.4898857084578994</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3731589851943989</v>
+        <v>0.3033998193437803</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1751414225189862</v>
+        <v>0.2067144721983203</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2349646650317804</v>
+        <v>-0.2062649876927968</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2349646650317804</v>
+        <v>-0.2062649876927968</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.451699592286615</v>
+        <v>0.4898857084578994</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.381910706095444</v>
+        <v>2.54772315418092</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.381910706095444</v>
+        <v>2.54772315418092</v>
       </c>
     </row>
     <row r="4">
@@ -829,35 +829,35 @@
         <v>0.06322843822843827</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4363069180470675</v>
+        <v>0.3973652619394932</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4085451754263297</v>
+        <v>0.4461028893086317</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1551479065266028</v>
+        <v>0.1565318487518751</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1515253647701427</v>
+        <v>0.2049409271272122</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1515253647701427</v>
+        <v>0.2049409271272122</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4363069180470675</v>
+        <v>0.4461028893086317</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.129741196956368</v>
+        <v>4.905561807696712</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.129741196956368</v>
+        <v>4.905561807696712</v>
       </c>
     </row>
     <row r="5">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3739565943238731</v>
+        <v>0.3959390862944163</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2921535893155259</v>
+        <v>0.2899492385786802</v>
       </c>
       <c r="N5" t="n">
-        <v>0.333889816360601</v>
+        <v>0.3141116751269035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06964285714285712</v>
+        <v>0.06119370825253179</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2238881585576396</v>
+        <v>0.2011790054413466</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3877088490258642</v>
+        <v>0.3135190302220439</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3884029924164961</v>
+        <v>0.4853019643366095</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.05451317605589512</v>
+        <v>0.171190289209706</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05451317605589512</v>
+        <v>0.171190289209706</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3884029924164961</v>
+        <v>0.4853019643366095</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.867636134838203</v>
+        <v>5.257681324218095</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.867636134838203</v>
+        <v>5.257681324218095</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7246698241864312</v>
+        <v>0.7437511028209046</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2358725665321518</v>
+        <v>0.2048589002921467</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03945760928141705</v>
+        <v>0.05138999688694862</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.05090937438173027</v>
+        <v>-0.03182809574725687</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.05090937438173027</v>
+        <v>-0.03182809574725687</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7246698241864312</v>
+        <v>0.7437511028209046</v>
       </c>
       <c r="Z6" t="n">
         <v>1.22</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.404608242244911</v>
+        <v>6.395099498452482</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.404608242244911</v>
+        <v>6.395099498452482</v>
       </c>
     </row>
     <row r="7">
@@ -1129,29 +1129,29 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5864276947950272</v>
+        <v>0.7578527909849696</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3484494216273408</v>
+        <v>0.1759939888099082</v>
       </c>
       <c r="S7" t="n">
-        <v>0.065122883577632</v>
+        <v>0.0661532202051222</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.2105293781989956</v>
+        <v>-0.03910428200905325</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2105293781989956</v>
+        <v>-0.03910428200905325</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5864276947950272</v>
+        <v>0.7578527909849696</v>
       </c>
       <c r="Z7" t="n">
         <v>1.18</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.131111842673111</v>
+        <v>6.456411976569051</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.131111842673111</v>
+        <v>6.456411976569051</v>
       </c>
     </row>
     <row r="8">
@@ -1228,29 +1228,29 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6183617614959116</v>
+        <v>0.4901890948818928</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2777173132762904</v>
+        <v>0.3509674704577015</v>
       </c>
       <c r="S8" t="n">
-        <v>0.103920925227798</v>
+        <v>0.1588434346604057</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.007010483888245544</v>
+        <v>-0.1351831505022644</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.007010483888245544</v>
+        <v>-0.1351831505022644</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6183617614959116</v>
+        <v>0.4901890948818928</v>
       </c>
       <c r="Z8" t="n">
         <v>1.48</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.718733209099529</v>
+        <v>3.188966102081529</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.718733209099529</v>
+        <v>3.188966102081529</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1395859575540654</v>
+        <v>0.1304845598761571</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4045739451383095</v>
+        <v>0.367134948145229</v>
       </c>
       <c r="S9" t="n">
-        <v>0.455840097307625</v>
+        <v>0.5023804919786139</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02755674537065478</v>
+        <v>0.01898364930033414</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02755674537065478</v>
+        <v>0.01898364930033414</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.455840097307625</v>
+        <v>0.5023804919786139</v>
       </c>
       <c r="Z9" t="n">
         <v>1.95</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.706821895954275</v>
+        <v>4.683337278435774</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.706821895954275</v>
+        <v>4.683337278435774</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2406061042326519</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2681039447163835</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4912899510509645</v>
+        <v>0.4276704769412692</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06568475154862607</v>
+        <v>0.06284038542103065</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2863278608168799</v>
+        <v>0.2171091815023194</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2915906923464772</v>
+        <v>0.3855349734078036</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4220814468366429</v>
+        <v>0.3973558450898771</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.06920850421432156</v>
+        <v>-0.0303146318513921</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.06920850421432156</v>
+        <v>-0.0303146318513921</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4220814468366429</v>
+        <v>0.3973558450898771</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.878063635471388</v>
+        <v>3.297077149313147</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.878063635471388</v>
+        <v>3.297077149313147</v>
       </c>
     </row>
     <row r="11">
@@ -1525,29 +1525,29 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1746719819048206</v>
+        <v>0.232445401436955</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4380454543529845</v>
+        <v>0.5234441864834976</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3872825637421948</v>
+        <v>0.2441104120795475</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1617296648793002</v>
+        <v>0.2471283970098133</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1617296648793002</v>
+        <v>0.2471283970098133</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4380454543529845</v>
+        <v>0.5234441864834976</v>
       </c>
       <c r="Z11" t="n">
         <v>3.4</v>
@@ -1558,10 +1558,1000 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.913104289750668</v>
+        <v>5.600307286994703</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.913104289750668</v>
+        <v>5.600307286994703</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.313989239046887</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2478862413528055</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4381245196003075</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0616075071399429</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2200195519464885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3199551399459578</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4600253081075536</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.02190078850724614</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.02190078850724614</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4600253081075536</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.329071132875527</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.329071132875527</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06280193236714959</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4458687251002932</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.398612760081293</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1555185148184138</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1814040021724341</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1814040021724341</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4458687251002932</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.375647647498159</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.375647647498159</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2123502124746074</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.395115799990801</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3925339875345916</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1319579052539589</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1319579052539589</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.395115799990801</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.447552295313753</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.447552295313753</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3937947494033414</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2625298329355609</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3436754176610979</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05808080808080796</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.317254084792287</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.296813590934868</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.385932324272845</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.04225690661174708</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.04225690661174708</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.385932324272845</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.846360784052499</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.846360784052499</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1782437745740498</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1336828309305373</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7486890388678413</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1847375400650916</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.0665734210670671</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.0606156443724285</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0606156443724285</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7486890388678413</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.269864750065151</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.269864750065151</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3900705275442326</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3457678644020001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2641616080537674</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.07025290231661729</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.07025290231661729</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3900705275442326</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.872874614765478</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.872874614765478</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6334721412704321</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2165216556767297</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1500062030528383</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06662255789276572</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6307400795162977</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2770662688436109</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.09219365164009152</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.002732061754134318</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.002732061754134318</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6307400795162977</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.64130351106841</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.64130351106841</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3485612577870068</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2509641056066449</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4004746366063483</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06256895193065404</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1875647844074269</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.298961152926921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.513474062665652</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1129994260593037</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1129994260593037</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.513474062665652</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.510747133447906</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.510747133447906</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5704256252742431</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2413339183852567</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1882404563405002</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06247086247086253</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.336362116536787</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3182327499021554</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3454051335610576</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1571646772205574</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1571646772205574</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.3454051335610576</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.00100870170335</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.00100870170335</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4931506849315069</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2602739726027398</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2465753424657534</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06725146198830401</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3505825022226306</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2863265081547461</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3630909896226233</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1165156471568698</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.1165156471568698</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3630909896226233</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.159878141383253</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.159878141383253</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45556.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -613,53 +613,53 @@
         <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.297096053611318</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2501861504095309</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.4527177959791511</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.05184837092731831</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2340446263039808</v>
+        <v>0.239674966912956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4078079258876711</v>
+        <v>0.369734667594138</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3581474478083481</v>
+        <v>0.390590365492906</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1364123977458053</v>
+        <v>-0.06212743048624514</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1364123977458053</v>
+        <v>-0.06212743048624514</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4078079258876711</v>
+        <v>0.390590365492906</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.561563792555579</v>
+        <v>2.658535924198337</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.561563792555579</v>
+        <v>2.658535924198337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>wolves</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>newcastle</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,67 +709,1849 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.245554830894029</v>
+        <v>0.4579955865915901</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5286363546220297</v>
+        <v>0.3442474133077784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2258088144839412</v>
+        <v>0.1977570001006316</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2654784598851876</v>
+        <v>-0.1397840888994433</v>
       </c>
       <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.1397840888994433</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4579955865915901</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.575562134858147</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.575562134858147</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>481</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3165610142630745</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2793185419968304</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4041204437400951</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05298289528577382</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1870390370801672</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3660151960612215</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4469457668586114</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.04282532311851633</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04282532311851633</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4469457668586114</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.964142977994048</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.964142977994048</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3932584269662922</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2696629213483146</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3370786516853932</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3345235758401949</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2983237294795029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3671526946803023</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.03007404299490901</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03007404299490901</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3671526946803023</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.21510112591621</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.21510112591621</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.730136005726557</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1581961345740873</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1116678596993558</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05354449472096512</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7721449180919745</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1506850112758456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.07717007063217994</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.04200891236541748</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.04200891236541748</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.7721449180919745</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.589654342736619</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.589654342736619</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.2654784598851876</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.5286363546220297</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="Q7" t="n">
+        <v>0.3609177081085149</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3711652624776265</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2679170294138585</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1024677424620046</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1024677424620046</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3711652624776265</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.813549850017955</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.813549850017955</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6303499679729809</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2183660397135038</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1512839923135154</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05761354888375658</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6116191339900605</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2744934018931671</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1138874641167725</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.01873083398292041</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.01873083398292041</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6116191339900605</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.798760154091356</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.798760154091356</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3543534856812265</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2551345096904831</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3905120046282904</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04520030234315953</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2030939005831883</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3158412636864135</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4810648357303983</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.09055283110210793</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.09055283110210793</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4810648357303983</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.62659843841996</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.62659843841996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5392195506503745</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2621206148994876</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.198659834450138</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05973266499582275</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3381706629455596</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.324115841522644</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3377134955317965</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.2010488877048149</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.2010488877048149</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3381706629455596</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>5.646947768519657</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.646947768519657</v>
+      <c r="AB10" t="n">
+        <v>1.109845667852835</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.109845667852835</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3965827546443815</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3171850825917799</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2862321627638386</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.1297330348293027</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1297330348293027</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3965827546443815</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.159846639853782</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.159846639853782</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1982507288629737</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2478134110787172</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5539358600583091</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0619195046439629</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1237496109224775</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4149995530464007</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4612508360311219</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.0926850240271872</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0926850240271872</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4612508360311219</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.983123351875062</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.983123351875062</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.820304960432349</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.124686353985717</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.05500868558193399</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06934984520123844</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7144360330189207</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2422484344084087</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.04331553257267067</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1058689274134283</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1058689274134283</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7144360330189207</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.925662350623504</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.925662350623504</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.417910447761194</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3014163227240694</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3569772150547542</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3416064622211764</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.08832049863684371</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.08832049863684371</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3569772150547542</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.604181302187084</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.604181302187084</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5239520958083832</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2514970059880239</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2245508982035928</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06031746031746033</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4523054312035968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.420170788106802</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1275237806896011</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.07164666460478636</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.07164666460478636</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4523054312035968</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.081002140602091</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.081002140602091</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06334841628959276</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2057095063396061</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4693720847819884</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3249184088784055</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1927763401011373</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1927763401011373</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4693720847819884</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.608422991768984</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.608422991768984</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.418835684482416</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2771706735545401</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3039936419630439</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06114273666455827</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2689635374730732</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4948047510515651</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2362317114753615</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2176340774970251</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2176340774970251</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4948047510515651</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.814271657538368</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.814271657538368</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1338028169014084</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1971830985915493</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6690140845070423</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06766917293233088</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.09157263196774297</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3920088822611182</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5164184857711388</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.1525955987359034</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1525955987359034</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5164184857711388</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.94473473912395</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.94473473912395</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2219477769936486</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2741707833450953</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5038814396612561</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07275342569460208</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1456265037012017</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2542107804293871</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6001627158694112</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.09628127620815508</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.09628127620815508</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.6001627158694112</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.636926346325088</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.636926346325088</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3780697200814599</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.262548416723236</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3593818631953041</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.05800591465990701</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2926145718784502</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4464447623919321</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2609406657296175</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1838963456686961</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1838963456686961</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4464447623919321</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.422852250831638</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.422852250831638</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5668257756563246</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2461217183770883</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1870525059665871</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06921850079744818</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3449389445897823</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5318949179144392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1231661374957785</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.2857731995373509</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.2857731995373509</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5318949179144392</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.114474604447619</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.114474604447619</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.297096053611318</v>
+        <v>0.2799712849964106</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2501861504095309</v>
+        <v>0.2440775305096913</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4527177959791511</v>
+        <v>0.4759511844938981</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05184837092731831</v>
+        <v>0.05052790346907998</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.239674966912956</v>
+        <v>0.2594390134222618</v>
       </c>
       <c r="R2" t="n">
-        <v>0.369734667594138</v>
+        <v>0.3677793633505436</v>
       </c>
       <c r="S2" t="n">
-        <v>0.390590365492906</v>
+        <v>0.3727816232271945</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.06212743048624514</v>
+        <v>-0.1031695612667035</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.06212743048624514</v>
+        <v>-0.1031695612667035</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.390590365492906</v>
+        <v>0.3727816232271945</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.658535924198337</v>
+        <v>2.182204674949452</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.658535924198337</v>
+        <v>2.182204674949452</v>
       </c>
     </row>
     <row r="3">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K3" t="n">
         <v>5.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.6048853824355068</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2165294094168674</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.1785852081476258</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.06658436301586113</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4579955865915901</v>
+        <v>0.4325904807631163</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3442474133077784</v>
+        <v>0.3688302193269432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1977570001006316</v>
+        <v>0.1985792999099405</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1397840888994433</v>
+        <v>-0.1722949016723905</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1397840888994433</v>
+        <v>-0.1722949016723905</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4579955865915901</v>
+        <v>0.4325904807631163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.575562134858147</v>
+        <v>2.106798284283343</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.575562134858147</v>
+        <v>2.106798284283343</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.3422818791946309</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.2818791946308725</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.3758389261744967</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.04341736694677878</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1870390370801672</v>
+        <v>0.2118872969693765</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3660151960612215</v>
+        <v>0.3666103734672845</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4469457668586114</v>
+        <v>0.421502329563339</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.04282532311851633</v>
+        <v>0.04566340338884234</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04282532311851633</v>
+        <v>0.04566340338884234</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4469457668586114</v>
+        <v>0.421502329563339</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.964142977994048</v>
+        <v>3.78117818250219</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.964142977994048</v>
+        <v>3.78117818250219</v>
       </c>
     </row>
     <row r="5">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3932584269662922</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3370786516853932</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3345235758401949</v>
+        <v>0.3574813062872536</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2983237294795029</v>
+        <v>0.2872842849595075</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3671526946803023</v>
+        <v>0.3552344087532389</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.03007404299490901</v>
+        <v>-0.03142964772021328</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03007404299490901</v>
+        <v>-0.03142964772021328</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3671526946803023</v>
+        <v>0.3574813062872536</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.21510112591621</v>
+        <v>2.639019368889671</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.21510112591621</v>
+        <v>2.639019368889671</v>
       </c>
     </row>
     <row r="6">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="K6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>0.730136005726557</v>
+        <v>0.7408870888076656</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1581961345740873</v>
+        <v>0.1529190951299022</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1116678596993558</v>
+        <v>0.1061938160624321</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05354449472096512</v>
+        <v>0.04630490956072353</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7721449180919745</v>
+        <v>0.8098025866633201</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1506850112758456</v>
+        <v>0.1119148755081621</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07717007063217994</v>
+        <v>0.07828253782851795</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.04200891236541748</v>
+        <v>0.06891549785565443</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04200891236541748</v>
+        <v>0.06891549785565443</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7721449180919745</v>
+        <v>0.8098025866633201</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.589654342736619</v>
+        <v>7.112228948721628</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.589654342736619</v>
+        <v>7.112228948721628</v>
       </c>
     </row>
     <row r="7">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
@@ -1114,44 +1114,44 @@
         <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4374145674672915</v>
+        <v>0.4262607040913415</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2686975200156219</v>
+        <v>0.2740247383444339</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2938879125170865</v>
+        <v>0.2997145575642245</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06333056478405319</v>
+        <v>0.04265873015873023</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3609177081085149</v>
+        <v>0.3580884688101586</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3711652624776265</v>
+        <v>0.3726872028428803</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2679170294138585</v>
+        <v>0.2692243283469611</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1024677424620046</v>
+        <v>0.0986624644984464</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1024677424620046</v>
+        <v>0.0986624644984464</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3711652624776265</v>
+        <v>0.3726872028428803</v>
       </c>
       <c r="Z7" t="n">
         <v>3.5</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.813549850017955</v>
+        <v>3.815042398803509</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.813549850017955</v>
+        <v>3.815042398803509</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="J8" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6303499679729809</v>
+        <v>0.6149068322981366</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2183660397135038</v>
+        <v>0.2118012422360248</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1512839923135154</v>
+        <v>0.1732919254658385</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05761354888375658</v>
+        <v>0.04920169436298472</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6116191339900605</v>
+        <v>0.5936038742582015</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2744934018931671</v>
+        <v>0.3022785461784125</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1138874641167725</v>
+        <v>0.1041175795633861</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.01873083398292041</v>
+        <v>-0.02130295803993509</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01873083398292041</v>
+        <v>-0.02130295803993509</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6116191339900605</v>
+        <v>0.5936038742582015</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.798760154091356</v>
+        <v>4.632128569352977</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.798760154091356</v>
+        <v>4.632128569352977</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3543534856812265</v>
+        <v>0.3461313584096667</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2551345096904831</v>
+        <v>0.2572597934125901</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3905120046282904</v>
+        <v>0.3966088481777431</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04520030234315953</v>
+        <v>0.05057330057330067</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2030939005831883</v>
+        <v>0.2234133438274793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3158412636864135</v>
+        <v>0.2996595181782242</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4810648357303983</v>
+        <v>0.4769271379942966</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.09055283110210793</v>
+        <v>0.08031828981655353</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.09055283110210793</v>
+        <v>0.08031828981655353</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4810648357303983</v>
+        <v>0.4769271379942966</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.62659843841996</v>
+        <v>4.510271420427921</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.62659843841996</v>
+        <v>4.510271420427921</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>4.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.5496094879953717</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2502169511136824</v>
       </c>
       <c r="N10" t="n">
-        <v>0.198659834450138</v>
+        <v>0.2001735608909459</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.05171889260724072</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3381706629455596</v>
+        <v>0.33879162816969</v>
       </c>
       <c r="R10" t="n">
-        <v>0.324115841522644</v>
+        <v>0.3087007154691069</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3377134955317965</v>
+        <v>0.3525076563612032</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.2010488877048149</v>
+        <v>0.1523340954702573</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2010488877048149</v>
+        <v>0.1523340954702573</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3381706629455596</v>
+        <v>0.3525076563612032</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.109845667852835</v>
+        <v>3.662537632706287</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.109845667852835</v>
+        <v>3.662537632706287</v>
       </c>
     </row>
     <row r="11">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3965827546443815</v>
+        <v>0.4640880005977176</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3171850825917799</v>
+        <v>0.2653519561551284</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2862321627638386</v>
+        <v>0.2705600432471539</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.1297330348293027</v>
+        <v>-0.07513155005265693</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1297330348293027</v>
+        <v>-0.07513155005265693</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3965827546443815</v>
+        <v>0.4640880005977176</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,1000 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>2.159846639853782</v>
+        <v>3.148162506377616</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.159846639853782</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45563.35416666666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>newcastle</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>manchester city</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.1982507288629737</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2478134110787172</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.5539358600583091</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.0619195046439629</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.1237496109224775</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.4149995530464007</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.4612508360311219</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.0926850240271872</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.0926850240271872</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.4612508360311219</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.983123351875062</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.983123351875062</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>arsenal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>leicester</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" t="n">
-        <v>481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.820304960432349</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.124686353985717</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.05500868558193399</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06934984520123844</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.7144360330189207</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2422484344084087</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.04331553257267067</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.1058689274134283</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.1058689274134283</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.7144360330189207</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.925662350623504</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.925662350623504</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>brentford</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>west ham</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.417910447761194</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2686567164179104</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3134328358208955</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06349206349206349</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3014163227240694</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3569772150547542</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3416064622211764</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.08832049863684371</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.08832049863684371</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3569772150547542</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.604181302187084</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.604181302187084</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>brighton</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>48</v>
-      </c>
-      <c r="F15" t="n">
-        <v>481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5239520958083832</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2514970059880239</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2245508982035928</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06031746031746033</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.4523054312035968</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.420170788106802</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1275237806896011</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.07164666460478636</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.07164666460478636</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4523054312035968</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.081002140602091</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.081002140602091</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>everton</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>crystal palace</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F16" t="n">
-        <v>481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.3617021276595744</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2765957446808511</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.3617021276595744</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06334841628959276</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2057095063396061</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.4693720847819884</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.3249184088784055</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.1927763401011373</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.1927763401011373</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4693720847819884</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.608422991768984</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.608422991768984</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>fulham</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" t="n">
-        <v>481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.418835684482416</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2771706735545401</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.3039936419630439</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06114273666455827</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.2689635374730732</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.4948047510515651</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.2362317114753615</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.2176340774970251</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.2176340774970251</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.4948047510515651</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.814271657538368</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.814271657538368</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>wolves</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>liverpool</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>48</v>
-      </c>
-      <c r="F18" t="n">
-        <v>481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.1338028169014084</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.1971830985915493</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.6690140845070423</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06766917293233088</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.09157263196774297</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3920088822611182</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.5164184857711388</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>-0.1525955987359034</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.1525955987359034</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.5164184857711388</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.94473473912395</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.94473473912395</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ipswich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>aston villa</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>48</v>
-      </c>
-      <c r="F19" t="n">
-        <v>481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.2219477769936486</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2741707833450953</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.5038814396612561</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.07275342569460208</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1456265037012017</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2542107804293871</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.6001627158694112</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.09628127620815508</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.09628127620815508</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.6001627158694112</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.636926346325088</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.636926346325088</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>48</v>
-      </c>
-      <c r="F20" t="n">
-        <v>481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.3780697200814599</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.262548416723236</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.3593818631953041</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.05800591465990701</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.2926145718784502</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.4464447623919321</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.2609406657296175</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>0.1838963456686961</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.1838963456686961</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.4464447623919321</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB20" t="n">
-        <v>4.422852250831638</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.422852250831638</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45565.66666666666</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>bournemouth</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>southampton</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>48</v>
-      </c>
-      <c r="F21" t="n">
-        <v>481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.5668257756563246</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2461217183770883</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.1870525059665871</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.06921850079744818</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.3449389445897823</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.5318949179144392</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1231661374957785</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>0.2857731995373509</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.2857731995373509</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.5318949179144392</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.114474604447619</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.114474604447619</v>
+        <v>3.148162506377616</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45563.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2346368715083799</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.06547619047619047</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2340446263039808</v>
+        <v>0.09458509658434557</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4078079258876711</v>
+        <v>0.3349333539573172</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3581474478083481</v>
+        <v>0.5704815494583373</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.1364123977458053</v>
+        <v>-0.01611062931261242</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1364123977458053</v>
+        <v>-0.01611062931261242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4078079258876711</v>
+        <v>0.5704815494583373</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +669,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.561563792555579</v>
+        <v>6.537192504423396</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.561563792555579</v>
+        <v>6.537192504423396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45563.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,67 +711,1887 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8031206975676917</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1342358880220285</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.06264341441027994</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06422466422466422</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6695099969525026</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2878860639301022</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.04260393911739525</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.1336107006151891</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.1336107006151891</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.6695099969525026</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.319373430015355</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.319373430015355</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>481</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4134419551934827</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2657841140529532</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3207739307535642</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07498631636562658</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1945047091784793</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.503781905666259</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3017133851552616</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2379977916133059</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.2379977916133059</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.503781905666259</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.940642226904513</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.940642226904513</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5533287619997507</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2294289988779454</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2172422391223039</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06308461535912735</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.485446602005489</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4292997610350112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.08525363695949989</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.06788215999426167</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.06788215999426167</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.485446602005489</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.923958023829948</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.923958023829948</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3565186997553303</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2757777001048585</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3677036001398113</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06650264668605077</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3018422215014211</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3877562041179587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3104015743806202</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1119785040131002</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1119785040131002</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3877562041179587</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.572456561100404</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.572456561100404</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4134954884268341</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2797175362887407</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3067869752844253</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05148090091576596</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2616808151980905</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4671359481771092</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2711832366248002</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1874184118883685</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1874184118883685</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4671359481771092</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.50850975041654</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.50850975041654</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1178918169209431</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.188626907073509</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6934812760055478</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06029411764705883</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.06721204327175043</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3292195839974335</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.6035683727308161</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.08991290327473167</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.08991290327473167</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6035683727308161</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.057072192570509</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.057072192570509</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2341530251676642</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2754741472560756</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4903728275762601</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06767785648290747</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2419640310755157</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3751775069423153</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.382858461982169</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1075143655940911</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.1075143655940911</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.382858461982169</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.246882723524215</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.246882723524215</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4107177782123997</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2519069039702718</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3373753178173283</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05859213250517614</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3287373858794205</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4260822950896866</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2451803190308928</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1741753911194148</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1741753911194148</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4260822950896866</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.024401325011126</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.024401325011126</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.578368999421631</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2342394447657606</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1873915558126084</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06728395061728398</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3961303563323148</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4345972002559619</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1692724434117232</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2003577554902014</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2003577554902014</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4345972002559619</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.124809864142686</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.124809864142686</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1773962804005723</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2217453505007153</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6008583690987125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07373271889400912</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1073945540654191</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3452346844954233</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5473707614391575</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.05348760765955496</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.05348760765955496</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5473707614391575</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.823915240901013</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.823915240901013</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8103727714748785</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.126418152350081</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.06320907617504051</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05470085470085473</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.708348736421995</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2578391777376444</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.03381208584036061</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1020240350528835</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1020240350528835</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.708348736421995</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.149836235989798</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.149836235989798</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4885133350937418</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2574597306575125</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2540269342487457</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.04975744975744978</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3449659598273141</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4391172893230524</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2159167508496334</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.18165755866554</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.18165755866554</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4391172893230524</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.178111167105949</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.178111167105949</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3027576765108547</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2607079992176805</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4365343242714649</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06547470200883554</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3580080241090116</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4439901544824147</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1980018214085738</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1832821552647342</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1832821552647342</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4439901544824147</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.235572437957738</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.235572437957738</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.794066317626527</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1338568935427574</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.07207678883071553</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06723784689886392</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6916419764286408</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2801869856356778</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.02817103793568125</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1024243411978862</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1024243411978862</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6916419764286408</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.948108150211153</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.948108150211153</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5391413189859399</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2454511794330726</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2154075015809875</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.07213945903485719</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.63708711445497</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.251457704084658</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.111455181460372</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.09794579546903015</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.09794579546903015</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.63708711445497</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.512589419706556</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.512589419706556</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.4736842105263158</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.05555555555555558</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="L18" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3402000128044111</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3022981141396776</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3575018730559113</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.112647380675432</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.112647380675432</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3575018730559113</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.887346529365766</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.887346529365766</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.371859296482412</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2562814070351758</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.371859296482412</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05458399576046657</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0.245554830894029</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5286363546220297</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2258088144839412</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>0.2654784598851876</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="Q19" t="n">
+        <v>0.2552304567751397</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4545763172681021</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2901932259567582</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1982949102329263</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.2654784598851876</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.5286363546220297</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="X19" t="n">
+        <v>0.1982949102329263</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4545763172681021</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>5.646947768519657</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.646947768519657</v>
+      <c r="AB19" t="n">
+        <v>5.360405436043227</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.360405436043227</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.621470932916652</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2263929827053518</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1521360843779964</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.05169000933706802</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5073932959169137</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3982288011415805</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.09437790294150582</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.1140776369997383</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1140776369997383</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5073932959169137</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.638014159670992</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.638014159670992</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3548821015983541</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2393179300522234</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4057999683494223</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.07142100198803814</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1041210585517342</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3323236315689546</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5635553098793111</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.1577553415298888</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.1577553415298888</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5635553098793111</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.645495666696628</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.645495666696628</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>KnvLwLo4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45563.35416666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1820259849450217</v>
+        <v>0.2372595342558219</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2207012519541257</v>
+        <v>0.249746878164023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5972727631008525</v>
+        <v>0.5129935875801553</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04642307269328061</v>
+        <v>0.05369843527738238</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08996758652343546</v>
+        <v>0.3080176867217602</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3633329085271265</v>
+        <v>0.3632057122376812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.546699504949438</v>
+        <v>0.3287766010405587</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.05057325815141456</v>
+        <v>0.1134588340736582</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05057325815141456</v>
+        <v>0.1134588340736582</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.546699504949438</v>
+        <v>0.3632057122376812</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.850365998568624</v>
+        <v>5.958107908843205</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.850365998568624</v>
+        <v>5.958107908843205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.45833333334</v>
+        <v>45564.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8168266285480907</v>
+        <v>0.4120836560805577</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1194608944251583</v>
+        <v>0.249419054996127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06371247702675106</v>
+        <v>0.3384972889233152</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04636752136752142</v>
+        <v>0.05508336057535157</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5955114349070181</v>
+        <v>0.307428380162004</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3493107699608392</v>
+        <v>0.4416943582415432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05517779513214271</v>
+        <v>0.2508772615964528</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2213151936410727</v>
+        <v>0.1922753032454162</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2213151936410727</v>
+        <v>0.1922753032454162</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5955114349070181</v>
+        <v>0.4416943582415432</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.412556241124856</v>
+        <v>7.245653249550787</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.412556241124856</v>
+        <v>7.245653249550787</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.45833333334</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2259887005649717</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.1807909604519774</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.0535714285714286</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1842370961237536</v>
+        <v>0.3851744143727539</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5019809705430481</v>
+        <v>0.4428213546885988</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3137819333331981</v>
+        <v>0.1720042309386473</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2305854424011823</v>
+        <v>0.2168326541236271</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2305854424011823</v>
+        <v>0.2168326541236271</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5019809705430481</v>
+        <v>0.4428213546885988</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,608 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.919405435506234</v>
+        <v>7.264140751862001</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.919405435506234</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>brighton</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" t="n">
-        <v>481</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5483028720626633</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.2258485639686684</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.2258485639686684</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.05422515827140106</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.5183309699812199</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.3949838438589283</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.08668518615985178</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>-0.0299719020814434</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.0299719020814434</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.5183309699812199</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>5.758774715857063</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.758774715857063</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>everton</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>crystal palace</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>48</v>
-      </c>
-      <c r="F6" t="n">
-        <v>481</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3515188335358444</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.287606318347509</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.3608748481166464</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.05362881028280286</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3027369787356111</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3818310254938334</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3154319957705554</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>0.0942247071463243</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.0942247071463243</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.3818310254938334</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>4.50258631379591</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.50258631379591</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>fulham</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>48</v>
-      </c>
-      <c r="F7" t="n">
-        <v>481</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3956834532374101</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2877697841726619</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.316546762589928</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.05303030303030298</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.2472205570352049</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.473994661990604</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2787847809741911</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.1862248778179421</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1862248778179421</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.473994661990604</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>5.589388329905842</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.589388329905842</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>wolves</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>liverpool</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>48</v>
-      </c>
-      <c r="F8" t="n">
-        <v>481</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.1269302562362125</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.1730867130493806</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.6999830307144069</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.05044563279857384</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.06724860389337818</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3290126864264664</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6037387096801553</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.09624432103425162</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.09624432103425162</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.6037387096801553</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>5.984420165150179</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.984420165150179</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ipswich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>aston villa</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>48</v>
-      </c>
-      <c r="F9" t="n">
-        <v>481</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2388718994223582</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2582398912674142</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.5028882093102277</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.04658605974395424</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3080176867217602</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3632057122376812</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3287766010405587</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.104965820970267</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.104965820970267</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.3632057122376812</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.282954919388263</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.282954919388263</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>48</v>
-      </c>
-      <c r="F10" t="n">
-        <v>481</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4146032477254405</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2542899919382701</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3311067603362892</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.04867149758454126</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.307428380162004</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4416943582415432</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2508772615964528</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>0.1874043663032731</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.1874043663032731</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4416943582415432</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>5.208500199079184</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.208500199079184</v>
+        <v>7.264140751862001</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2372595342558219</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M2" t="n">
-        <v>0.249746878164023</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5129935875801553</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05369843527738238</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3080176867217602</v>
+        <v>0.3061133325099945</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3632057122376812</v>
+        <v>0.1881647855043411</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3287766010405587</v>
+        <v>0.5057219266891479</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1134588340736582</v>
+        <v>-0.1329745647381257</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1134588340736582</v>
+        <v>-0.1329745647381257</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3632057122376812</v>
+        <v>0.5057219266891479</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.958107908843205</v>
+        <v>3.581373889463438</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.958107908843205</v>
+        <v>3.581373889463438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4120836560805577</v>
+        <v>0.8377135348226018</v>
       </c>
       <c r="M3" t="n">
-        <v>0.249419054996127</v>
+        <v>0.1061103810775295</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3384972889233152</v>
+        <v>0.05617608409986859</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05508336057535157</v>
+        <v>0.04712762297901629</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.307428380162004</v>
+        <v>0.1242063418030739</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4416943582415432</v>
+        <v>0.8154500126838684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2508772615964528</v>
+        <v>0.06034373492002487</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1922753032454162</v>
+        <v>-0.02226352213873339</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1922753032454162</v>
+        <v>-0.02226352213873339</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4416943582415432</v>
+        <v>0.8154500126838684</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.245653249550787</v>
+        <v>7.62097247810098</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.245653249550787</v>
+        <v>7.62097247810098</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,67 +808,1368 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2259887005649717</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1807909604519774</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0535714285714286</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3851744143727539</v>
+        <v>0.3120746612548828</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4428213546885988</v>
+        <v>0.3800264298915863</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1720042309386473</v>
+        <v>0.3078988194465637</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2168326541236271</v>
+        <v>-0.08029699996926359</v>
       </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.08029699996926359</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3800264298915863</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.879814222182516</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.879814222182516</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2897350993377484</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2549668874172186</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4552980132450331</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04588744588744587</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
-        <v>0.2168326541236271</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.4428213546885988</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0.371945708990097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2966949939727783</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3313592076301575</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1169788215728785</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1169788215728785</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.371945708990097</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>7.264140751862001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.264140751862001</v>
+      <c r="AB5" t="n">
+        <v>3.573671570746436</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.573671570746436</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.763271162123386</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1362984218077475</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1004304160688666</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04812030075187979</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1592103838920593</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7894311547279358</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.05135850235819817</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.02615999260454982</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.02615999260454982</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.7894311547279358</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.584891037922602</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.584891037922602</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5292717447246527</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2507076685537828</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2200205867215646</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04966033250948776</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.278355598449707</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4412356913089752</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2804087400436401</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.08803605341567744</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.08803605341567744</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4412356913089752</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.393558452830062</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.393558452830062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.417910447761194</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3107372224330902</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2813779413700104</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4078847467899323</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.01002570097126176</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.01002570097126176</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4078847467899323</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.822648109228065</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.822648109228065</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4310344827586207</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2528735632183908</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3160919540229885</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05454545454545445</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5972409248352051</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2755087912082672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1272503286600113</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3443673616168142</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3443673616168142</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5972409248352051</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.738318422237015</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.738318422237015</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6424335602899187</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2112892598286844</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1462771798813969</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05174405174405172</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2634107172489166</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5643032193183899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1722860336303711</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.07813034097152882</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.07813034097152882</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5643032193183899</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.671171495790536</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.671171495790536</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3286034353995519</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2382374906646751</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4331590739357729</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04937304075235116</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3413679897785187</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2127946466207504</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4458373486995697</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.01267827476379679</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.01267827476379679</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4458373486995697</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.283625861824469</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.283625861824469</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07936507936507931</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3592177331447601</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4991156458854675</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1416666209697723</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1185314129380619</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1185314129380619</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4991156458854675</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.656670908373605</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.656670908373605</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3684400320053101</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2222336232662201</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4093263745307922</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.0613935051079515</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0613935051079515</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4093263745307922</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.93282673374341</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.93282673374341</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4059040590405905</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2829028290282903</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3111931119311193</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.07114624505928857</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4324784576892853</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3284854590892792</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2390360683202744</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.149575628660995</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.149575628660995</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4324784576892853</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.155273019282537</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.155273019282537</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5918858330143802</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2187107004210181</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1894034665646017</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0559468822170901</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.322594165802002</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5304591059684753</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1469467580318451</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.06142672704590491</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.06142672704590491</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5304591059684753</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.506484784745258</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.506484784745258</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4664634146341464</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2591463414634146</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.274390243902439</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07189542483660127</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2503193616867065</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5716579556465149</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1780226528644562</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1051945410123685</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1051945410123685</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5716579556465149</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.492516071315585</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.492516071315585</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3997567403202919</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2763024528684371</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.323940806811271</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06447714815933714</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3887055218219757</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.253214955329895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3580794930458069</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1124030689535386</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1124030689535386</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3887055218219757</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.734700627408872</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.734700627408872</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45570.35416666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.25</v>
+        <v>2.15</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3061133325099945</v>
+        <v>0.4948056638240814</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1881647855043411</v>
+        <v>0.3227694630622864</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5057219266891479</v>
+        <v>0.1824248433113098</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1329745647381257</v>
+        <v>0.2393438010414061</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1329745647381257</v>
+        <v>0.2393438010414061</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5057219266891479</v>
+        <v>0.4948056638240814</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.581373889463438</v>
+        <v>6.701463016800957</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.581373889463438</v>
+        <v>6.701463016800957</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>6.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8377135348226018</v>
+        <v>0.6424335602899187</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1061103810775295</v>
+        <v>0.2112892598286844</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05617608409986859</v>
+        <v>0.1462771798813969</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04712762297901629</v>
+        <v>0.05174405174405172</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1242063418030739</v>
+        <v>0.263410747051239</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8154500126838684</v>
+        <v>0.5643032789230347</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06034373492002487</v>
+        <v>0.1722859889268875</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.02226352213873339</v>
+        <v>-0.07813028136688405</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.02226352213873339</v>
+        <v>-0.07813028136688405</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8154500126838684</v>
+        <v>0.5643032789230347</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.62097247810098</v>
+        <v>6.584545410636507</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.62097247810098</v>
+        <v>6.584545410636507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.3179297597042514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2384473197781886</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.4436229205175601</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.04844961240310064</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3120746612548828</v>
+        <v>0.3511871993541718</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3800264298915863</v>
+        <v>0.2138539254665375</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3078988194465637</v>
+        <v>0.4349587857723236</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.08029699996926359</v>
+        <v>-0.008664134745236529</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.08029699996926359</v>
+        <v>-0.008664134745236529</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3800264298915863</v>
+        <v>0.4349587857723236</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.879814222182516</v>
+        <v>5.773575459988618</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.879814222182516</v>
+        <v>5.773575459988618</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.35416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,58 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2897350993377484</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2549668874172186</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4552980132450331</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04588744588744587</v>
+        <v>0.07936507936507931</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.371945708990097</v>
+        <v>0.3594461381435394</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2966949939727783</v>
+        <v>0.4944868683815002</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3313592076301575</v>
+        <v>0.1460669487714767</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
-        <v>0.1169788215728785</v>
+        <v>-0.1231601904420292</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1169788215728785</v>
+        <v>-0.1231601904420292</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.371945708990097</v>
+        <v>0.4944868683815002</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +966,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.573671570746436</v>
+        <v>5.02910977237245</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.573671570746436</v>
+        <v>5.02910977237245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1008,58 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.25</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.763271162123386</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1362984218077475</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1004304160688666</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04812030075187979</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1592103838920593</v>
+        <v>0.360698938369751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7894311547279358</v>
+        <v>0.2233530133962631</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05135850235819817</v>
+        <v>0.4159480929374695</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
-        <v>0.02615999260454982</v>
+        <v>0.07479932668375799</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02615999260454982</v>
+        <v>0.07479932668375799</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7894311547279358</v>
+        <v>0.4159480929374695</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1067,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.584891037922602</v>
+        <v>5.633445543421199</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.584891037922602</v>
+        <v>5.633445543421199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,37 +1109,37 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5292717447246527</v>
+        <v>0.4059040590405905</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2507076685537828</v>
+        <v>0.2829028290282903</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2200205867215646</v>
+        <v>0.3111931119311193</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04966033250948776</v>
+        <v>0.07114624505928857</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.278355598449707</v>
+        <v>0.3838543593883514</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4412356913089752</v>
+        <v>0.3601999580860138</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2804087400436401</v>
+        <v>0.2559456825256348</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1144,19 +1148,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.08803605341567744</v>
+        <v>0.1009515303600612</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08803605341567744</v>
+        <v>0.1009515303600612</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4412356913089752</v>
+        <v>0.3838543593883514</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1164,29 +1168,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.393558452830062</v>
+        <v>5.198780008697359</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.393558452830062</v>
+        <v>5.198780008697359</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1206,56 +1210,58 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="K8" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.5860437947885057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.216551979598524</v>
       </c>
       <c r="N8" t="n">
-        <v>0.417910447761194</v>
+        <v>0.1974042256129703</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06647319800656382</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3107372224330902</v>
+        <v>0.3106180727481842</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2813779413700104</v>
+        <v>0.5455252528190613</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4078847467899323</v>
+        <v>0.1438566744327545</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>-0.01002570097126176</v>
+        <v>-0.04051854196944438</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01002570097126176</v>
+        <v>-0.04051854196944438</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4078847467899323</v>
+        <v>0.5455252528190613</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1263,29 +1269,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.822648109228065</v>
+        <v>6.839622185889568</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.822648109228065</v>
+        <v>6.839622185889568</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1305,56 +1311,58 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4310344827586207</v>
+        <v>0.4664634146341464</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2528735632183908</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3160919540229885</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05454545454545445</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5972409248352051</v>
+        <v>0.2445431053638458</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2755087912082672</v>
+        <v>0.5760452151298523</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1272503286600113</v>
+        <v>0.1794116646051407</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
       <c r="V9" t="n">
-        <v>0.3443673616168142</v>
+        <v>0.1095818004957059</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3443673616168142</v>
+        <v>0.1095818004957059</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5972409248352051</v>
+        <v>0.5760452151298523</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1362,29 +1370,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.738318422237015</v>
+        <v>7.801741142903182</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.738318422237015</v>
+        <v>7.801741142903182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1404,56 +1412,58 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6424335602899187</v>
+        <v>0.3997567403202919</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2112892598286844</v>
+        <v>0.2763024528684371</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1462771798813969</v>
+        <v>0.323940806811271</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05174405174405172</v>
+        <v>0.06447714815933714</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2634107172489166</v>
+        <v>0.4143766462802887</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5643032193183899</v>
+        <v>0.2349821478128433</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1722860336303711</v>
+        <v>0.3506411910057068</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
-        <v>-0.07813034097152882</v>
+        <v>0.1380741934118516</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.07813034097152882</v>
+        <v>0.1380741934118516</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5643032193183899</v>
+        <v>0.4143766462802887</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1461,29 +1471,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.671171495790536</v>
+        <v>5.612162457098814</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.671171495790536</v>
+        <v>5.612162457098814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1503,56 +1513,58 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3286034353995519</v>
+        <v>0.1785852081476258</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2382374906646751</v>
+        <v>0.2165294094168674</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4331590739357729</v>
+        <v>0.6048853824355068</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04937304075235116</v>
+        <v>0.06658436301586113</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3413679897785187</v>
+        <v>0.3628591895103455</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2127946466207504</v>
+        <v>0.1506211757659912</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4458373486995697</v>
+        <v>0.4865196645259857</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
       <c r="V11" t="n">
-        <v>0.01267827476379679</v>
+        <v>-0.1183657179095211</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01267827476379679</v>
+        <v>-0.1183657179095211</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4458373486995697</v>
+        <v>0.4865196645259857</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1560,29 +1572,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.283625861824469</v>
+        <v>4.986139484888165</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.283625861824469</v>
+        <v>4.986139484888165</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1602,37 +1614,37 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="K12" t="n">
-        <v>5.25</v>
+        <v>1.29</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.1179029722516726</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.1509158044821409</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.7311812232661865</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07936507936507931</v>
+        <v>0.06019379844961237</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3592177331447601</v>
+        <v>0.2923648655414581</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4991156458854675</v>
+        <v>0.198116809129715</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1416666209697723</v>
+        <v>0.5095183849334717</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1641,19 +1653,19 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1185314129380619</v>
+        <v>-0.2216628383327148</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1185314129380619</v>
+        <v>-0.2216628383327148</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4991156458854675</v>
+        <v>0.5095183849334717</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1661,29 +1673,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3.656670908373605</v>
+        <v>3.898607960178552</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.656670908373605</v>
+        <v>3.898607960178552</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1703,37 +1715,37 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.375767498976668</v>
+        <v>0.5879059350503919</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2239641657334826</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.1881298992161254</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.06309523809523809</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3684400320053101</v>
+        <v>0.3455632627010345</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2222336232662201</v>
+        <v>0.5473897457122803</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4093263745307922</v>
+        <v>0.1070470809936523</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1742,19 +1754,19 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0613935051079515</v>
+        <v>-0.04051618933811163</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0613935051079515</v>
+        <v>-0.04051618933811163</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4093263745307922</v>
+        <v>0.5473897457122803</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1762,414 +1774,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3.93282673374341</v>
+        <v>6.86490604408993</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.93282673374341</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ipswich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>everton</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.4059040590405905</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2829028290282903</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3111931119311193</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.07114624505928857</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.4324784576892853</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3284854590892792</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2390360683202744</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.149575628660995</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.149575628660995</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4324784576892853</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>4.155273019282537</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.155273019282537</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>brentford</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>48</v>
-      </c>
-      <c r="F15" t="n">
-        <v>481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5918858330143802</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2187107004210181</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1894034665646017</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.0559468822170901</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.322594165802002</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5304591059684753</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1469467580318451</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.06142672704590491</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.06142672704590491</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.5304591059684753</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.506484784745258</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.506484784745258</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>newcastle</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>brighton</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F16" t="n">
-        <v>481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4664634146341464</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2591463414634146</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.274390243902439</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.07189542483660127</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2503193616867065</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.5716579556465149</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.1780226528644562</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.1051945410123685</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.1051945410123685</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.5716579556465149</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.492516071315585</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.492516071315585</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>southampton</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>leicester</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" t="n">
-        <v>481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.3997567403202919</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2763024528684371</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.323940806811271</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06447714815933714</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3887055218219757</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.253214955329895</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3580794930458069</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.1124030689535386</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1124030689535386</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.3887055218219757</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.734700627408872</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.734700627408872</v>
+        <v>6.86490604408993</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_1</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
@@ -564,11 +564,6 @@
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +605,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.439632042928325</v>
+        <v>0.6306306306306306</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.1801801801801802</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.05714285714285716</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4948056638240814</v>
+        <v>0.4802414178848267</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3227694630622864</v>
+        <v>0.3722254633903503</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1824248433113098</v>
+        <v>0.1475331038236618</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.2393438010414061</v>
+        <v>-0.150389212745804</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2393438010414061</v>
+        <v>-0.150389212745804</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4948056638240814</v>
+        <v>0.4802414178848267</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +664,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.701463016800957</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6.701463016800957</v>
+        <v>4.997862501327692</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +703,58 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6424335602899187</v>
+        <v>0.4020260838352012</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2112892598286844</v>
+        <v>0.2699317991464922</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1462771798813969</v>
+        <v>0.3280421170183065</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05174405174405172</v>
+        <v>0.0584684228301251</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.263410747051239</v>
+        <v>0.2029433697462082</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5643032789230347</v>
+        <v>0.3414356410503387</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1722859889268875</v>
+        <v>0.4556211531162262</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>-0.07813028136688405</v>
+        <v>0.1275790360979197</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.07813028136688405</v>
+        <v>0.1275790360979197</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5643032789230347</v>
+        <v>0.4556211531162262</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +762,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.584545410636507</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.584545410636507</v>
+        <v>5.621898040553345</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +801,58 @@
         </is>
       </c>
       <c r="I4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.3179297597042514</v>
+        <v>0.3976861894432394</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2384473197781886</v>
+        <v>0.2868161002651242</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4436229205175601</v>
+        <v>0.3154977102916365</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04844961240310064</v>
+        <v>0.05653170359052706</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3511871993541718</v>
+        <v>0.3545161485671997</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2138539254665375</v>
+        <v>0.3959226608276367</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4349587857723236</v>
+        <v>0.24956114590168</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
-        <v>-0.008664134745236529</v>
+        <v>0.1091065605625126</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.008664134745236529</v>
+        <v>0.1091065605625126</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4349587857723236</v>
+        <v>0.3959226608276367</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +860,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.773575459988618</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.773575459988618</v>
+        <v>4.885279833681822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,37 +899,37 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="J5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>5.25</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.5766567227786064</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2157468570210952</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2075964202002983</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07936507936507931</v>
+        <v>0.07045305505659627</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3594461381435394</v>
+        <v>0.5418547987937927</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4944868683815002</v>
+        <v>0.3147798776626587</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1460669487714767</v>
+        <v>0.1433653831481934</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -946,19 +938,19 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1231601904420292</v>
+        <v>-0.03480192398481363</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1231601904420292</v>
+        <v>-0.03480192398481363</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4944868683815002</v>
+        <v>0.5418547987937927</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -966,16 +958,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.02910977237245</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.02910977237245</v>
+        <v>6.685932843039379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -983,12 +972,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1008,37 +997,37 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3829220845704924</v>
+        <v>0.4814305364511692</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2759291491757961</v>
+        <v>0.2503438789546079</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3411487662537115</v>
+        <v>0.2682255845942227</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06591727600130959</v>
+        <v>0.06520146520146541</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.360698938369751</v>
+        <v>0.6030269861221313</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2233530133962631</v>
+        <v>0.2290270328521729</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4159480929374695</v>
+        <v>0.1679459363222122</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1047,19 +1036,19 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07479932668375799</v>
+        <v>0.1215964496709622</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07479932668375799</v>
+        <v>0.1215964496709622</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4159480929374695</v>
+        <v>0.6030269861221313</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1067,16 +1056,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.633445543421199</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.633445543421199</v>
+        <v>7.440734936237675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1084,12 +1070,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1109,37 +1095,37 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4059040590405905</v>
+        <v>0.3997567403202919</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2829028290282903</v>
+        <v>0.2763024528684371</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3111931119311193</v>
+        <v>0.323940806811271</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07114624505928857</v>
+        <v>0.06447714815933714</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3838543593883514</v>
+        <v>0.2403905987739563</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3601999580860138</v>
+        <v>0.4160029888153076</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2559456825256348</v>
+        <v>0.3436063826084137</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1148,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1009515303600612</v>
+        <v>0.1397005359468705</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1009515303600612</v>
+        <v>0.1397005359468705</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3838543593883514</v>
+        <v>0.4160029888153076</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1168,29 +1154,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.198780008697359</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.198780008697359</v>
+        <v>5.13305049971751</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1210,37 +1193,37 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="J8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5860437947885057</v>
+        <v>0.197540225352967</v>
       </c>
       <c r="M8" t="n">
-        <v>0.216551979598524</v>
+        <v>0.2405938642119471</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1974042256129703</v>
+        <v>0.5618659104350859</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06647319800656382</v>
+        <v>0.06573896740931096</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3106180727481842</v>
+        <v>0.1511439085006714</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5455252528190613</v>
+        <v>0.3679043650627136</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1438566744327545</v>
+        <v>0.4809516966342926</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1249,19 +1232,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.04051854196944438</v>
+        <v>-0.08091421380079333</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.04051854196944438</v>
+        <v>-0.08091421380079333</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5455252528190613</v>
+        <v>0.4809516966342926</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1269,29 +1252,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.839622185889568</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.839622185889568</v>
+        <v>5.934450985025705</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1311,37 +1291,37 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1185698650127691</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1517694272163444</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7296607077708864</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0542307692307693</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4664634146341464</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2591463414634146</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.274390243902439</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.07189542483660127</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.2445431053638458</v>
+        <v>0.1943183243274689</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5760452151298523</v>
+        <v>0.2882589101791382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1794116646051407</v>
+        <v>0.5174227356910706</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1350,19 +1330,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1095818004957059</v>
+        <v>-0.2122379720798159</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1095818004957059</v>
+        <v>-0.2122379720798159</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5760452151298523</v>
+        <v>0.5174227356910706</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1370,29 +1350,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.801741142903182</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.801741142903182</v>
+        <v>5.075066704917142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1412,37 +1389,37 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.5714914533049666</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2299904629154134</v>
       </c>
       <c r="N10" t="n">
-        <v>0.323940806811271</v>
+        <v>0.19851808377962</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.06048936087446988</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4143766462802887</v>
+        <v>0.5172398686408997</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2349821478128433</v>
+        <v>0.3701968193054199</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3506411910057068</v>
+        <v>0.1125633493065834</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
@@ -1451,19 +1428,19 @@
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1380741934118516</v>
+        <v>-0.05425158466406699</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1380741934118516</v>
+        <v>-0.05425158466406699</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4143766462802887</v>
+        <v>0.5172398686408997</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1471,29 +1448,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.612162457098814</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.612162457098814</v>
+        <v>6.382209834025338</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1513,37 +1487,37 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1785852081476258</v>
+        <v>0.4081222356252514</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2165294094168674</v>
+        <v>0.268194611982308</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6048853824355068</v>
+        <v>0.3236831523924407</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06658436301586113</v>
+        <v>0.06532448061683449</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3628591895103455</v>
+        <v>0.2508946657180786</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1506211757659912</v>
+        <v>0.37337726354599</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4865196645259857</v>
+        <v>0.3757281303405762</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -1552,19 +1526,19 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1183657179095211</v>
+        <v>0.05204497794813545</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1183657179095211</v>
+        <v>0.05204497794813545</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4865196645259857</v>
+        <v>0.3757281303405762</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1572,29 +1546,26 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.986139484888165</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.986139484888165</v>
+        <v>4.636100025855518</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1614,37 +1585,37 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.29</v>
+        <v>2.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1179029722516726</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1509158044821409</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7311812232661865</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06019379844961237</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2923648655414581</v>
+        <v>0.3111074566841125</v>
       </c>
       <c r="R12" t="n">
-        <v>0.198116809129715</v>
+        <v>0.4535876512527466</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5095183849334717</v>
+        <v>0.2353049218654633</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1653,19 +1624,19 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2216628383327148</v>
+        <v>0.175237135788829</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2216628383327148</v>
+        <v>0.175237135788829</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5095183849334717</v>
+        <v>0.4535876512527466</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.29</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1673,29 +1644,26 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3.898607960178552</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.898607960178552</v>
+        <v>5.596806711795741</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1715,37 +1683,37 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5879059350503919</v>
+        <v>0.509891622226045</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2239641657334826</v>
+        <v>0.2418716669533804</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1881298992161254</v>
+        <v>0.2482367108205746</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06309523809523809</v>
+        <v>0.06010869168763899</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3455632627010345</v>
+        <v>0.3935825228691101</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5473897457122803</v>
+        <v>0.4183503687381744</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1070470809936523</v>
+        <v>0.1880670338869095</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1754,19 +1722,19 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.04051618933811163</v>
+        <v>0.1764787017847941</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.04051618933811163</v>
+        <v>0.1764787017847941</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5473897457122803</v>
+        <v>0.4183503687381744</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1774,10 +1742,791 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>6.86490604408993</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6.86490604408993</v>
+        <v>5.162014762018634</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5490012957333573</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2193469380181774</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2316517662484654</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05288400332240517</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.373563140630722</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3170212209224701</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3094155788421631</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.1754381551026353</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1754381551026353</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.373563140630722</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.527022762527397</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6179775280898876</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2101123595505618</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1719101123595506</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05763517528223416</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5057827234268188</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3135067522525787</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.18071049451828</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.1121948046630687</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1121948046630687</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5057827234268188</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.548655957345954</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>21</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8449904139742952</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1103458070013491</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0446637790243556</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06616700734347791</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.8248028755187988</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1331712007522583</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.04202590882778168</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.02018753845549637</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.02018753845549637</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.8248028755187988</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.17722210219472</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3530351437699681</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2803514376996806</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3666134185303515</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.04910340204457841</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3205142021179199</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3738568127155304</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3056288659572601</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.09350537501584982</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.09350537501584982</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3738568127155304</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.613009884369452</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5095541401273885</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2356687898089172</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2547770700636943</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06081081081081074</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2984151542186737</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4624479711055756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2391369342803955</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2267791812966584</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.2267791812966584</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4624479711055756</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.706133977394818</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2775479503572772</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.46032342986085</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05970030288538175</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2369374632835388</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3419689536094666</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4210935235023499</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.03922990635850016</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.03922990635850016</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4210935235023499</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.195862480212083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3362307388384038</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2544448834452785</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4093243777163176</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06219573610877971</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.273058295249939</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.366264671087265</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3606770038604736</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1118197876419865</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1118197876419865</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.366264671087265</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.519330638242219</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4302959501557632</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2784267912772586</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2912772585669782</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.05635540929658589</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3594544529914856</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.4124374985694885</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2281080931425095</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.13401070729223</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.13401070729223</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.4124374985694885</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.08905600453333</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -611,49 +611,47 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6306306306306306</v>
+        <v>0.6406685236768802</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.1922005571030641</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1801801801801802</v>
+        <v>0.1671309192200557</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.04057971014492745</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4802414178848267</v>
+        <v>0.4629707038402557</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3722254633903503</v>
+        <v>0.3904054462909698</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1475331038236618</v>
+        <v>0.1466238349676132</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.150389212745804</v>
+        <v>-0.1776978198366245</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.150389212745804</v>
+        <v>-0.1776978198366245</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4802414178848267</v>
+        <v>0.4629707038402557</v>
       </c>
       <c r="Z2" t="n">
         <v>1.5</v>
@@ -664,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.997862501327692</v>
+        <v>4.616279480864103</v>
       </c>
     </row>
     <row r="3">
@@ -703,58 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4020260838352012</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2699317991464922</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3280421170183065</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0584684228301251</v>
+        <v>0.05102040816326525</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2029433697462082</v>
+        <v>0.2126755714416504</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3414356410503387</v>
+        <v>0.4157065749168396</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4556211531162262</v>
+        <v>0.37161785364151</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1275790360979197</v>
+        <v>0.1438619147226649</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1275790360979197</v>
+        <v>0.1438619147226649</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4556211531162262</v>
+        <v>0.4157065749168396</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.621898040553345</v>
+        <v>5.12939305601984</v>
       </c>
     </row>
     <row r="4">
@@ -801,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -810,49 +806,47 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.3956834532374101</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.316546762589928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3545161485671997</v>
+        <v>0.3598228693008423</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3959226608276367</v>
+        <v>0.34445720911026</v>
       </c>
       <c r="S4" t="n">
-        <v>0.24956114590168</v>
+        <v>0.2957199215888977</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1091065605625126</v>
+        <v>-0.03586058393656782</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1091065605625126</v>
+        <v>-0.03586058393656782</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3959226608276367</v>
+        <v>0.3598228693008423</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -860,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.885279833681822</v>
+        <v>4.439845406722504</v>
       </c>
     </row>
     <row r="5">
@@ -899,58 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5766567227786064</v>
+        <v>0.5609973285841497</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2157468570210952</v>
+        <v>0.2270703472840606</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2075964202002983</v>
+        <v>0.2119323241317899</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07045305505659627</v>
+        <v>0.0485527544351072</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5418547987937927</v>
+        <v>0.531466007232666</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3147798776626587</v>
+        <v>0.3264229893684387</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1433653831481934</v>
+        <v>0.1421109735965729</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.03480192398481363</v>
+        <v>-0.02953132135148373</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.03480192398481363</v>
+        <v>-0.02953132135148373</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5418547987937927</v>
+        <v>0.531466007232666</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -958,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.685932843039379</v>
+        <v>6.557745803166986</v>
       </c>
     </row>
     <row r="6">
@@ -1003,49 +995,47 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4814305364511692</v>
+        <v>0.4850444624090541</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2503438789546079</v>
+        <v>0.2522231204527081</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2682255845942227</v>
+        <v>0.2627324171382376</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06520146520146541</v>
+        <v>0.05726495726495751</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6030269861221313</v>
+        <v>0.5834006071090698</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2290270328521729</v>
+        <v>0.2403881400823593</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1679459363222122</v>
+        <v>0.1762113869190216</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1215964496709622</v>
+        <v>0.09835614470001569</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1215964496709622</v>
+        <v>0.09835614470001569</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6030269861221313</v>
+        <v>0.5834006071090698</v>
       </c>
       <c r="Z6" t="n">
         <v>1.95</v>
@@ -1056,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.440734936237675</v>
+        <v>7.198565535273666</v>
       </c>
     </row>
     <row r="7">
@@ -1095,58 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.4125736738703341</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="N7" t="n">
-        <v>0.323940806811271</v>
+        <v>0.3163064833005894</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.05383022774327118</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2403905987739563</v>
+        <v>0.2406667470932007</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4160029888153076</v>
+        <v>0.4178179502487183</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3436063826084137</v>
+        <v>0.3415153324604034</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1397005359468705</v>
+        <v>0.1466981074196416</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1397005359468705</v>
+        <v>0.1466981074196416</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4160029888153076</v>
+        <v>0.4178179502487183</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1154,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.13305049971751</v>
+        <v>5.155445263561076</v>
       </c>
     </row>
     <row r="8">
@@ -1193,7 +1181,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>3.9</v>
@@ -1202,46 +1190,44 @@
         <v>1.67</v>
       </c>
       <c r="L8" t="n">
-        <v>0.197540225352967</v>
+        <v>0.1895352559438931</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2405938642119471</v>
+        <v>0.2429939178767861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5618659104350859</v>
+        <v>0.5674708261793209</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06573896740931096</v>
+        <v>0.05521265161983724</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1511439085006714</v>
+        <v>0.1538346707820892</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3679043650627136</v>
+        <v>0.3727922737598419</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4809516966342926</v>
+        <v>0.4733730852603912</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.08091421380079333</v>
+        <v>-0.09409774091892964</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.08091421380079333</v>
+        <v>-0.09409774091892964</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4809516966342926</v>
+        <v>0.4733730852603912</v>
       </c>
       <c r="Z8" t="n">
         <v>1.67</v>
@@ -1252,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.934450985025705</v>
+        <v>5.840938688369491</v>
       </c>
     </row>
     <row r="9">
@@ -1294,55 +1280,53 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1185698650127691</v>
+        <v>0.1197838486940859</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1517694272163444</v>
+        <v>0.1597117982587811</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7296607077708864</v>
+        <v>0.7205043530471329</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0542307692307693</v>
+        <v>0.043546365914787</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1943183243274689</v>
+        <v>0.1648818552494049</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2882589101791382</v>
+        <v>0.2964842617511749</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5174227356910706</v>
+        <v>0.5386338233947754</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.2122379720798159</v>
+        <v>-0.1818705296523575</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2122379720798159</v>
+        <v>-0.1818705296523575</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5174227356910706</v>
+        <v>0.5386338233947754</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1350,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.075066704917142</v>
+        <v>5.524141344098878</v>
       </c>
     </row>
     <row r="10">
@@ -1389,58 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5714914533049666</v>
+        <v>0.5608856088560886</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2299904629154134</v>
+        <v>0.2383763837638377</v>
       </c>
       <c r="N10" t="n">
-        <v>0.19851808377962</v>
+        <v>0.2007380073800738</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06048936087446988</v>
+        <v>0.04876160990712064</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5172398686408997</v>
+        <v>0.5502976775169373</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3701968193054199</v>
+        <v>0.3375295698642731</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1125633493065834</v>
+        <v>0.1121727451682091</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.05425158466406699</v>
+        <v>-0.01058793133915137</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.05425158466406699</v>
+        <v>-0.01058793133915137</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5172398686408997</v>
+        <v>0.5502976775169373</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1448,7 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.382209834025338</v>
+        <v>6.790109312954435</v>
       </c>
     </row>
     <row r="11">
@@ -1493,52 +1475,50 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.4125736738703341</v>
       </c>
       <c r="M11" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.3163064833005894</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.05383022774327118</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2508946657180786</v>
+        <v>0.2533594071865082</v>
       </c>
       <c r="R11" t="n">
-        <v>0.37337726354599</v>
+        <v>0.376624584197998</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3757281303405762</v>
+        <v>0.3700159192085266</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.05204497794813545</v>
+        <v>0.1055047413689214</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.05204497794813545</v>
+        <v>0.1055047413689214</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3757281303405762</v>
+        <v>0.376624584197998</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1546,7 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.636100025855518</v>
+        <v>4.647161347635723</v>
       </c>
     </row>
     <row r="12">
@@ -1585,55 +1565,53 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3111074566841125</v>
+        <v>0.3169910907745361</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4535876512527466</v>
+        <v>0.4297073781490326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2353049218654633</v>
+        <v>0.2533015012741089</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.175237135788829</v>
+        <v>0.152086981548466</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.175237135788829</v>
+        <v>0.152086981548466</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4535876512527466</v>
+        <v>0.4297073781490326</v>
       </c>
       <c r="Z12" t="n">
         <v>3.4</v>
@@ -1644,7 +1622,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>5.596806711795741</v>
+        <v>5.302148617781828</v>
       </c>
     </row>
     <row r="13">
@@ -1707,31 +1685,29 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3935825228691101</v>
+        <v>0.3607814013957977</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4183503687381744</v>
+        <v>0.4571996331214905</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1880670338869095</v>
+        <v>0.1820190101861954</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1764787017847941</v>
+        <v>0.2153279661681101</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1764787017847941</v>
+        <v>0.2153279661681101</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4183503687381744</v>
+        <v>0.4571996331214905</v>
       </c>
       <c r="Z13" t="n">
         <v>3.9</v>
@@ -1742,7 +1718,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.162014762018634</v>
+        <v>5.641374865955225</v>
       </c>
     </row>
     <row r="14">
@@ -1781,58 +1757,56 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5490012957333573</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2193469380181774</v>
+        <v>0.2233676975945017</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2316517662484654</v>
+        <v>0.2405498281786942</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05288400332240517</v>
+        <v>0.06593406593406592</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.373563140630722</v>
+        <v>0.3838088512420654</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3170212209224701</v>
+        <v>0.2944603562355042</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3094155788421631</v>
+        <v>0.3217307925224304</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1754381551026353</v>
+        <v>-0.1522736229847387</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1754381551026353</v>
+        <v>-0.1522736229847387</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.373563140630722</v>
+        <v>0.3838088512420654</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1840,7 +1814,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.527022762527397</v>
+        <v>3.796357622054108</v>
       </c>
     </row>
     <row r="15">
@@ -1903,31 +1877,29 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5057827234268188</v>
+        <v>0.5222343802452087</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3135067522525787</v>
+        <v>0.2484476268291473</v>
       </c>
       <c r="S15" t="n">
-        <v>0.18071049451828</v>
+        <v>0.2293179929256439</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.1121948046630687</v>
+        <v>-0.09574314784467886</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1121948046630687</v>
+        <v>-0.09574314784467886</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5057827234268188</v>
+        <v>0.5222343802452087</v>
       </c>
       <c r="Z15" t="n">
         <v>1.53</v>
@@ -1938,7 +1910,7 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.548655957345954</v>
+        <v>6.443836988097844</v>
       </c>
     </row>
     <row r="16">
@@ -2001,31 +1973,29 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8248028755187988</v>
+        <v>0.846028208732605</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1331712007522583</v>
+        <v>0.1117368414998055</v>
       </c>
       <c r="S16" t="n">
-        <v>0.04202590882778168</v>
+        <v>0.04223495721817017</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-0.02018753845549637</v>
+        <v>0.001037794758309785</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.02018753845549637</v>
+        <v>0.001037794758309785</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.8248028755187988</v>
+        <v>0.846028208732605</v>
       </c>
       <c r="Z16" t="n">
         <v>1.11</v>
@@ -2036,7 +2006,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>10.17722210219472</v>
+        <v>10.43912095914781</v>
       </c>
     </row>
     <row r="17">
@@ -2078,55 +2048,53 @@
         <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
         <v>2.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3530351437699681</v>
+        <v>0.3500611995104039</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2803514376996806</v>
+        <v>0.2864137086903305</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3666134185303515</v>
+        <v>0.3635250917992656</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04910340204457841</v>
+        <v>0.05801605801605803</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3205142021179199</v>
+        <v>0.3225607573986053</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3738568127155304</v>
+        <v>0.3748155534267426</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3056288659572601</v>
+        <v>0.3026237189769745</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.09350537501584982</v>
+        <v>0.08840184473641205</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.09350537501584982</v>
+        <v>0.08840184473641205</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3738568127155304</v>
+        <v>0.3748155534267426</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2134,7 +2102,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.613009884369452</v>
+        <v>4.624839762084519</v>
       </c>
     </row>
     <row r="18">
@@ -2197,31 +2165,29 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2984151542186737</v>
+        <v>0.3361214995384216</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4624479711055756</v>
+        <v>0.4123643636703491</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2391369342803955</v>
+        <v>0.2515142261981964</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2267791812966584</v>
+        <v>0.1766955738614319</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2267791812966584</v>
+        <v>0.1766955738614319</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4624479711055756</v>
+        <v>0.4123643636703491</v>
       </c>
       <c r="Z18" t="n">
         <v>4</v>
@@ -2232,7 +2198,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.706133977394818</v>
+        <v>5.088153594837564</v>
       </c>
     </row>
     <row r="19">
@@ -2271,58 +2237,56 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="N19" t="n">
-        <v>0.46032342986085</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="O19" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2369374632835388</v>
+        <v>0.2351477593183517</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3419689536094666</v>
+        <v>0.3429699242115021</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4210935235023499</v>
+        <v>0.4218823909759521</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-0.03922990635850016</v>
+        <v>-0.04826686275539116</v>
       </c>
       <c r="W19" t="n">
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.03922990635850016</v>
+        <v>-0.04826686275539116</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4210935235023499</v>
+        <v>0.4218823909759521</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2330,7 +2294,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>5.195862480212083</v>
+        <v>5.205596296286619</v>
       </c>
     </row>
     <row r="20">
@@ -2393,31 +2357,29 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.273058295249939</v>
+        <v>0.2728021442890167</v>
       </c>
       <c r="R20" t="n">
-        <v>0.366264671087265</v>
+        <v>0.3646692931652069</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3606770038604736</v>
+        <v>0.3625285625457764</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1118197876419865</v>
+        <v>0.1102244097199284</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1118197876419865</v>
+        <v>0.1102244097199284</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.366264671087265</v>
+        <v>0.3646692931652069</v>
       </c>
       <c r="Z20" t="n">
         <v>3.7</v>
@@ -2428,7 +2390,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>4.519330638242219</v>
+        <v>4.499645309866624</v>
       </c>
     </row>
     <row r="21">
@@ -2473,49 +2435,47 @@
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="O21" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3594544529914856</v>
+        <v>0.354951411485672</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4124374985694885</v>
+        <v>0.4376508295536041</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2281080931425095</v>
+        <v>0.2073977738618851</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.13401070729223</v>
+        <v>0.1579898126044516</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.13401070729223</v>
+        <v>0.1579898126044516</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.4124374985694885</v>
+        <v>0.4376508295536041</v>
       </c>
       <c r="Z21" t="n">
         <v>3.4</v>
@@ -2526,7 +2486,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.08905600453333</v>
+        <v>5.400162666473724</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6406685236768802</v>
+        <v>0.6389405204460966</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1922005571030641</v>
+        <v>0.1891263940520446</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1671309192200557</v>
+        <v>0.1719330855018587</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04057971014492745</v>
+        <v>0.05749385749385749</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -642,19 +642,19 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1776978198366245</v>
+        <v>-0.1759698166058409</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1776978198366245</v>
+        <v>-0.1759698166058409</v>
       </c>
       <c r="Y2" t="n">
         <v>0.4629707038402557</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.616279480864103</v>
+        <v>4.626940375239582</v>
       </c>
     </row>
     <row r="3">
@@ -722,35 +722,35 @@
         <v>0.05102040816326525</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2126755714416504</v>
+        <v>0.2106043696403503</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4157065749168396</v>
+        <v>0.3789964616298676</v>
       </c>
       <c r="S3" t="n">
-        <v>0.37161785364151</v>
+        <v>0.4103991985321045</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1438619147226649</v>
+        <v>0.07059337328938603</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1438619147226649</v>
+        <v>0.07059337328938603</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4157065749168396</v>
+        <v>0.4103991985321045</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.12939305601984</v>
+        <v>5.063905471227634</v>
       </c>
     </row>
     <row r="4">
@@ -821,29 +821,29 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3598228693008423</v>
+        <v>0.3562606275081635</v>
       </c>
       <c r="R4" t="n">
-        <v>0.34445720911026</v>
+        <v>0.3404795527458191</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2957199215888977</v>
+        <v>0.3032599091529846</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.03586058393656782</v>
+        <v>-0.03942282572924666</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.03586058393656782</v>
+        <v>-0.03942282572924666</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3598228693008423</v>
+        <v>0.3562606275081635</v>
       </c>
       <c r="Z4" t="n">
         <v>2.4</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.439845406722504</v>
+        <v>4.395890994120572</v>
       </c>
     </row>
     <row r="5">
@@ -917,29 +917,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.531466007232666</v>
+        <v>0.5347434282302856</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3264229893684387</v>
+        <v>0.3243873119354248</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1421109735965729</v>
+        <v>0.1408692300319672</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.02953132135148373</v>
+        <v>-0.0262539003538641</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02953132135148373</v>
+        <v>-0.0262539003538641</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.531466007232666</v>
+        <v>0.5347434282302856</v>
       </c>
       <c r="Z5" t="n">
         <v>1.7</v>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.557745803166986</v>
+        <v>6.598185819084961</v>
       </c>
     </row>
     <row r="6">
@@ -992,50 +992,50 @@
         <v>1.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4850444624090541</v>
+        <v>0.4833968426782798</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2522231204527081</v>
+        <v>0.2547632008709852</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2627324171382376</v>
+        <v>0.2618399564507349</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05726495726495751</v>
+        <v>0.06086856086856107</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5834006071090698</v>
+        <v>0.5999532341957092</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2403881400823593</v>
+        <v>0.2258628904819489</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1762113869190216</v>
+        <v>0.1741838157176971</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.09835614470001569</v>
+        <v>0.1165563915174295</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09835614470001569</v>
+        <v>0.1165563915174295</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5834006071090698</v>
+        <v>0.5999532341957092</v>
       </c>
       <c r="Z6" t="n">
         <v>1.95</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.198565535273666</v>
+        <v>7.402807987907663</v>
       </c>
     </row>
     <row r="7">
@@ -1109,29 +1109,29 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2406667470932007</v>
+        <v>0.2432092428207397</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4178179502487183</v>
+        <v>0.4212515652179718</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3415153324604034</v>
+        <v>0.3355391025543213</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1466981074196416</v>
+        <v>0.1501317223888952</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1466981074196416</v>
+        <v>0.1501317223888952</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4178179502487183</v>
+        <v>0.4212515652179718</v>
       </c>
       <c r="Z7" t="n">
         <v>3.5</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.155445263561076</v>
+        <v>5.197812552998002</v>
       </c>
     </row>
     <row r="8">
@@ -1187,50 +1187,50 @@
         <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1895352559438931</v>
+        <v>0.1882404563405002</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2429939178767861</v>
+        <v>0.2413339183852567</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5674708261793209</v>
+        <v>0.5704256252742431</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05521265161983724</v>
+        <v>0.06247086247086253</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1538346707820892</v>
+        <v>0.1528116166591644</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3727922737598419</v>
+        <v>0.3622519373893738</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4733730852603912</v>
+        <v>0.484936386346817</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.09409774091892964</v>
+        <v>-0.0854892389274261</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09409774091892964</v>
+        <v>-0.0854892389274261</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4733730852603912</v>
+        <v>0.484936386346817</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.840938688369491</v>
+        <v>5.983617971970536</v>
       </c>
     </row>
     <row r="9">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -1286,44 +1286,44 @@
         <v>1.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1197838486940859</v>
+        <v>0.1267572075291875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1597117982587811</v>
+        <v>0.1584465094114844</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7205043530471329</v>
+        <v>0.7147962830593281</v>
       </c>
       <c r="O9" t="n">
-        <v>0.043546365914787</v>
+        <v>0.0518796992481203</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1648818552494049</v>
+        <v>0.1729756444692612</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2964842617511749</v>
+        <v>0.296008825302124</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5386338233947754</v>
+        <v>0.5310155153274536</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1818705296523575</v>
+        <v>-0.1837807677318745</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1818705296523575</v>
+        <v>-0.1837807677318745</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5386338233947754</v>
+        <v>0.5310155153274536</v>
       </c>
       <c r="Z9" t="n">
         <v>1.33</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.524141344098878</v>
+        <v>5.418354040931621</v>
       </c>
     </row>
     <row r="10">
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5608856088560886</v>
+        <v>0.5772208925805997</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2383763837638377</v>
+        <v>0.2322962128678023</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2007380073800738</v>
+        <v>0.1904828945515979</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04876160990712064</v>
+        <v>0.04996304508499638</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1410,19 +1410,19 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.01058793133915137</v>
+        <v>-0.02692321506366246</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01058793133915137</v>
+        <v>-0.02692321506366246</v>
       </c>
       <c r="Y10" t="n">
         <v>0.5502976775169373</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1493,29 +1493,29 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2533594071865082</v>
+        <v>0.2538716197013855</v>
       </c>
       <c r="R11" t="n">
-        <v>0.376624584197998</v>
+        <v>0.375970184803009</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3700159192085266</v>
+        <v>0.3701580762863159</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1055047413689214</v>
+        <v>0.1048503419739324</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1055047413689214</v>
+        <v>0.1048503419739324</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.376624584197998</v>
+        <v>0.375970184803009</v>
       </c>
       <c r="Z11" t="n">
         <v>3.5</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.647161347635723</v>
+        <v>4.639086729828218</v>
       </c>
     </row>
     <row r="12">
@@ -1565,25 +1565,25 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1602,13 +1602,13 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.152086981548466</v>
+        <v>0.1534077465485414</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.152086981548466</v>
+        <v>0.1534077465485414</v>
       </c>
       <c r="Y12" t="n">
         <v>0.4297073781490326</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
@@ -1766,47 +1766,47 @@
         <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5360824742268041</v>
+        <v>0.5403800475059383</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2233676975945017</v>
+        <v>0.221298495645289</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2405498281786942</v>
+        <v>0.2383214568487728</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06593406593406592</v>
+        <v>0.07590084334270375</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3838088512420654</v>
+        <v>0.3818604648113251</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2944603562355042</v>
+        <v>0.294249564409256</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3217307925224304</v>
+        <v>0.3238899409770966</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1522736229847387</v>
+        <v>-0.1585195826946132</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1522736229847387</v>
+        <v>-0.1585195826946132</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3838088512420654</v>
+        <v>0.3818604648113251</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.796357622054108</v>
+        <v>3.733782159985721</v>
       </c>
     </row>
     <row r="15">
@@ -2237,56 +2237,56 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2618399564507349</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2547632008709852</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.4833968426782798</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06086856086856107</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2351477593183517</v>
+        <v>0.2331060171127319</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3429699242115021</v>
+        <v>0.3418344557285309</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4218823909759521</v>
+        <v>0.4250595569610596</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-0.04826686275539116</v>
+        <v>-0.05833728571722019</v>
       </c>
       <c r="W19" t="n">
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.04826686275539116</v>
+        <v>-0.05833728571722019</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4218823909759521</v>
+        <v>0.4250595569610596</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>5.205596296286619</v>
+        <v>5.244799268106568</v>
       </c>
     </row>
     <row r="20">

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1061224489795918</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1591836734693878</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04700854700854684</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1828196793794632</v>
+        <v>0.319741427898407</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2998478710651398</v>
+        <v>0.4340426027774811</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5173324346542358</v>
+        <v>0.2462159693241119</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.2173614428967846</v>
+        <v>0.1577429711769899</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2173614428967846</v>
+        <v>0.1577429711769899</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5173324346542358</v>
+        <v>0.4340426027774811</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.042343293386659</v>
+        <v>4.043875181011076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5908776779543885</v>
+        <v>0.509891622226045</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2100898410504492</v>
+        <v>0.2418716669533804</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1990324809951624</v>
+        <v>0.2482367108205746</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05774853801169577</v>
+        <v>0.06010869168763899</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5400474071502686</v>
+        <v>0.359193354845047</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3467968702316284</v>
+        <v>0.4526554346084595</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1131557673215866</v>
+        <v>0.1881512105464935</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.05083027080411995</v>
+        <v>0.2107837676550791</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.05083027080411995</v>
+        <v>0.2107837676550791</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5400474071502686</v>
+        <v>0.4526554346084595</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.663631482644355</v>
+        <v>4.217286657690967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,64 +797,1696 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3956834532374101</v>
+        <v>0.556367975035947</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.2184354636399792</v>
       </c>
       <c r="N4" t="n">
-        <v>0.316546762589928</v>
+        <v>0.2251965613240738</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.05727741442997525</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2499844878911972</v>
+        <v>0.3805594146251678</v>
       </c>
       <c r="R4" t="n">
-        <v>0.380704402923584</v>
+        <v>0.2967153489589691</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3693111538887024</v>
+        <v>0.322725236415863</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.09293461875092207</v>
+        <v>-0.1758085604107792</v>
       </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1758085604107792</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3805594146251678</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.726600631142012</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6068194952802928</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2117125794644577</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1814679252552495</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04964108785764831</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.396569550037384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3206329345703125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.282797634601593</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>-0.2102499452429087</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.2102499452429087</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.396569550037384</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.715322149740102</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8560394765071873</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.09912036043767432</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.04484016305513838</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06197311460469357</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8328315615653992</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1226308792829514</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.04453747719526291</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.02320791494178809</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.02320791494178809</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8328315615653992</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.759300262752334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3434343434343434</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2861952861952861</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3703703703703703</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05882352941176494</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
-        <v>0.09293461875092207</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.380704402923584</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="Q7" t="n">
+        <v>0.3173985779285431</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3763180673122406</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3062833845615387</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.09012278111695449</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.09012278111695449</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3763180673122406</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>4.69750212909925</v>
+      <c r="AB7" t="n">
+        <v>3.506068949987824</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5261599210266535</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2309970384995065</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2428430404738401</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05586825099020221</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3592883050441742</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.384587824344635</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2561239302158356</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1535907858451286</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1535907858451286</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.384587824344635</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.5831163757527</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2339261285909713</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2462380300957592</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5198358413132695</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06871345029239762</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2216976583003998</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3273646831512451</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4509376883506775</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.06889815296259205</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.06889815296259205</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4509376883506775</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.201282810569351</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3373753178173283</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2519069039702718</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4107177782123997</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05859213250517614</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2607450187206268</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3697629272937775</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3694920837879181</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1178560233235056</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1178560233235056</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3697629272937775</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.444996216898751</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3729406297206879</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4138306081295013</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.213228777050972</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1281163224152156</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1281163224152156</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4138306081295013</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.855564671875187</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.276595744680851</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2411347517730496</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4822695035460993</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06334841628959298</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1865646541118622</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4124358296394348</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4009995460510254</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1713010778663852</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1713010778663852</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4124358296394348</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.842569841222861</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1693682296196727</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.221791729263857</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6088400411164703</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07350819115524998</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1914869099855423</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3122490644454956</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4962640404701233</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.112576000646347</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.112576000646347</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4962640404701233</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.099155653395441</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2832726538181305</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3239926099777222</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3927347362041473</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.09884682368706083</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.09884682368706083</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3927347362041473</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.659019281273375</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6585824796153043</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2078193602341626</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1335981601505331</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06930471719204112</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6169694662094116</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3135440349578857</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.06948645412921906</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.04161301340589263</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.04161301340589263</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6169694662094116</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.74816272845218</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4276704769412693</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2688214426487978</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.303508080409933</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06284038542103043</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2771597802639008</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4005228579044342</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.322317361831665</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1317014152556364</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1317014152556364</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4005228579044342</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.731579421335547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3781597573306371</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2780586450960567</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3437815975733064</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05775401069518704</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2585683166980743</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5105438828468323</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.230887696146965</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2324852377507756</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2324852377507756</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5105438828468323</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.756620026352043</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.35437430786268</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2912513842746401</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.35437430786268</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.07295627376425862</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2586992979049683</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4132872819900513</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3280134201049805</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1220358977154112</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1220358977154112</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4132872819900513</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.850502627097884</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5011684342980406</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.226136976451555</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2726945892504045</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07856062662375418</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4929071366786957</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2933664619922638</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2137264013290405</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.008261297619344909</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.008261297619344909</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4929071366786957</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.592302515474699</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3787575150300601</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2705410821643286</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3507014028056112</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.05608465608465618</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.3013293743133545</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4174540936946869</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2812166213989258</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1469130115303583</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1469130115303583</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4174540936946869</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.889323854158309</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4452054794520548</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2671232876712329</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2876712328767124</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06959706959706957</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3036673367023468</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5178395509719849</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1784931123256683</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.250716263300752</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.250716263300752</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5178395509719849</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.824592089627416</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,53 +605,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.3181818181818181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2807486631016043</v>
       </c>
       <c r="N2" t="n">
-        <v>0.375767498976668</v>
+        <v>0.4010695187165775</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.04761904761904767</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.319741427898407</v>
+        <v>0.2699255049228668</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4340426027774811</v>
+        <v>0.5417613983154297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2462159693241119</v>
+        <v>0.1883131116628647</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1577429711769899</v>
+        <v>0.2610127352138254</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1577429711769899</v>
+        <v>0.2610127352138254</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4340426027774811</v>
+        <v>0.5417613983154297</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.043875181011076</v>
+        <v>5.047466443750865</v>
       </c>
     </row>
     <row r="3">
@@ -725,29 +725,29 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.359193354845047</v>
+        <v>0.3803949654102325</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4526554346084595</v>
+        <v>0.4264385104179382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1881512105464935</v>
+        <v>0.1931665986776352</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2107837676550791</v>
+        <v>0.1845668434645578</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2107837676550791</v>
+        <v>0.1845668434645578</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4526554346084595</v>
+        <v>0.4264385104179382</v>
       </c>
       <c r="Z3" t="n">
         <v>3.9</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.217286657690967</v>
+        <v>3.973029600024097</v>
       </c>
     </row>
     <row r="4">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="J4" t="n">
         <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.556367975035947</v>
+        <v>0.5692192187805826</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2184354636399792</v>
+        <v>0.2195372044719568</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2251965613240738</v>
+        <v>0.2112435767474606</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05727741442997525</v>
+        <v>0.05197149964889314</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3805594146251678</v>
+        <v>0.3901978135108948</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2967153489589691</v>
+        <v>0.2847239077091217</v>
       </c>
       <c r="S4" t="n">
-        <v>0.322725236415863</v>
+        <v>0.3250783383846283</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1758085604107792</v>
+        <v>-0.1790214052696878</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1758085604107792</v>
+        <v>-0.1790214052696878</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3805594146251678</v>
+        <v>0.3901978135108948</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.726600631142012</v>
+        <v>2.801432709924467</v>
       </c>
     </row>
     <row r="5">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6068194952802928</v>
+        <v>0.5878712871287128</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2117125794644577</v>
+        <v>0.2116336633663366</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1814679252552495</v>
+        <v>0.2004950495049505</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04964108785764831</v>
+        <v>0.0500324886289798</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.396569550037384</v>
+        <v>0.4161856174468994</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3206329345703125</v>
+        <v>0.3569003641605377</v>
       </c>
       <c r="S5" t="n">
-        <v>0.282797634601593</v>
+        <v>0.2269140928983688</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.2102499452429087</v>
+        <v>-0.1716856696818134</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2102499452429087</v>
+        <v>-0.1716856696818134</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.396569550037384</v>
+        <v>0.4161856174468994</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.715322149740102</v>
+        <v>3.077727788143792</v>
       </c>
     </row>
     <row r="6">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="J6" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8560394765071873</v>
+        <v>0.8501275191278691</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09912036043767432</v>
+        <v>0.09436415462319349</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04484016305513838</v>
+        <v>0.05550832624893734</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06197311460469357</v>
+        <v>0.05972443031266561</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8328315615653992</v>
+        <v>0.8189796805381775</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1226308792829514</v>
+        <v>0.1364652812480927</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04453747719526291</v>
+        <v>0.04455514252185822</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.02320791494178809</v>
+        <v>-0.03114783858969161</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.02320791494178809</v>
+        <v>-0.03114783858969161</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8328315615653992</v>
+        <v>0.8189796805381775</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.759300262752334</v>
+        <v>7.630245470577896</v>
       </c>
     </row>
     <row r="7">
@@ -1085,56 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.3530351437699681</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2861952861952861</v>
+        <v>0.2803514376996806</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3666134185303515</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05882352941176494</v>
+        <v>0.04910340204457841</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3173985779285431</v>
+        <v>0.3196344375610352</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3763180673122406</v>
+        <v>0.3744441568851471</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3062833845615387</v>
+        <v>0.3059214353561401</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09012278111695449</v>
+        <v>0.09409271918546652</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09012278111695449</v>
+        <v>0.09409271918546652</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3763180673122406</v>
+        <v>0.3744441568851471</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.506068949987824</v>
+        <v>3.488610157189445</v>
       </c>
     </row>
     <row r="8">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5261599210266535</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2309970384995065</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2428430404738401</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05586825099020221</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3592883050441742</v>
+        <v>0.300824373960495</v>
       </c>
       <c r="R8" t="n">
-        <v>0.384587824344635</v>
+        <v>0.4699707627296448</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2561239302158356</v>
+        <v>0.2292047888040543</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1535907858451286</v>
+        <v>0.2452516616060493</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1535907858451286</v>
+        <v>0.2452516616060493</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.384587824344635</v>
+        <v>0.4699707627296448</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.5831163757527</v>
+        <v>4.378609590491235</v>
       </c>
     </row>
     <row r="9">
@@ -1277,53 +1277,53 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.2324080051646223</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.2382182052937379</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.5293737895416398</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.04945799457994582</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2216976583003998</v>
+        <v>0.2213420569896698</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3273646831512451</v>
+        <v>0.3242479562759399</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4509376883506775</v>
+        <v>0.4544099569320679</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.06889815296259205</v>
+        <v>-0.07496383260957196</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.06889815296259205</v>
+        <v>-0.07496383260957196</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4509376883506775</v>
+        <v>0.4544099569320679</v>
       </c>
       <c r="Z9" t="n">
         <v>1.8</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.201282810569351</v>
+        <v>4.233633138966233</v>
       </c>
     </row>
     <row r="10">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
@@ -1382,44 +1382,44 @@
         <v>2.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3373753178173283</v>
+        <v>0.3311067603362892</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2519069039702718</v>
+        <v>0.2542899919382701</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4107177782123997</v>
+        <v>0.4146032477254405</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05859213250517614</v>
+        <v>0.04867149758454126</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2607450187206268</v>
+        <v>0.2703346908092499</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3697629272937775</v>
+        <v>0.3729034066200256</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3694920837879181</v>
+        <v>0.3567618727684021</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1178560233235056</v>
+        <v>0.1186134146817555</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1178560233235056</v>
+        <v>0.1186134146817555</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3697629272937775</v>
+        <v>0.3729034066200256</v>
       </c>
       <c r="Z10" t="n">
         <v>3.75</v>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.444996216898751</v>
+        <v>3.47425534105529</v>
       </c>
     </row>
     <row r="11">
@@ -1469,56 +1469,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.3800403225806452</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2923387096774194</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.3276209677419355</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06060606060606055</v>
+        <v>0.0525198938992042</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3729406297206879</v>
+        <v>0.3565034568309784</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4138306081295013</v>
+        <v>0.4090585112571716</v>
       </c>
       <c r="S11" t="n">
-        <v>0.213228777050972</v>
+        <v>0.2344381064176559</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1281163224152156</v>
+        <v>0.1167198015797523</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1281163224152156</v>
+        <v>0.1167198015797523</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4138306081295013</v>
+        <v>0.4090585112571716</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1526,967 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3.855564671875187</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45598.39583333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>newcastle</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>arsenal</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.276595744680851</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2411347517730496</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.4822695035460993</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06334841628959298</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.1865646541118622</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.4124358296394348</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.4009995460510254</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.1713010778663852</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.1713010778663852</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.4124358296394348</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.842569841222861</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>bournemouth</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>manchester city</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" t="n">
-        <v>481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1693682296196727</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.221791729263857</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.6088400411164703</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.07350819115524998</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1914869099855423</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3122490644454956</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.4962640404701233</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.112576000646347</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.112576000646347</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.4962640404701233</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.099155653395441</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ipswich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>leicester</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.4374145674672915</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2686975200156219</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.2938879125170865</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06333056478405319</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2832726538181305</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3239926099777222</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3927347362041473</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.09884682368706083</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.09884682368706083</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3927347362041473</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.659019281273375</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>liverpool</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>brighton</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>48</v>
-      </c>
-      <c r="F15" t="n">
-        <v>481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.6585824796153043</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2078193602341626</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1335981601505331</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06930471719204112</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.6169694662094116</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3135440349578857</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.06948645412921906</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.04161301340589263</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.04161301340589263</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.6169694662094116</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.74816272845218</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>west ham</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F16" t="n">
-        <v>481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4276704769412693</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2688214426487978</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.303508080409933</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06284038542103043</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2771597802639008</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.4005228579044342</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.322317361831665</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.1317014152556364</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.1317014152556364</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4005228579044342</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.731579421335547</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>southampton</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>everton</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" t="n">
-        <v>481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.3781597573306371</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2780586450960567</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.3437815975733064</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.05775401069518704</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.2585683166980743</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.5105438828468323</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.230887696146965</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.2324852377507756</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.2324852377507756</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.5105438828468323</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.756620026352043</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>wolves</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>crystal palace</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>48</v>
-      </c>
-      <c r="F18" t="n">
-        <v>481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.35437430786268</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2912513842746401</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.35437430786268</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.07295627376425862</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.2586992979049683</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.4132872819900513</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3280134201049805</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.1220358977154112</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.1220358977154112</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.4132872819900513</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.850502627097884</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>aston villa</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>48</v>
-      </c>
-      <c r="F19" t="n">
-        <v>481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.5011684342980406</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.226136976451555</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.2726945892504045</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.07856062662375418</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.4929071366786957</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2933664619922638</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2137264013290405</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-0.008261297619344909</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.008261297619344909</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.4929071366786957</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>4.592302515474699</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>48</v>
-      </c>
-      <c r="F20" t="n">
-        <v>481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.3787575150300601</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.2705410821643286</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.3507014028056112</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.05608465608465618</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.3013293743133545</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.4174540936946869</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.2812166213989258</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>0.1469130115303583</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.1469130115303583</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.4174540936946869</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.889323854158309</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>fulham</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>brentford</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>48</v>
-      </c>
-      <c r="F21" t="n">
-        <v>481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4452054794520548</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2671232876712329</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.2876712328767124</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.06959706959706957</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.3036673367023468</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.5178395509719849</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1784931123256683</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>0.250716263300752</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.250716263300752</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.5178395509719849</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB21" t="n">
-        <v>4.824592089627416</v>
+        <v>3.811104142010362</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45598.39583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3181818181818181</v>
+        <v>0.2674124864669793</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2807486631016043</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4010695187165775</v>
+        <v>0.492601948754962</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.06844033159822649</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2699255049228668</v>
+        <v>0.1892061829566956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5417613983154297</v>
+        <v>0.3946299850940704</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1883131116628647</v>
+        <v>0.4161638617515564</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2610127352138254</v>
+        <v>-0.0764380870034056</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2610127352138254</v>
+        <v>-0.0764380870034056</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5417613983154297</v>
+        <v>0.4161638617515564</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.047466443750865</v>
+        <v>5.377117205402176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>5.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0.509891622226045</v>
+        <v>0.16450818118643</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2418716669533804</v>
+        <v>0.2252195337671362</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2482367108205746</v>
+        <v>0.6102722850464337</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06010869168763899</v>
+        <v>0.05716957189607963</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3803949654102325</v>
+        <v>0.2029496431350708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4264385104179382</v>
+        <v>0.3178140819072723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1931665986776352</v>
+        <v>0.4792363047599792</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1845668434645578</v>
+        <v>-0.1310359802864545</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1845668434645578</v>
+        <v>-0.1310359802864545</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4264385104179382</v>
+        <v>0.4792363047599792</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.973029600024097</v>
+        <v>5.345519090371639</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="J4" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5692192187805826</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2195372044719568</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2112435767474606</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05197149964889314</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3901978135108948</v>
+        <v>0.2861753106117249</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2847239077091217</v>
+        <v>0.3283967971801758</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3250783383846283</v>
+        <v>0.3854278922080994</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1790214052696878</v>
+        <v>0.07900765874506438</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1790214052696878</v>
+        <v>0.07900765874506438</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3901978135108948</v>
+        <v>0.3854278922080994</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,26 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.801432709924467</v>
+        <v>4.979987791134332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>brighton</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>wolves</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5878712871287128</v>
+        <v>0.6585824796153043</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2116336633663366</v>
+        <v>0.2078193602341626</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2004950495049505</v>
+        <v>0.1335981601505331</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0500324886289798</v>
+        <v>0.06930471719204112</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4161856174468994</v>
+        <v>0.6612443327903748</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3569003641605377</v>
+        <v>0.2605928778648376</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2269140928983688</v>
+        <v>0.07816275209188461</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1716856696818134</v>
+        <v>0.002661853175070505</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1716856696818134</v>
+        <v>0.002661853175070505</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4161856174468994</v>
+        <v>0.6612443327903748</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,26 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.077727788143792</v>
+        <v>8.543721849987156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.11</v>
+        <v>2.15</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8501275191278691</v>
+        <v>0.4374145674672915</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09436415462319349</v>
+        <v>0.2686975200156219</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05550832624893734</v>
+        <v>0.2938879125170865</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05972443031266561</v>
+        <v>0.06333056478405319</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8189796805381775</v>
+        <v>0.2642138004302979</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1364652812480927</v>
+        <v>0.4037013947963715</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04455514252185822</v>
+        <v>0.3320848047733307</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.03114783858969161</v>
+        <v>0.1350038747807495</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03114783858969161</v>
+        <v>0.1350038747807495</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8189796805381775</v>
+        <v>0.4037013947963715</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.11</v>
+        <v>3.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.630245470577896</v>
+        <v>5.216093744103929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45598.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>everton</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>fulham</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,53 +1085,53 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3530351437699681</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2803514376996806</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3666134185303515</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04910340204457841</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3196344375610352</v>
+        <v>0.3060139119625092</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3744441568851471</v>
+        <v>0.4548696875572205</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3059214353561401</v>
+        <v>0.2391165196895599</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09409271918546652</v>
+        <v>0.1771280141209897</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09409271918546652</v>
+        <v>0.1771280141209897</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3744441568851471</v>
+        <v>0.4548696875572205</v>
       </c>
       <c r="Z7" t="n">
         <v>3.4</v>
@@ -1142,26 +1142,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.488610157189445</v>
+        <v>5.877222526928589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45598.60416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.3559693318729463</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.2880613362541073</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.3559693318729463</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.06814858145656633</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.300824373960495</v>
+        <v>0.3209521770477295</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4699707627296448</v>
+        <v>0.4095042049884796</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2292047888040543</v>
+        <v>0.2695436477661133</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2452516616060493</v>
+        <v>0.1214428687343723</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2452516616060493</v>
+        <v>0.1214428687343723</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4699707627296448</v>
+        <v>0.4095042049884796</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,26 +1238,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.378609590491235</v>
+        <v>5.29106995754145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1277,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.1</v>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2324080051646223</v>
+        <v>0.5210981189628877</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2382182052937379</v>
+        <v>0.2287747839349263</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5293737895416398</v>
+        <v>0.2501270971021861</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04945799457994582</v>
+        <v>0.06612466124661243</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2213420569896698</v>
+        <v>0.3553861379623413</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3242479562759399</v>
+        <v>0.3705885410308838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4544099569320679</v>
+        <v>0.2740253508090973</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.07496383260957196</v>
+        <v>0.1418137570959575</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.07496383260957196</v>
+        <v>0.1418137570959575</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4544099569320679</v>
+        <v>0.3705885410308838</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,26 +1334,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.233633138966233</v>
+        <v>4.788253385854215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1373,56 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3311067603362892</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2542899919382701</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4146032477254405</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04867149758454126</v>
+        <v>0.06334841628959276</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2703346908092499</v>
+        <v>0.313491016626358</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3729034066200256</v>
+        <v>0.4183876514434814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3567618727684021</v>
+        <v>0.2681213617324829</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1186134146817555</v>
+        <v>0.1417919067626304</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1186134146817555</v>
+        <v>0.1417919067626304</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3729034066200256</v>
+        <v>0.4183876514434814</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,26 +1430,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.47425534105529</v>
+        <v>5.405850065010214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1469,56 +1469,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3800403225806452</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2923387096774194</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3276209677419355</v>
+        <v>0.2705667276051189</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0525198938992042</v>
+        <v>0.05598455598455576</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3565034568309784</v>
+        <v>0.3107284307479858</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4090585112571716</v>
+        <v>0.5152260065078735</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2344381064176559</v>
+        <v>0.1740455627441406</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1167198015797523</v>
+        <v>0.2592845074219503</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1167198015797523</v>
+        <v>0.2592845074219503</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4090585112571716</v>
+        <v>0.5152260065078735</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1526,7 +1526,967 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3.811104142010362</v>
+        <v>6.657066792402187</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2621082621082621</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3276353276353276</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05978260869565233</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2863462865352631</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3893815875053406</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3242721259593964</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1272733253970785</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1272733253970785</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3893815875053406</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.031072195527918</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4072069160539711</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2675931162640381</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3251999676819907</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06771911663216024</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3946582078933716</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3251065611839294</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.280235230922699</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.0125487081605995</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.0125487081605995</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3946582078933716</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.09924968252893</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>west ham</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4942630185348632</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2697263901147396</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2360105913503972</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05927449513836947</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4694347381591797</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2931571006774902</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2374081909656525</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.02482828037568352</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.02482828037568352</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4694347381591797</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.065412784150162</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>southampton</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4918386424102969</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2472136334220176</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2609477241676853</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06449588193870381</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4304688274860382</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3050307929515839</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2645003795623779</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.06136981492425869</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.06136981492425869</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4304688274860382</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.561946991078018</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1873915558126084</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2342394447657606</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.578368999421631</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06728395061728398</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2041287422180176</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2842639684677124</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5116072297096252</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.06676176971200576</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.06676176971200576</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5116072297096252</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.610309760442531</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>liverpool</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.664390756302521</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1640756302521008</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1715336134453781</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05995657740911886</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.536185622215271</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3014119267463684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1624024510383606</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.12820513408725</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.12820513408725</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.536185622215271</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.099630822480441</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KK9ggF3s</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6964285714285715</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1578571428571429</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1457142857142857</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05580693815987914</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.630205512046814</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2340293526649475</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1357650905847549</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.06622305938175754</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.06622305938175754</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.630205512046814</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.142679394370886</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>newcastle</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3507014028056112</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2705410821643286</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3787575150300601</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05608465608465618</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2622977197170258</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3495545387268066</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3881476819515228</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.009390166921462717</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.009390166921462717</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3881476819515228</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.015129305255443</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ipswich</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7662835249042146</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1558109833971903</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.07790549169859515</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06967213114754101</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.6978784203529358</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2133120447397232</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.08880952000617981</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.06840510455127879</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.06840510455127879</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.6978784203529358</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.017058918967102</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CEnSxfJ0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2104300260543823</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.4436271488666534</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3459427952766418</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1754325368843455</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.1754325368843455</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.4436271488666534</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.731961359918522</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2674124864669793</v>
+        <v>0.2424114225277631</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.2626123744050766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.492601948754962</v>
+        <v>0.4949762030671601</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06844033159822649</v>
+        <v>0.05774824361211817</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1892061829566956</v>
+        <v>0.2341693490743637</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3946299850940704</v>
+        <v>0.3661408126354218</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4161638617515564</v>
+        <v>0.399689793586731</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.0764380870034056</v>
+        <v>-0.09528640948042916</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0764380870034056</v>
+        <v>-0.09528640948042916</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4161638617515564</v>
+        <v>0.399689793586731</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.377117205402176</v>
+        <v>5.164261156346831</v>
       </c>
     </row>
     <row r="3">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.16450818118643</v>
+        <v>0.1797999177744278</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2252195337671362</v>
+        <v>0.2302316020282308</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6102722850464337</v>
+        <v>0.5899684801973414</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05716957189607963</v>
+        <v>0.0593786295005807</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2029496431350708</v>
+        <v>0.1864132285118103</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3178140819072723</v>
+        <v>0.3068226873874664</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4792363047599792</v>
+        <v>0.5067640542984009</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1310359802864545</v>
+        <v>-0.0832044258989405</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1310359802864545</v>
+        <v>-0.0832044258989405</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4792363047599792</v>
+        <v>0.5067640542984009</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.345519090371639</v>
+        <v>6.547732674285006</v>
       </c>
     </row>
     <row r="4">
@@ -821,29 +821,29 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2861753106117249</v>
+        <v>0.3219195306301117</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3283967971801758</v>
+        <v>0.3356355130672455</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3854278922080994</v>
+        <v>0.3424450159072876</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.07900765874506438</v>
+        <v>0.03602478244425261</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07900765874506438</v>
+        <v>0.03602478244425261</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3854278922080994</v>
+        <v>0.3424450159072876</v>
       </c>
       <c r="Z4" t="n">
         <v>3.1</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.979987791134332</v>
+        <v>4.424620098413463</v>
       </c>
     </row>
     <row r="5">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6585824796153043</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2078193602341626</v>
+        <v>0.1909090909090909</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1335981601505331</v>
+        <v>0.1272727272727273</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06930471719204112</v>
+        <v>0.04761904761904767</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6612443327903748</v>
+        <v>0.6000548005104065</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2605928778648376</v>
+        <v>0.3242278099060059</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07816275209188461</v>
+        <v>0.07571738213300705</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.002661853175070505</v>
+        <v>-0.08176338130777527</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002661853175070505</v>
+        <v>-0.08176338130777527</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6612443327903748</v>
+        <v>0.6000548005104065</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>8.543721849987156</v>
+        <v>7.75311190747958</v>
       </c>
     </row>
     <row r="6">
@@ -995,47 +995,47 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4374145674672915</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2686975200156219</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2938879125170865</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06333056478405319</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2642138004302979</v>
+        <v>0.263253927230835</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4037013947963715</v>
+        <v>0.3768643736839294</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3320848047733307</v>
+        <v>0.359881579875946</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1350038747807495</v>
+        <v>0.1057524134240899</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1350038747807495</v>
+        <v>0.1057524134240899</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4037013947963715</v>
+        <v>0.3768643736839294</v>
       </c>
       <c r="Z6" t="n">
         <v>3.5</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.216093744103929</v>
+        <v>4.869341367869008</v>
       </c>
     </row>
     <row r="7">
@@ -1085,22 +1085,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3632006498781478</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="M7" t="n">
         <v>0.2777416734362307</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3590576766856215</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="O7" t="n">
         <v>0.05896116855633737</v>
@@ -1109,29 +1109,29 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3060139119625092</v>
+        <v>0.3158493936061859</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4548696875572205</v>
+        <v>0.4297194182872772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2391165196895599</v>
+        <v>0.2544311881065369</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1771280141209897</v>
+        <v>0.1519777448510465</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1771280141209897</v>
+        <v>0.1519777448510465</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4548696875572205</v>
+        <v>0.4297194182872772</v>
       </c>
       <c r="Z7" t="n">
         <v>3.4</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.877222526928589</v>
+        <v>5.552264119817683</v>
       </c>
     </row>
     <row r="8">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3559693318729463</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2880613362541073</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3559693318729463</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06814858145656633</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3209521770477295</v>
+        <v>0.2659438252449036</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4095042049884796</v>
+        <v>0.4160873293876648</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2695436477661133</v>
+        <v>0.3179688453674316</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1214428687343723</v>
+        <v>0.1374644310690099</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1214428687343723</v>
+        <v>0.1374644310690099</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4095042049884796</v>
+        <v>0.4160873293876648</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.29106995754145</v>
+        <v>5.376128355748294</v>
       </c>
     </row>
     <row r="9">
@@ -1277,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5210981189628877</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2287747839349263</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2501270971021861</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06612466124661243</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3553861379623413</v>
+        <v>0.3639144003391266</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3705885410308838</v>
+        <v>0.3591214716434479</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2740253508090973</v>
+        <v>0.2769640982151031</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1418137570959575</v>
+        <v>-0.134079789728656</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1418137570959575</v>
+        <v>-0.134079789728656</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3705885410308838</v>
+        <v>0.3639144003391266</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.788253385854215</v>
+        <v>3.835818431026543</v>
       </c>
     </row>
     <row r="10">
@@ -1376,53 +1376,53 @@
         <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
         <v>2.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2653061224489797</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.04700854700854684</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.313491016626358</v>
+        <v>0.2972066402435303</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4183876514434814</v>
+        <v>0.394818902015686</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2681213617324829</v>
+        <v>0.3079743981361389</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1417919067626304</v>
+        <v>0.1295127795667064</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1417919067626304</v>
+        <v>0.1295127795667064</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4183876514434814</v>
+        <v>0.394818902015686</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.405850065010214</v>
+        <v>5.101325958749232</v>
       </c>
     </row>
     <row r="11">
@@ -1472,53 +1472,53 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4751131221719458</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2533936651583711</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2705667276051189</v>
+        <v>0.2714932126696833</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05598455598455576</v>
+        <v>0.05238095238095219</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3107284307479858</v>
+        <v>0.3409564793109894</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5152260065078735</v>
+        <v>0.5051291584968567</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1740455627441406</v>
+        <v>0.1539143621921539</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2592845074219503</v>
+        <v>0.2517354933384856</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2592845074219503</v>
+        <v>0.2517354933384856</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5152260065078735</v>
+        <v>0.5051291584968567</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1526,967 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.657066792402187</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>brentford</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>bournemouth</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4102564102564102</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2621082621082621</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.3276353276353276</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.05978260869565233</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.2863462865352631</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3893815875053406</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.3242721259593964</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.1272733253970785</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.1272733253970785</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.3893815875053406</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.031072195527918</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>crystal palace</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>fulham</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" t="n">
-        <v>481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4072069160539711</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2675931162640381</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.3251999676819907</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06771911663216024</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3946582078933716</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3251065611839294</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.280235230922699</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.0125487081605995</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.0125487081605995</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.3946582078933716</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>5.09924968252893</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>west ham</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>everton</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.4942630185348632</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2697263901147396</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.2360105913503972</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.05927449513836947</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.4694347381591797</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2931571006774902</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2374081909656525</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.02482828037568352</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.02482828037568352</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4694347381591797</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.065412784150162</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>wolves</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>southampton</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>48</v>
-      </c>
-      <c r="F15" t="n">
-        <v>481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.4918386424102969</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2472136334220176</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2609477241676853</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06449588193870381</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.4304688274860382</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3050307929515839</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2645003795623779</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.06136981492425869</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.06136981492425869</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4304688274860382</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.561946991078018</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>brighton</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>manchester city</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F16" t="n">
-        <v>481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1873915558126084</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2342394447657606</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.578368999421631</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06728395061728398</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2041287422180176</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.2842639684677124</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.5116072297096252</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.06676176971200576</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.06676176971200576</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.5116072297096252</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>6.610309760442531</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>liverpool</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>aston villa</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" t="n">
-        <v>481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.664390756302521</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.1640756302521008</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.1715336134453781</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.05995657740911886</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.536185622215271</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3014119267463684</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.1624024510383606</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-0.12820513408725</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.12820513408725</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.536185622215271</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.099630822480441</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>manchester utd</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>leicester</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>48</v>
-      </c>
-      <c r="F18" t="n">
-        <v>481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6964285714285715</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.1578571428571429</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.05580693815987914</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.630205512046814</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2340293526649475</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.1357650905847549</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>-0.06622305938175754</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.06622305938175754</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.630205512046814</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.142679394370886</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>newcastle</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>48</v>
-      </c>
-      <c r="F19" t="n">
-        <v>481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3507014028056112</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2705410821643286</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.3787575150300601</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.05608465608465618</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2622977197170258</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3495545387268066</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3881476819515228</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.009390166921462717</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.009390166921462717</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.3881476819515228</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.015129305255443</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ipswich</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>48</v>
-      </c>
-      <c r="F20" t="n">
-        <v>481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7662835249042146</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.1558109833971903</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.07790549169859515</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.06967213114754101</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.6978784203529358</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2133120447397232</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.08880952000617981</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>-0.06840510455127879</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.06840510455127879</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.6978784203529358</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.017058918967102</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45606.5625</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>chelsea</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>arsenal</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>48</v>
-      </c>
-      <c r="F21" t="n">
-        <v>481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.3236831523924407</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.268194611982308</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.4081222356252514</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.06532448061683449</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2104300260543823</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.4436271488666534</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.3459427952766418</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>0.1754325368843455</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.1754325368843455</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.4436271488666534</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.731961359918522</v>
+        <v>6.52660872011339</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.39583333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2424114225277631</v>
+        <v>0.3940828402366864</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2626123744050766</v>
+        <v>0.2556213017751479</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4949762030671601</v>
+        <v>0.3502958579881656</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05774824361211817</v>
+        <v>0.05730730730730738</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2341693490743637</v>
+        <v>0.3078418672084808</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3661408126354218</v>
+        <v>0.361346960067749</v>
       </c>
       <c r="S2" t="n">
-        <v>0.399689793586731</v>
+        <v>0.3308112323284149</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.09528640948042916</v>
+        <v>0.1057256582926012</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.09528640948042916</v>
+        <v>0.1057256582926012</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.399689793586731</v>
+        <v>0.361346960067749</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.164261156346831</v>
+        <v>13.38596147096674</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1797999177744278</v>
+        <v>0.3864042933810376</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2302316020282308</v>
+        <v>0.262969588550984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5899684801973414</v>
+        <v>0.3506261180679786</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0593786295005807</v>
+        <v>0.05631141345427038</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1864132285118103</v>
+        <v>0.4053996801376343</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3068226873874664</v>
+        <v>0.3239441215991974</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5067640542984009</v>
+        <v>0.2706562578678131</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.0832044258989405</v>
+        <v>0.01899538675659668</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0832044258989405</v>
+        <v>0.01899538675659668</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5067640542984009</v>
+        <v>0.4053996801376343</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.547732674285006</v>
+        <v>12.16285389166539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4221789883268482</v>
+        <v>0.4505119453924914</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2714007782101167</v>
+        <v>0.2866894197952218</v>
       </c>
       <c r="N4" t="n">
-        <v>0.306420233463035</v>
+        <v>0.2627986348122867</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05273937532002049</v>
+        <v>0.05699855699855716</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3219195306301117</v>
+        <v>0.3898195028305054</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3356355130672455</v>
+        <v>0.3265766799449921</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3424450159072876</v>
+        <v>0.2836038172245026</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.03602478244425261</v>
+        <v>-0.06069244256198603</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03602478244425261</v>
+        <v>-0.06069244256198603</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3424450159072876</v>
+        <v>0.3898195028305054</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,26 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.424620098413463</v>
+        <v>9.432542124333931</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.4950053514092044</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1909090909090909</v>
+        <v>0.2508027113806636</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1272727272727273</v>
+        <v>0.254191937210132</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.06325272641062107</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6000548005104065</v>
+        <v>0.3786422312259674</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3242278099060059</v>
+        <v>0.3237687945365906</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07571738213300705</v>
+        <v>0.297588974237442</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.08176338130777527</v>
+        <v>-0.116363120183237</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.08176338130777527</v>
+        <v>-0.116363120183237</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6000548005104065</v>
+        <v>0.3786422312259674</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,26 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.75311190747958</v>
+        <v>7.516728527958243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.210304843837666</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.2426594351973069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.5470357209650272</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.0566671607134035</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.263253927230835</v>
+        <v>0.1807558834552765</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3768643736839294</v>
+        <v>0.2972142100334167</v>
       </c>
       <c r="S6" t="n">
-        <v>0.359881579875946</v>
+        <v>0.5220298171043396</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1057524134240899</v>
+        <v>-0.02500590386068757</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1057524134240899</v>
+        <v>-0.02500590386068757</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3768643736839294</v>
+        <v>0.5220298171043396</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.869341367869008</v>
+        <v>14.24434379429987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,56 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3590576766856215</v>
+        <v>0.6389405204460966</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2777416734362307</v>
+        <v>0.1891263940520446</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3632006498781478</v>
+        <v>0.1719330855018587</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05896116855633737</v>
+        <v>0.05749385749385749</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3158493936061859</v>
+        <v>0.5496260523796082</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4297194182872772</v>
+        <v>0.2800574898719788</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2544311881065369</v>
+        <v>0.1703164726495743</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1519777448510465</v>
+        <v>-0.08931446806648846</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1519777448510465</v>
+        <v>-0.08931446806648846</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4297194182872772</v>
+        <v>0.5496260523796082</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,26 +1142,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.552264119817683</v>
+        <v>13.19219515347669</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3947157726180945</v>
+        <v>0.6845564074479737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.1642935377875137</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.1511500547645126</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05561189993238669</v>
+        <v>0.0585507246376813</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2659438252449036</v>
+        <v>0.6246979236602783</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4160873293876648</v>
+        <v>0.2300899177789688</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3179688453674316</v>
+        <v>0.1452121138572693</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1374644310690099</v>
+        <v>-0.05985848378769543</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1374644310690099</v>
+        <v>-0.05985848378769543</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4160873293876648</v>
+        <v>0.6246979236602783</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,26 +1238,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.376128355748294</v>
+        <v>16.18788745518694</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1277,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4979941900677826</v>
+        <v>0.3593501499808749</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2377922257573662</v>
+        <v>0.2700259698427717</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2642135841748513</v>
+        <v>0.3706238801763534</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05133798720186156</v>
+        <v>0.05809928534151299</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3639144003391266</v>
+        <v>0.2653241157531738</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3591214716434479</v>
+        <v>0.3373605012893677</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2769640982151031</v>
+        <v>0.3973154425621033</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.134079789728656</v>
+        <v>0.02669156238574988</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.134079789728656</v>
+        <v>0.02669156238574988</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3639144003391266</v>
+        <v>0.3973154425621033</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,26 +1334,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.835818431026543</v>
+        <v>12.15173231857726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1373,56 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.7612456747404844</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2653061224489797</v>
+        <v>0.1522491349480969</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.08650519031141868</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04700854700854684</v>
+        <v>0.05090909090909101</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2972066402435303</v>
+        <v>0.7240597009658813</v>
       </c>
       <c r="R10" t="n">
-        <v>0.394818902015686</v>
+        <v>0.1891239732503891</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3079743981361389</v>
+        <v>0.08681630343198776</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1295127795667064</v>
+        <v>-0.03718597377460309</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1295127795667064</v>
+        <v>-0.03718597377460309</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.394818902015686</v>
+        <v>0.7240597009658813</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,26 +1430,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.101325958749232</v>
+        <v>19.68530135609057</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1469,56 +1469,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4751131221719458</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2533936651583711</v>
+        <v>0.2777017783857729</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2714932126696833</v>
+        <v>0.3967168262653898</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05238095238095219</v>
+        <v>0.05911330049261099</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3409564793109894</v>
+        <v>0.2332454323768616</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5051291584968567</v>
+        <v>0.4092691540718079</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1539143621921539</v>
+        <v>0.3574853837490082</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2517354933384856</v>
+        <v>0.131567375686035</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2517354933384856</v>
+        <v>0.131567375686035</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5051291584968567</v>
+        <v>0.4092691540718079</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.52660872011339</v>
+        <v>15.49998151217767</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>13.38596147096674</v>
+        <v>12.28400986287721</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>12.16285389166539</v>
+        <v>11.16159025931827</v>
       </c>
     </row>
     <row r="4">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>9.432542124333931</v>
+        <v>8.656041685062059</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.516728527958243</v>
+        <v>6.897940620423809</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>14.24434379429987</v>
+        <v>13.07172891830805</v>
       </c>
     </row>
     <row r="7">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>13.19219515347669</v>
+        <v>12.10619466743505</v>
       </c>
     </row>
     <row r="8">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>16.18788745518694</v>
+        <v>14.85527726864893</v>
       </c>
     </row>
     <row r="9">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>12.15173231857726</v>
+        <v>11.15138423012854</v>
       </c>
     </row>
     <row r="10">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>19.68530135609057</v>
+        <v>18.06477902513062</v>
       </c>
     </row>
     <row r="11">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>15.49998151217767</v>
+        <v>14.22400073263127</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/predicciones.xlsx
+++ b/data/england/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>2.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3940828402366864</v>
+        <v>0.3787575150300601</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2556213017751479</v>
+        <v>0.2705410821643286</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3502958579881656</v>
+        <v>0.3507014028056112</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05730730730730738</v>
+        <v>0.05608465608465618</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3078418672084808</v>
+        <v>0.2797083581673301</v>
       </c>
       <c r="R2" t="n">
-        <v>0.361346960067749</v>
+        <v>0.197922895538261</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3308112323284149</v>
+        <v>0.5223687462944088</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1057256582926012</v>
+        <v>0.1716673434887976</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1057256582926012</v>
+        <v>0.1716673434887976</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.361346960067749</v>
+        <v>0.5223687462944088</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>12.28400986287721</v>
+        <v>6.045190601247996</v>
       </c>
     </row>
     <row r="3">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3864042933810376</v>
+        <v>0.3465346534653466</v>
       </c>
       <c r="M3" t="n">
-        <v>0.262969588550984</v>
+        <v>0.2722772277227723</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3506261180679786</v>
+        <v>0.3811881188118812</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05631141345427038</v>
+        <v>0.04935064935064926</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4053996801376343</v>
+        <v>0.5492019214616395</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3239441215991974</v>
+        <v>0.2663478059471888</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2706562578678131</v>
+        <v>0.1844502725911718</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.01899538675659668</v>
+        <v>0.2026672679962929</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01899538675659668</v>
+        <v>0.2026672679962929</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4053996801376343</v>
+        <v>0.5492019214616395</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>11.16159025931827</v>
+        <v>6.799354967234056</v>
       </c>
     </row>
     <row r="4">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4505119453924914</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2866894197952218</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2627986348122867</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05699855699855716</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3898195028305054</v>
+        <v>0.508869364374401</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3265766799449921</v>
+        <v>0.4028344811580645</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2836038172245026</v>
+        <v>0.0882961544675344</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.06069244256198603</v>
+        <v>0.06731092281595946</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.06069244256198603</v>
+        <v>0.06731092281595946</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3898195028305054</v>
+        <v>0.508869364374401</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>8.656041685062059</v>
+        <v>3.890565278191194</v>
       </c>
     </row>
     <row r="5">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4950053514092044</v>
+        <v>0.4953764861294584</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2508027113806636</v>
+        <v>0.2523117569352708</v>
       </c>
       <c r="N5" t="n">
-        <v>0.254191937210132</v>
+        <v>0.2523117569352708</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06325272641062107</v>
+        <v>0.05689354275741709</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3786422312259674</v>
+        <v>0.47726904936604</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3237687945365906</v>
+        <v>0.2400526308861448</v>
       </c>
       <c r="S5" t="n">
-        <v>0.297588974237442</v>
+        <v>0.2826783197478153</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.116363120183237</v>
+        <v>-0.01810743676341842</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.116363120183237</v>
+        <v>-0.01810743676341842</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3786422312259674</v>
+        <v>0.47726904936604</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.897940620423809</v>
+        <v>2.024196511561831</v>
       </c>
     </row>
     <row r="6">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.210304843837666</v>
+        <v>0.2315325248070562</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2426594351973069</v>
+        <v>0.2260198456449835</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5470357209650272</v>
+        <v>0.5424476295479603</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0566671607134035</v>
+        <v>0.05342624854819977</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1807558834552765</v>
+        <v>0.05587305509160116</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2972142100334167</v>
+        <v>0.3446916743651515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5220298171043396</v>
+        <v>0.5994352705432473</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.02500590386068757</v>
+        <v>0.05698764099528697</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.02500590386068757</v>
+        <v>0.05698764099528697</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5220298171043396</v>
+        <v>0.5994352705432473</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>13.07172891830805</v>
+        <v>4.136929172621976</v>
       </c>
     </row>
     <row r="7">
@@ -1085,56 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6389405204460966</v>
+        <v>0.6716197598897855</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1891263940520446</v>
+        <v>0.1816571541035229</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1719330855018587</v>
+        <v>0.1467230860066916</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05749385749385749</v>
+        <v>0.04854769643502044</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5496260523796082</v>
+        <v>0.6018557569807923</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2800574898719788</v>
+        <v>0.3202946445129535</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1703164726495743</v>
+        <v>0.07784959850625414</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08931446806648846</v>
+        <v>-0.06976400290899321</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08931446806648846</v>
+        <v>-0.06976400290899321</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5496260523796082</v>
+        <v>0.6018557569807923</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>12.10619466743505</v>
+        <v>1.613998726724097</v>
       </c>
     </row>
     <row r="8">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6845564074479737</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1642935377875137</v>
+        <v>0.1715315315315316</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1511500547645126</v>
+        <v>0.1347747747747748</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0585507246376813</v>
+        <v>0.05996944232238333</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6246979236602783</v>
+        <v>0.5736403463949913</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2300899177789688</v>
+        <v>0.3644374378711059</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1452121138572693</v>
+        <v>0.06192221573390277</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.05985848378769543</v>
+        <v>-0.1200533472987024</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.05985848378769543</v>
+        <v>-0.1200533472987024</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6246979236602783</v>
+        <v>0.5736403463949913</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>14.85527726864893</v>
+        <v>0.4671347860009079</v>
       </c>
     </row>
     <row r="9">
@@ -1277,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.63</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.55</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3593501499808749</v>
+        <v>0.3515188335358444</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2700259698427717</v>
+        <v>0.287606318347509</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3706238801763534</v>
+        <v>0.3608748481166464</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05809928534151299</v>
+        <v>0.05362881028280286</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2653241157531738</v>
+        <v>0.1919490033785586</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3373605012893677</v>
+        <v>0.3633721987060077</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3973154425621033</v>
+        <v>0.4446787979154337</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.02669156238574988</v>
+        <v>0.08380394979878736</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02669156238574988</v>
+        <v>0.08380394979878736</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3973154425621033</v>
+        <v>0.4446787979154337</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>11.15138423012854</v>
+        <v>3.899472985552916</v>
       </c>
     </row>
     <row r="10">
@@ -1373,56 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="J10" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7612456747404844</v>
+        <v>0.7561209793566971</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1522491349480969</v>
+        <v>0.1371819491118579</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08650519031141868</v>
+        <v>0.106697071531445</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05090909090909101</v>
+        <v>0.04136982877140349</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7240597009658813</v>
+        <v>0.6484027698424354</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1891239732503891</v>
+        <v>0.3011042777339618</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08681630343198776</v>
+        <v>0.05049295242360272</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.03718597377460309</v>
+        <v>-0.1077182095142617</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.03718597377460309</v>
+        <v>-0.1077182095142617</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7240597009658813</v>
+        <v>0.6484027698424354</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>18.06477902513062</v>
+        <v>1.087649658926943</v>
       </c>
     </row>
     <row r="11">
@@ -1469,64 +1469,736 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2777017783857729</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3967168262653898</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05911330049261099</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2332454323768616</v>
+        <v>0.5423281239799856</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4092691540718079</v>
+        <v>0.1883515769780034</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3574853837490082</v>
+        <v>0.2693202990420109</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.131567375686035</v>
+        <v>0.1918126600624599</v>
       </c>
       <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1918126600624599</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5423281239799856</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.547893821149127</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>chelsea</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1893830703012913</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.236728837876614</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5738880918220947</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05606060606060614</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1413065091688256</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4078634062770092</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4508300845541651</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1230580072679295</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1230580072679295</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4508300845541651</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="X11" t="n">
-        <v>0.131567375686035</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4092691540718079</v>
-      </c>
-      <c r="Z11" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nottingham</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7155356795644564</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1655065137079526</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1189578067275909</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05079274272638123</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7501533031177688</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1480937774734568</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1017529194087745</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.03461762355331244</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.03461762355331244</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7501533031177688</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.443118986655093</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>aston villa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>crystal palace</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5574781823653325</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2430033102618116</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1995185073728558</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05517186631737725</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.318295233421524</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.467122865816885</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2145819007615911</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2241195555550734</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2241195555550734</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.467122865816885</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.818005440185892</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bournemouth</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>brighton</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="K15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4302959501557632</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2784267912772586</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2912772585669782</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05635540929658589</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.740850919529086</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1916123727298028</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.06753670774111104</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.3105549693733228</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3105549693733228</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.740850919529086</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB11" t="n">
-        <v>14.22400073263127</v>
+      <c r="AB15" t="n">
+        <v>9.915353985111887</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>everton</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>brentford</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4102408758399712</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2792937644542169</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3104653597058119</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.002118640214719858</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.002118640214719858</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4102408758399712</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.093577183494253</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fulham</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>wolves</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5574781823653325</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2430033102618116</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1995185073728558</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05517186631737725</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3357476902870436</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2702324548598613</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3940198548530951</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1945013474802393</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1945013474802393</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3940198548530951</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.860126223870261</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>manchester city</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>tottenham</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6026768243366641</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2252863367163244</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1720368389470114</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05685609507265554</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2355670630895556</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6893672198989927</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.07506571701145179</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.4640808831826683</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.4640808831826683</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6893672198989927</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>12.72845376314833</v>
       </c>
     </row>
   </sheetData>
